--- a/docs/gara-appalto/SERVICE-RESOURCE-MODEL-W3SUITE-FINAL.xlsx
+++ b/docs/gara-appalto/SERVICE-RESOURCE-MODEL-W3SUITE-FINAL.xlsx
@@ -5924,46 +5924,46 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A4:AL18"/>
+  <dimension ref="A4:AL19"/>
   <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="24.83203125" customWidth="1"/>
-    <col min="3" max="3" width="24.83203125" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" customWidth="1"/>
-    <col min="5" max="5" width="24.83203125" customWidth="1"/>
-    <col min="6" max="6" width="24.83203125" customWidth="1"/>
-    <col min="7" max="7" width="24.83203125" customWidth="1"/>
-    <col min="8" max="8" width="24.83203125" customWidth="1"/>
-    <col min="9" max="9" width="24.83203125" customWidth="1"/>
-    <col min="10" max="10" width="24.83203125" customWidth="1"/>
-    <col min="11" max="11" width="24.83203125" customWidth="1"/>
-    <col min="12" max="12" width="24.83203125" customWidth="1"/>
-    <col min="13" max="13" width="24.83203125" customWidth="1"/>
-    <col min="14" max="14" width="24.83203125" customWidth="1"/>
-    <col min="15" max="15" width="24.83203125" customWidth="1"/>
-    <col min="16" max="16" width="24.83203125" customWidth="1"/>
-    <col min="17" max="17" width="24.83203125" customWidth="1"/>
-    <col min="18" max="18" width="24.83203125" customWidth="1"/>
-    <col min="19" max="19" width="24.83203125" customWidth="1"/>
-    <col min="20" max="20" width="24.83203125" customWidth="1"/>
-    <col min="21" max="21" width="24.83203125" customWidth="1"/>
-    <col min="22" max="22" width="24.83203125" customWidth="1"/>
-    <col min="23" max="23" width="24.83203125" customWidth="1"/>
-    <col min="24" max="24" width="24.83203125" customWidth="1"/>
-    <col min="25" max="25" width="24.83203125" customWidth="1"/>
-    <col min="26" max="26" width="24.83203125" customWidth="1"/>
-    <col min="27" max="27" width="24.83203125" customWidth="1"/>
-    <col min="28" max="28" width="24.83203125" customWidth="1"/>
-    <col min="29" max="29" width="24.83203125" customWidth="1"/>
-    <col min="30" max="30" width="24.83203125" customWidth="1"/>
-    <col min="31" max="31" width="24.83203125" customWidth="1"/>
-    <col min="32" max="32" width="24.83203125" customWidth="1"/>
-    <col min="33" max="33" width="24.83203125" customWidth="1"/>
-    <col min="34" max="34" width="24.83203125" customWidth="1"/>
-    <col min="35" max="35" width="24.83203125" customWidth="1"/>
-    <col min="36" max="36" width="24.83203125" customWidth="1"/>
-    <col min="37" max="37" width="24.83203125" customWidth="1"/>
-    <col min="38" max="38" width="24.83203125" customWidth="1"/>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
+    <col min="8" max="8" width="26.83203125" customWidth="1"/>
+    <col min="9" max="9" width="26.83203125" customWidth="1"/>
+    <col min="10" max="10" width="26.83203125" customWidth="1"/>
+    <col min="11" max="11" width="26.83203125" customWidth="1"/>
+    <col min="12" max="12" width="26.83203125" customWidth="1"/>
+    <col min="13" max="13" width="26.83203125" customWidth="1"/>
+    <col min="14" max="14" width="26.83203125" customWidth="1"/>
+    <col min="15" max="15" width="26.83203125" customWidth="1"/>
+    <col min="16" max="16" width="26.83203125" customWidth="1"/>
+    <col min="17" max="17" width="26.83203125" customWidth="1"/>
+    <col min="18" max="18" width="26.83203125" customWidth="1"/>
+    <col min="19" max="19" width="26.83203125" customWidth="1"/>
+    <col min="20" max="20" width="26.83203125" customWidth="1"/>
+    <col min="21" max="21" width="26.83203125" customWidth="1"/>
+    <col min="22" max="22" width="26.83203125" customWidth="1"/>
+    <col min="23" max="23" width="26.83203125" customWidth="1"/>
+    <col min="24" max="24" width="26.83203125" customWidth="1"/>
+    <col min="25" max="25" width="26.83203125" customWidth="1"/>
+    <col min="26" max="26" width="26.83203125" customWidth="1"/>
+    <col min="27" max="27" width="26.83203125" customWidth="1"/>
+    <col min="28" max="28" width="26.83203125" customWidth="1"/>
+    <col min="29" max="29" width="26.83203125" customWidth="1"/>
+    <col min="30" max="30" width="26.83203125" customWidth="1"/>
+    <col min="31" max="31" width="26.83203125" customWidth="1"/>
+    <col min="32" max="32" width="26.83203125" customWidth="1"/>
+    <col min="33" max="33" width="26.83203125" customWidth="1"/>
+    <col min="34" max="34" width="26.83203125" customWidth="1"/>
+    <col min="35" max="35" width="26.83203125" customWidth="1"/>
+    <col min="36" max="36" width="26.83203125" customWidth="1"/>
+    <col min="37" max="37" width="26.83203125" customWidth="1"/>
+    <col min="38" max="38" width="26.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4">
@@ -6294,7 +6294,7 @@
         <v>Multinodo Cluster</v>
       </c>
       <c r="K8" t="str">
-        <v>Seeweb Multinodo Italy</v>
+        <v>Seeweb Multinodo Italy (DC1)</v>
       </c>
       <c r="L8" t="str">
         <v>Resources - SW configuration</v>
@@ -6354,7 +6354,7 @@
         <v>1 week</v>
       </c>
       <c r="AE8" t="str">
-        <v xml:space="preserve">Zone Resilent </v>
+        <v xml:space="preserve">Region Resilent </v>
       </c>
       <c r="AF8" t="str">
         <v>Automated By App</v>
@@ -6369,13 +6369,13 @@
         <v>HW/SW vendor</v>
       </c>
       <c r="AJ8" t="str">
-        <v>VM Management, Backup, Snapshot</v>
+        <v>VM Mgmt, PBS Replication</v>
       </c>
       <c r="AK8" t="str">
         <v>Public Cloud Consumption</v>
       </c>
       <c r="AL8" t="str">
-        <v>Seeweb Multinodo Contract</v>
+        <v>Seeweb Multinodo + PBS</v>
       </c>
     </row>
     <row r="9">
@@ -6398,19 +6398,19 @@
         <v>Vendor Private</v>
       </c>
       <c r="G9" t="str">
-        <v>HW Appliance</v>
+        <v>Full IaaS</v>
       </c>
       <c r="H9" t="str">
-        <v>Fortinet Inc.</v>
+        <v>Proxmox Server Solutions GmbH</v>
       </c>
       <c r="I9" t="str">
-        <v>HW Appliance - FortiGate NGFW</v>
+        <v>Bare Metal-Linux OS</v>
       </c>
       <c r="J9" t="str">
-        <v>2 (HA Cluster)</v>
+        <v>1 (Dedicato)</v>
       </c>
       <c r="K9" t="str">
-        <v>Seeweb Multinodo Italy</v>
+        <v>Seeweb Italy (DC2 - DR Site)</v>
       </c>
       <c r="L9" t="str">
         <v>Resources - SW configuration</v>
@@ -6419,10 +6419,10 @@
         <v>Active</v>
       </c>
       <c r="N9" t="str">
-        <v>Fixed capacity</v>
+        <v>Ops Manual</v>
       </c>
       <c r="O9" t="str">
-        <v>Do not scale - Fixed capacity</v>
+        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
       </c>
       <c r="P9" t="str">
         <v>No outages</v>
@@ -6440,13 +6440,13 @@
         <v>File (TXT)</v>
       </c>
       <c r="U9" t="str">
-        <v>7.4.x</v>
+        <v>3.x</v>
       </c>
       <c r="V9" t="str">
         <v>SW Bins</v>
       </c>
       <c r="W9" t="str">
-        <v>Private Others Registry</v>
+        <v>Object Store (SW bins)</v>
       </c>
       <c r="X9" t="str">
         <v>Resource Recovery</v>
@@ -6464,13 +6464,13 @@
         <v>1 month</v>
       </c>
       <c r="AC9" t="str">
-        <v>N/A</v>
+        <v>1 min</v>
       </c>
       <c r="AD9" t="str">
-        <v>N/A</v>
+        <v>1 week</v>
       </c>
       <c r="AE9" t="str">
-        <v xml:space="preserve">Local Resilent </v>
+        <v xml:space="preserve">Region Resilent </v>
       </c>
       <c r="AF9" t="str">
         <v>Manual By Operation</v>
@@ -6479,19 +6479,19 @@
         <v>Hour (1-5)</v>
       </c>
       <c r="AH9" t="str">
-        <v>Hour (1-5)</v>
+        <v>Minutes (1-5)</v>
       </c>
       <c r="AI9" t="str">
         <v>HW/SW vendor</v>
       </c>
       <c r="AJ9" t="str">
-        <v>Security, Threat Monitoring</v>
+        <v>Backup Storage, DR</v>
       </c>
       <c r="AK9" t="str">
-        <v>COTs SW License</v>
+        <v>Public Cloud Consumption</v>
       </c>
       <c r="AL9" t="str">
-        <v>FortiCare + FortiGuard</v>
+        <v>Seeweb PBS Dedicated</v>
       </c>
     </row>
     <row r="10">
@@ -6499,10 +6499,10 @@
         <v>PROD</v>
       </c>
       <c r="B10" t="str">
-        <v>99,9%</v>
+        <v>99,5%</v>
       </c>
       <c r="C10" t="str">
-        <v>HA</v>
+        <v>HA-</v>
       </c>
       <c r="D10" t="str">
         <v>CORE PLATFORM</v>
@@ -6514,19 +6514,19 @@
         <v>Vendor Private</v>
       </c>
       <c r="G10" t="str">
-        <v>Full IaaS</v>
+        <v>HW Appliance</v>
       </c>
       <c r="H10" t="str">
-        <v>W3Suite (Easy Digital Group)</v>
+        <v>Fortinet Inc.</v>
       </c>
       <c r="I10" t="str">
-        <v>App (RunTime) - Linux native</v>
+        <v>HW Appliance - FortiGate NGFW</v>
       </c>
       <c r="J10" t="str">
-        <v>3 VPS dedicate</v>
+        <v>1 (Single)</v>
       </c>
       <c r="K10" t="str">
-        <v>Seeweb Multinodo Italy</v>
+        <v>Seeweb Multinodo Italy (DC1)</v>
       </c>
       <c r="L10" t="str">
         <v>Resources - SW configuration</v>
@@ -6535,16 +6535,16 @@
         <v>Active</v>
       </c>
       <c r="N10" t="str">
-        <v>Ops Manual</v>
+        <v>Fixed capacity</v>
       </c>
       <c r="O10" t="str">
-        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
+        <v>Do not scale - Fixed capacity</v>
       </c>
       <c r="P10" t="str">
         <v>No outages</v>
       </c>
       <c r="Q10" t="str">
-        <v>Ops - Automated</v>
+        <v>Ops - Manual</v>
       </c>
       <c r="R10" t="str">
         <v>Ops Manual - direct Log-on resource</v>
@@ -6553,16 +6553,16 @@
         <v>No outages</v>
       </c>
       <c r="T10" t="str">
-        <v>File (Ansible playbook) - VM configuration</v>
+        <v>File (TXT)</v>
       </c>
       <c r="U10" t="str">
-        <v>SemVer</v>
+        <v>7.4.x</v>
       </c>
       <c r="V10" t="str">
         <v>SW Bins</v>
       </c>
       <c r="W10" t="str">
-        <v>Object Store (SW bins)</v>
+        <v>Private Others Registry</v>
       </c>
       <c r="X10" t="str">
         <v>Resource Recovery</v>
@@ -6580,34 +6580,34 @@
         <v>1 month</v>
       </c>
       <c r="AC10" t="str">
-        <v>1 min</v>
+        <v>N/A</v>
       </c>
       <c r="AD10" t="str">
-        <v>1 week</v>
+        <v>N/A</v>
       </c>
       <c r="AE10" t="str">
-        <v xml:space="preserve">Zone Resilent </v>
+        <v xml:space="preserve">Local Resilent </v>
       </c>
       <c r="AF10" t="str">
-        <v>Automated By App</v>
+        <v>Manual By Operation</v>
       </c>
       <c r="AG10" t="str">
-        <v>Minutes (1-5)</v>
+        <v>Hour (1-5)</v>
       </c>
       <c r="AH10" t="str">
-        <v xml:space="preserve">Seconds </v>
+        <v>Hour (1-5)</v>
       </c>
       <c r="AI10" t="str">
-        <v>SW Integrator</v>
+        <v>HW/SW vendor</v>
       </c>
       <c r="AJ10" t="str">
-        <v>Deploy, Monitoring</v>
+        <v>Security, Monitoring</v>
       </c>
       <c r="AK10" t="str">
-        <v>Public Cloud Consumption</v>
+        <v>COTs SW License</v>
       </c>
       <c r="AL10" t="str">
-        <v>Seeweb VPS + W3Suite License</v>
+        <v>FortiCare + FortiGuard</v>
       </c>
     </row>
     <row r="11">
@@ -6633,16 +6633,16 @@
         <v>Full IaaS</v>
       </c>
       <c r="H11" t="str">
-        <v>F5 Networks (Nginx)</v>
+        <v>W3Suite (Easy Digital Group)</v>
       </c>
       <c r="I11" t="str">
         <v>App (RunTime) - Linux native</v>
       </c>
       <c r="J11" t="str">
-        <v>2 VPS dedicate</v>
+        <v>3 VPC</v>
       </c>
       <c r="K11" t="str">
-        <v>Seeweb Multinodo Italy</v>
+        <v>Seeweb Multinodo Italy (DC1)</v>
       </c>
       <c r="L11" t="str">
         <v>Resources - SW configuration</v>
@@ -6660,7 +6660,7 @@
         <v>No outages</v>
       </c>
       <c r="Q11" t="str">
-        <v>Ops - Manual</v>
+        <v>Ops - Automated</v>
       </c>
       <c r="R11" t="str">
         <v>Ops Manual - direct Log-on resource</v>
@@ -6669,10 +6669,10 @@
         <v>No outages</v>
       </c>
       <c r="T11" t="str">
-        <v>File (TXT)</v>
+        <v>File (Ansible playbook) - VM configuration</v>
       </c>
       <c r="U11" t="str">
-        <v>1.24.x</v>
+        <v>SemVer</v>
       </c>
       <c r="V11" t="str">
         <v>SW Bins</v>
@@ -6696,34 +6696,34 @@
         <v>1 month</v>
       </c>
       <c r="AC11" t="str">
-        <v>N/A</v>
+        <v>1 min</v>
       </c>
       <c r="AD11" t="str">
-        <v>N/A</v>
+        <v>1 week</v>
       </c>
       <c r="AE11" t="str">
-        <v xml:space="preserve">Local Resilent </v>
+        <v xml:space="preserve">Region Resilent </v>
       </c>
       <c r="AF11" t="str">
         <v>Automated By App</v>
       </c>
       <c r="AG11" t="str">
+        <v>Minutes (1-5)</v>
+      </c>
+      <c r="AH11" t="str">
         <v xml:space="preserve">Seconds </v>
-      </c>
-      <c r="AH11" t="str">
-        <v>N/A</v>
       </c>
       <c r="AI11" t="str">
         <v>SW Integrator</v>
       </c>
       <c r="AJ11" t="str">
-        <v>TLS, Config</v>
+        <v>Deploy, Monitoring</v>
       </c>
       <c r="AK11" t="str">
         <v>Public Cloud Consumption</v>
       </c>
       <c r="AL11" t="str">
-        <v>Seeweb VPS</v>
+        <v>Seeweb VPC + W3Suite</v>
       </c>
     </row>
     <row r="12">
@@ -6749,16 +6749,16 @@
         <v>Full IaaS</v>
       </c>
       <c r="H12" t="str">
-        <v>Redis Ltd</v>
+        <v>F5 Networks (Nginx)</v>
       </c>
       <c r="I12" t="str">
         <v>App (RunTime) - Linux native</v>
       </c>
       <c r="J12" t="str">
-        <v>2 VPS dedicate</v>
+        <v>2 VPC</v>
       </c>
       <c r="K12" t="str">
-        <v>Seeweb Multinodo Italy</v>
+        <v>Seeweb Multinodo Italy (DC1)</v>
       </c>
       <c r="L12" t="str">
         <v>Resources - SW configuration</v>
@@ -6788,7 +6788,7 @@
         <v>File (TXT)</v>
       </c>
       <c r="U12" t="str">
-        <v>7.2.x</v>
+        <v>1.24.x</v>
       </c>
       <c r="V12" t="str">
         <v>SW Bins</v>
@@ -6812,13 +6812,13 @@
         <v>1 month</v>
       </c>
       <c r="AC12" t="str">
-        <v>1 min</v>
+        <v>N/A</v>
       </c>
       <c r="AD12" t="str">
-        <v>1 week</v>
+        <v>N/A</v>
       </c>
       <c r="AE12" t="str">
-        <v xml:space="preserve">Local Resilent </v>
+        <v xml:space="preserve">Region Resilent </v>
       </c>
       <c r="AF12" t="str">
         <v>Automated By App</v>
@@ -6827,19 +6827,19 @@
         <v xml:space="preserve">Seconds </v>
       </c>
       <c r="AH12" t="str">
-        <v xml:space="preserve">Seconds </v>
+        <v>N/A</v>
       </c>
       <c r="AI12" t="str">
         <v>SW Integrator</v>
       </c>
       <c r="AJ12" t="str">
-        <v>Memory Monitoring</v>
+        <v>TLS, Config</v>
       </c>
       <c r="AK12" t="str">
         <v>Public Cloud Consumption</v>
       </c>
       <c r="AL12" t="str">
-        <v>Seeweb VPS</v>
+        <v>Seeweb VPC</v>
       </c>
     </row>
     <row r="13">
@@ -6853,7 +6853,7 @@
         <v>HA</v>
       </c>
       <c r="D13" t="str">
-        <v>DATABASE LAYER</v>
+        <v>CORE PLATFORM</v>
       </c>
       <c r="E13" t="str">
         <v>Not W3 Private datacenter</v>
@@ -6865,16 +6865,16 @@
         <v>Full IaaS</v>
       </c>
       <c r="H13" t="str">
-        <v>PostgreSQL Global Development Group</v>
+        <v>Redis Ltd</v>
       </c>
       <c r="I13" t="str">
         <v>App (RunTime) - Linux native</v>
       </c>
       <c r="J13" t="str">
-        <v>2 VPS (Primary+Replica)</v>
+        <v>2 VPC</v>
       </c>
       <c r="K13" t="str">
-        <v>Seeweb Multinodo Italy</v>
+        <v>Seeweb Multinodo Italy (DC1)</v>
       </c>
       <c r="L13" t="str">
         <v>Resources - SW configuration</v>
@@ -6889,7 +6889,7 @@
         <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
       </c>
       <c r="P13" t="str">
-        <v>Minutes (1-10)</v>
+        <v>No outages</v>
       </c>
       <c r="Q13" t="str">
         <v>Ops - Manual</v>
@@ -6898,13 +6898,13 @@
         <v>Ops Manual - direct Log-on resource</v>
       </c>
       <c r="S13" t="str">
-        <v>Minutes (1-10)</v>
+        <v>No outages</v>
       </c>
       <c r="T13" t="str">
         <v>File (TXT)</v>
       </c>
       <c r="U13" t="str">
-        <v>15.x</v>
+        <v>7.2.x</v>
       </c>
       <c r="V13" t="str">
         <v>SW Bins</v>
@@ -6913,7 +6913,7 @@
         <v>Object Store (SW bins)</v>
       </c>
       <c r="X13" t="str">
-        <v>Resource: Release and Recovery</v>
+        <v>Resource Recovery</v>
       </c>
       <c r="Y13" t="str">
         <v>On-Premise SW/Appliance</v>
@@ -6934,13 +6934,13 @@
         <v>1 week</v>
       </c>
       <c r="AE13" t="str">
-        <v xml:space="preserve">Zone Resilent </v>
+        <v xml:space="preserve">Region Resilent </v>
       </c>
       <c r="AF13" t="str">
         <v>Automated By App</v>
       </c>
       <c r="AG13" t="str">
-        <v>Minutes (1-5)</v>
+        <v xml:space="preserve">Seconds </v>
       </c>
       <c r="AH13" t="str">
         <v xml:space="preserve">Seconds </v>
@@ -6949,13 +6949,13 @@
         <v>SW Integrator</v>
       </c>
       <c r="AJ13" t="str">
-        <v>Backup, Tuning, PITR</v>
+        <v>Memory Monitoring</v>
       </c>
       <c r="AK13" t="str">
         <v>Public Cloud Consumption</v>
       </c>
       <c r="AL13" t="str">
-        <v>Seeweb VPS</v>
+        <v>Seeweb VPC</v>
       </c>
     </row>
     <row r="14">
@@ -6981,16 +6981,16 @@
         <v>Full IaaS</v>
       </c>
       <c r="H14" t="str">
-        <v>Seeweb S.r.l. (Ceph Storage)</v>
+        <v>PostgreSQL Global Development Group</v>
       </c>
       <c r="I14" t="str">
-        <v>Bare Metal-Linux OS</v>
+        <v>App (RunTime) - Linux native</v>
       </c>
       <c r="J14" t="str">
-        <v>Cluster Ceph Seeweb</v>
+        <v>2 VPC (Primary+Replica)</v>
       </c>
       <c r="K14" t="str">
-        <v>Seeweb Multinodo Italy</v>
+        <v>Seeweb Multinodo Italy (DC1)</v>
       </c>
       <c r="L14" t="str">
         <v>Resources - SW configuration</v>
@@ -7005,7 +7005,7 @@
         <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
       </c>
       <c r="P14" t="str">
-        <v>No outages</v>
+        <v>Minutes (1-10)</v>
       </c>
       <c r="Q14" t="str">
         <v>Ops - Manual</v>
@@ -7014,13 +7014,13 @@
         <v>Ops Manual - direct Log-on resource</v>
       </c>
       <c r="S14" t="str">
-        <v>No outages</v>
+        <v>Minutes (1-10)</v>
       </c>
       <c r="T14" t="str">
         <v>File (TXT)</v>
       </c>
       <c r="U14" t="str">
-        <v>Quincy</v>
+        <v>15.x</v>
       </c>
       <c r="V14" t="str">
         <v>SW Bins</v>
@@ -7029,7 +7029,7 @@
         <v>Object Store (SW bins)</v>
       </c>
       <c r="X14" t="str">
-        <v>Resource Recovery</v>
+        <v>Resource: Release and Recovery</v>
       </c>
       <c r="Y14" t="str">
         <v>On-Premise SW/Appliance</v>
@@ -7050,28 +7050,28 @@
         <v>1 week</v>
       </c>
       <c r="AE14" t="str">
-        <v xml:space="preserve">Zone Resilent </v>
+        <v xml:space="preserve">Region Resilent </v>
       </c>
       <c r="AF14" t="str">
         <v>Automated By App</v>
       </c>
       <c r="AG14" t="str">
-        <v xml:space="preserve">Seconds </v>
+        <v>Minutes (1-5)</v>
       </c>
       <c r="AH14" t="str">
         <v xml:space="preserve">Seconds </v>
       </c>
       <c r="AI14" t="str">
-        <v>HW/SW vendor</v>
+        <v>SW Integrator</v>
       </c>
       <c r="AJ14" t="str">
-        <v>Capacity, Health</v>
+        <v>Backup, Tuning, PITR</v>
       </c>
       <c r="AK14" t="str">
         <v>Public Cloud Consumption</v>
       </c>
       <c r="AL14" t="str">
-        <v>Seeweb Storage</v>
+        <v>Seeweb VPC</v>
       </c>
     </row>
     <row r="15">
@@ -7079,115 +7079,115 @@
         <v>PROD</v>
       </c>
       <c r="B15" t="str">
-        <v>99,5%</v>
+        <v>99,9%</v>
       </c>
       <c r="C15" t="str">
-        <v>HA-</v>
+        <v>HA</v>
       </c>
       <c r="D15" t="str">
-        <v>AI SERVICES</v>
+        <v>DATABASE LAYER</v>
       </c>
       <c r="E15" t="str">
-        <v>Not W3 Public cloud Tenant</v>
+        <v>Not W3 Private datacenter</v>
       </c>
       <c r="F15" t="str">
         <v>Vendor Private</v>
       </c>
       <c r="G15" t="str">
-        <v>Multi-tenant SaaS</v>
+        <v>Full IaaS</v>
       </c>
       <c r="H15" t="str">
-        <v>OpenAI</v>
+        <v>Seeweb S.r.l. (Ceph Storage)</v>
       </c>
       <c r="I15" t="str">
-        <v>SaaS  App - Generic Platform</v>
+        <v>Bare Metal-Linux OS</v>
       </c>
       <c r="J15" t="str">
-        <v>SaaS</v>
+        <v>Cluster Ceph</v>
       </c>
       <c r="K15" t="str">
-        <v>OpenAI Cloud (EU)</v>
+        <v>Seeweb Multinodo Italy (DC1)</v>
       </c>
       <c r="L15" t="str">
-        <v xml:space="preserve">Internal SaaS/Cloud provider -configuration  </v>
+        <v>Resources - SW configuration</v>
       </c>
       <c r="M15" t="str">
         <v>Active</v>
       </c>
       <c r="N15" t="str">
-        <v>Full Automated</v>
+        <v>Ops Manual</v>
       </c>
       <c r="O15" t="str">
-        <v>Native autoscale (SaaS /Cloud providers)</v>
+        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
       </c>
       <c r="P15" t="str">
         <v>No outages</v>
       </c>
       <c r="Q15" t="str">
-        <v>Fully Automated</v>
+        <v>Ops - Manual</v>
       </c>
       <c r="R15" t="str">
-        <v>Automated By SaaS/Cloud Provider</v>
+        <v>Ops Manual - direct Log-on resource</v>
       </c>
       <c r="S15" t="str">
         <v>No outages</v>
       </c>
       <c r="T15" t="str">
-        <v>Database (metadata) - section of application data App configuration</v>
+        <v>File (TXT)</v>
       </c>
       <c r="U15" t="str">
-        <v>API v1</v>
+        <v>Quincy</v>
       </c>
       <c r="V15" t="str">
-        <v>N/A</v>
+        <v>SW Bins</v>
       </c>
       <c r="W15" t="str">
-        <v>N/A</v>
+        <v>Object Store (SW bins)</v>
       </c>
       <c r="X15" t="str">
-        <v>N/A</v>
+        <v>Resource Recovery</v>
       </c>
       <c r="Y15" t="str">
-        <v>N/A</v>
+        <v>On-Premise SW/Appliance</v>
       </c>
       <c r="Z15" t="str">
-        <v>N/A</v>
+        <v>On-premise Store (Appliance)</v>
       </c>
       <c r="AA15" t="str">
-        <v>N/A</v>
+        <v>Daily</v>
       </c>
       <c r="AB15" t="str">
-        <v>N/A</v>
+        <v>1 month</v>
       </c>
       <c r="AC15" t="str">
-        <v>N/A</v>
+        <v>1 min</v>
       </c>
       <c r="AD15" t="str">
-        <v>N/A</v>
+        <v>1 week</v>
       </c>
       <c r="AE15" t="str">
-        <v xml:space="preserve">Region Resilent </v>
+        <v xml:space="preserve">Zone Resilent </v>
       </c>
       <c r="AF15" t="str">
-        <v>Automated by Cloud/SaaS Provider</v>
+        <v>Automated By App</v>
       </c>
       <c r="AG15" t="str">
         <v xml:space="preserve">Seconds </v>
       </c>
       <c r="AH15" t="str">
-        <v>N/A</v>
+        <v xml:space="preserve">Seconds </v>
       </c>
       <c r="AI15" t="str">
-        <v>SaaS Provider</v>
+        <v>HW/SW vendor</v>
       </c>
       <c r="AJ15" t="str">
-        <v>API Monitoring</v>
+        <v>Capacity, Health</v>
       </c>
       <c r="AK15" t="str">
-        <v>Subscription</v>
+        <v>Public Cloud Consumption</v>
       </c>
       <c r="AL15" t="str">
-        <v>OpenAI Pay-as-you-go</v>
+        <v>Seeweb Storage</v>
       </c>
     </row>
     <row r="16">
@@ -7195,85 +7195,85 @@
         <v>PROD</v>
       </c>
       <c r="B16" t="str">
-        <v>99,9%</v>
+        <v>99,5%</v>
       </c>
       <c r="C16" t="str">
-        <v>HA</v>
+        <v>HA-</v>
       </c>
       <c r="D16" t="str">
         <v>AI SERVICES</v>
       </c>
       <c r="E16" t="str">
-        <v>Not W3 Private datacenter</v>
+        <v>Not W3 Public cloud Tenant</v>
       </c>
       <c r="F16" t="str">
         <v>Vendor Private</v>
       </c>
       <c r="G16" t="str">
-        <v>Full IaaS</v>
+        <v>Multi-tenant SaaS</v>
       </c>
       <c r="H16" t="str">
-        <v>W3Suite (Easy Digital Group)</v>
+        <v>OpenAI</v>
       </c>
       <c r="I16" t="str">
-        <v>App (RunTime) - Linux native</v>
+        <v>SaaS  App - Generic Platform</v>
       </c>
       <c r="J16" t="str">
-        <v>2 VPS dedicate</v>
+        <v>SaaS</v>
       </c>
       <c r="K16" t="str">
-        <v>Seeweb Multinodo Italy</v>
+        <v>OpenAI Cloud (EU)</v>
       </c>
       <c r="L16" t="str">
-        <v>Resources - SW configuration</v>
+        <v xml:space="preserve">Internal SaaS/Cloud provider -configuration  </v>
       </c>
       <c r="M16" t="str">
         <v>Active</v>
       </c>
       <c r="N16" t="str">
-        <v>Ops Manual</v>
+        <v>Full Automated</v>
       </c>
       <c r="O16" t="str">
-        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
+        <v>Native autoscale (SaaS /Cloud providers)</v>
       </c>
       <c r="P16" t="str">
         <v>No outages</v>
       </c>
       <c r="Q16" t="str">
-        <v>Ops - Automated</v>
+        <v>Fully Automated</v>
       </c>
       <c r="R16" t="str">
-        <v>Ops Manual - direct Log-on resource</v>
+        <v>Automated By SaaS/Cloud Provider</v>
       </c>
       <c r="S16" t="str">
         <v>No outages</v>
       </c>
       <c r="T16" t="str">
-        <v>File (Ansible playbook) - VM configuration</v>
+        <v>Database (metadata) - section of application data App configuration</v>
       </c>
       <c r="U16" t="str">
-        <v>SemVer</v>
+        <v>API v1</v>
       </c>
       <c r="V16" t="str">
-        <v>SW Bins</v>
+        <v>N/A</v>
       </c>
       <c r="W16" t="str">
-        <v>Object Store (SW bins)</v>
+        <v>N/A</v>
       </c>
       <c r="X16" t="str">
-        <v>Resource Recovery</v>
+        <v>N/A</v>
       </c>
       <c r="Y16" t="str">
-        <v>On-Premise SW/Appliance</v>
+        <v>N/A</v>
       </c>
       <c r="Z16" t="str">
-        <v>On-premise Store (Appliance)</v>
+        <v>N/A</v>
       </c>
       <c r="AA16" t="str">
-        <v>Daily</v>
+        <v>N/A</v>
       </c>
       <c r="AB16" t="str">
-        <v>1 month</v>
+        <v>N/A</v>
       </c>
       <c r="AC16" t="str">
         <v>N/A</v>
@@ -7282,28 +7282,28 @@
         <v>N/A</v>
       </c>
       <c r="AE16" t="str">
-        <v xml:space="preserve">Local Resilent </v>
+        <v xml:space="preserve">Region Resilent </v>
       </c>
       <c r="AF16" t="str">
-        <v>Automated By App</v>
+        <v>Automated by Cloud/SaaS Provider</v>
       </c>
       <c r="AG16" t="str">
         <v xml:space="preserve">Seconds </v>
       </c>
       <c r="AH16" t="str">
-        <v xml:space="preserve">Seconds </v>
+        <v>N/A</v>
       </c>
       <c r="AI16" t="str">
-        <v>SW Integrator</v>
+        <v>SaaS Provider</v>
       </c>
       <c r="AJ16" t="str">
-        <v>AI Routing</v>
+        <v>API Monitoring</v>
       </c>
       <c r="AK16" t="str">
-        <v>Public Cloud Consumption</v>
+        <v>Subscription</v>
       </c>
       <c r="AL16" t="str">
-        <v>Seeweb VPS + W3Suite</v>
+        <v>OpenAI Pay-as-you-go</v>
       </c>
     </row>
     <row r="17">
@@ -7317,7 +7317,7 @@
         <v>HA</v>
       </c>
       <c r="D17" t="str">
-        <v>SECURITY</v>
+        <v>AI SERVICES</v>
       </c>
       <c r="E17" t="str">
         <v>Not W3 Private datacenter</v>
@@ -7335,10 +7335,10 @@
         <v>App (RunTime) - Linux native</v>
       </c>
       <c r="J17" t="str">
-        <v>3 VPS dedicate</v>
+        <v>2 VPC</v>
       </c>
       <c r="K17" t="str">
-        <v>Seeweb Multinodo Italy</v>
+        <v>Seeweb Multinodo Italy (DC1)</v>
       </c>
       <c r="L17" t="str">
         <v>Resources - SW configuration</v>
@@ -7365,7 +7365,7 @@
         <v>No outages</v>
       </c>
       <c r="T17" t="str">
-        <v>Database (metadata) - section of application data App configuration</v>
+        <v>File (Ansible playbook) - VM configuration</v>
       </c>
       <c r="U17" t="str">
         <v>SemVer</v>
@@ -7377,7 +7377,7 @@
         <v>Object Store (SW bins)</v>
       </c>
       <c r="X17" t="str">
-        <v>Resource: Release and Recovery</v>
+        <v>Resource Recovery</v>
       </c>
       <c r="Y17" t="str">
         <v>On-Premise SW/Appliance</v>
@@ -7392,19 +7392,19 @@
         <v>1 month</v>
       </c>
       <c r="AC17" t="str">
-        <v>1 min</v>
+        <v>N/A</v>
       </c>
       <c r="AD17" t="str">
-        <v>1 week</v>
+        <v>N/A</v>
       </c>
       <c r="AE17" t="str">
-        <v xml:space="preserve">Zone Resilent </v>
+        <v xml:space="preserve">Region Resilent </v>
       </c>
       <c r="AF17" t="str">
         <v>Automated By App</v>
       </c>
       <c r="AG17" t="str">
-        <v>Minutes (1-5)</v>
+        <v xml:space="preserve">Seconds </v>
       </c>
       <c r="AH17" t="str">
         <v xml:space="preserve">Seconds </v>
@@ -7413,13 +7413,13 @@
         <v>SW Integrator</v>
       </c>
       <c r="AJ17" t="str">
-        <v>Key Rotation, Audit</v>
+        <v>AI Routing</v>
       </c>
       <c r="AK17" t="str">
         <v>Public Cloud Consumption</v>
       </c>
       <c r="AL17" t="str">
-        <v>Seeweb VPS + W3Suite</v>
+        <v>Seeweb VPC + W3Suite</v>
       </c>
     </row>
     <row r="18">
@@ -7427,13 +7427,13 @@
         <v>PROD</v>
       </c>
       <c r="B18" t="str">
-        <v>99,5%</v>
+        <v>99,9%</v>
       </c>
       <c r="C18" t="str">
-        <v>HA-</v>
+        <v>HA</v>
       </c>
       <c r="D18" t="str">
-        <v>OBSERVABILITY</v>
+        <v>SECURITY</v>
       </c>
       <c r="E18" t="str">
         <v>Not W3 Private datacenter</v>
@@ -7445,16 +7445,16 @@
         <v>Full IaaS</v>
       </c>
       <c r="H18" t="str">
-        <v>Grafana Labs</v>
+        <v>W3Suite (Easy Digital Group)</v>
       </c>
       <c r="I18" t="str">
         <v>App (RunTime) - Linux native</v>
       </c>
       <c r="J18" t="str">
-        <v>2 VPS dedicate</v>
+        <v>3 VPC</v>
       </c>
       <c r="K18" t="str">
-        <v>Seeweb Multinodo Italy</v>
+        <v>Seeweb Multinodo Italy (DC1)</v>
       </c>
       <c r="L18" t="str">
         <v>Resources - SW configuration</v>
@@ -7472,7 +7472,7 @@
         <v>No outages</v>
       </c>
       <c r="Q18" t="str">
-        <v>Ops - Manual</v>
+        <v>Ops - Automated</v>
       </c>
       <c r="R18" t="str">
         <v>Ops Manual - direct Log-on resource</v>
@@ -7481,10 +7481,10 @@
         <v>No outages</v>
       </c>
       <c r="T18" t="str">
-        <v>File (TXT)</v>
+        <v>Database (metadata) - section of application data App configuration</v>
       </c>
       <c r="U18" t="str">
-        <v>10.x</v>
+        <v>SemVer</v>
       </c>
       <c r="V18" t="str">
         <v>SW Bins</v>
@@ -7493,7 +7493,7 @@
         <v>Object Store (SW bins)</v>
       </c>
       <c r="X18" t="str">
-        <v>Resource Recovery</v>
+        <v>Resource: Release and Recovery</v>
       </c>
       <c r="Y18" t="str">
         <v>On-Premise SW/Appliance</v>
@@ -7508,39 +7508,155 @@
         <v>1 month</v>
       </c>
       <c r="AC18" t="str">
-        <v>N/A</v>
+        <v>1 min</v>
       </c>
       <c r="AD18" t="str">
-        <v>N/A</v>
+        <v>1 week</v>
       </c>
       <c r="AE18" t="str">
-        <v xml:space="preserve">Local Resilent </v>
+        <v xml:space="preserve">Region Resilent </v>
       </c>
       <c r="AF18" t="str">
-        <v>Manual By Operation</v>
+        <v>Automated By App</v>
       </c>
       <c r="AG18" t="str">
-        <v>Hour (1-5)</v>
+        <v>Minutes (1-5)</v>
       </c>
       <c r="AH18" t="str">
-        <v>Hour (1-5)</v>
+        <v xml:space="preserve">Seconds </v>
       </c>
       <c r="AI18" t="str">
         <v>SW Integrator</v>
       </c>
       <c r="AJ18" t="str">
-        <v>Dashboards, Alerts</v>
+        <v>Key Rotation, Audit</v>
       </c>
       <c r="AK18" t="str">
         <v>Public Cloud Consumption</v>
       </c>
       <c r="AL18" t="str">
-        <v>Seeweb VPS</v>
+        <v>Seeweb VPC + W3Suite</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>PROD</v>
+      </c>
+      <c r="B19" t="str">
+        <v>99,5%</v>
+      </c>
+      <c r="C19" t="str">
+        <v>HA-</v>
+      </c>
+      <c r="D19" t="str">
+        <v>OBSERVABILITY</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Not W3 Private datacenter</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Vendor Private</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Full IaaS</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Grafana Labs</v>
+      </c>
+      <c r="I19" t="str">
+        <v>App (RunTime) - Linux native</v>
+      </c>
+      <c r="J19" t="str">
+        <v>2 VPC</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Seeweb Multinodo Italy (DC1)</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Resources - SW configuration</v>
+      </c>
+      <c r="M19" t="str">
+        <v>Active</v>
+      </c>
+      <c r="N19" t="str">
+        <v>Ops Manual</v>
+      </c>
+      <c r="O19" t="str">
+        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
+      </c>
+      <c r="P19" t="str">
+        <v>No outages</v>
+      </c>
+      <c r="Q19" t="str">
+        <v>Ops - Manual</v>
+      </c>
+      <c r="R19" t="str">
+        <v>Ops Manual - direct Log-on resource</v>
+      </c>
+      <c r="S19" t="str">
+        <v>No outages</v>
+      </c>
+      <c r="T19" t="str">
+        <v>File (TXT)</v>
+      </c>
+      <c r="U19" t="str">
+        <v>10.x</v>
+      </c>
+      <c r="V19" t="str">
+        <v>SW Bins</v>
+      </c>
+      <c r="W19" t="str">
+        <v>Object Store (SW bins)</v>
+      </c>
+      <c r="X19" t="str">
+        <v>Resource Recovery</v>
+      </c>
+      <c r="Y19" t="str">
+        <v>On-Premise SW/Appliance</v>
+      </c>
+      <c r="Z19" t="str">
+        <v>On-premise Store (Appliance)</v>
+      </c>
+      <c r="AA19" t="str">
+        <v>Daily</v>
+      </c>
+      <c r="AB19" t="str">
+        <v>1 month</v>
+      </c>
+      <c r="AC19" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD19" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE19" t="str">
+        <v xml:space="preserve">Region Resilent </v>
+      </c>
+      <c r="AF19" t="str">
+        <v>Manual By Operation</v>
+      </c>
+      <c r="AG19" t="str">
+        <v>Hour (1-5)</v>
+      </c>
+      <c r="AH19" t="str">
+        <v>Hour (1-5)</v>
+      </c>
+      <c r="AI19" t="str">
+        <v>SW Integrator</v>
+      </c>
+      <c r="AJ19" t="str">
+        <v>Dashboards, Alerts</v>
+      </c>
+      <c r="AK19" t="str">
+        <v>Public Cloud Consumption</v>
+      </c>
+      <c r="AL19" t="str">
+        <v>Seeweb VPC</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A4:AL18"/>
+    <ignoredError numberStoredAsText="1" sqref="A4:AL19"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/gara-appalto/SERVICE-RESOURCE-MODEL-W3SUITE-FINAL.xlsx
+++ b/docs/gara-appalto/SERVICE-RESOURCE-MODEL-W3SUITE-FINAL.xlsx
@@ -5896,6 +5896,12 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="B256:D256"/>
+    <mergeCell ref="B391:D391"/>
+    <mergeCell ref="B378:D378"/>
+    <mergeCell ref="B368:D368"/>
+    <mergeCell ref="B346:D346"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B208:D208"/>
@@ -5908,12 +5914,6 @@
     <mergeCell ref="B98:B101"/>
     <mergeCell ref="C98:C101"/>
     <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="B256:D256"/>
-    <mergeCell ref="B391:D391"/>
-    <mergeCell ref="B378:D378"/>
-    <mergeCell ref="B368:D368"/>
-    <mergeCell ref="B346:D346"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -5924,46 +5924,46 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A4:AL19"/>
+  <dimension ref="A4:AL14"/>
   <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" customWidth="1"/>
-    <col min="7" max="7" width="26.83203125" customWidth="1"/>
-    <col min="8" max="8" width="26.83203125" customWidth="1"/>
-    <col min="9" max="9" width="26.83203125" customWidth="1"/>
-    <col min="10" max="10" width="26.83203125" customWidth="1"/>
-    <col min="11" max="11" width="26.83203125" customWidth="1"/>
-    <col min="12" max="12" width="26.83203125" customWidth="1"/>
-    <col min="13" max="13" width="26.83203125" customWidth="1"/>
-    <col min="14" max="14" width="26.83203125" customWidth="1"/>
-    <col min="15" max="15" width="26.83203125" customWidth="1"/>
-    <col min="16" max="16" width="26.83203125" customWidth="1"/>
-    <col min="17" max="17" width="26.83203125" customWidth="1"/>
-    <col min="18" max="18" width="26.83203125" customWidth="1"/>
-    <col min="19" max="19" width="26.83203125" customWidth="1"/>
-    <col min="20" max="20" width="26.83203125" customWidth="1"/>
-    <col min="21" max="21" width="26.83203125" customWidth="1"/>
-    <col min="22" max="22" width="26.83203125" customWidth="1"/>
-    <col min="23" max="23" width="26.83203125" customWidth="1"/>
-    <col min="24" max="24" width="26.83203125" customWidth="1"/>
-    <col min="25" max="25" width="26.83203125" customWidth="1"/>
-    <col min="26" max="26" width="26.83203125" customWidth="1"/>
-    <col min="27" max="27" width="26.83203125" customWidth="1"/>
-    <col min="28" max="28" width="26.83203125" customWidth="1"/>
-    <col min="29" max="29" width="26.83203125" customWidth="1"/>
-    <col min="30" max="30" width="26.83203125" customWidth="1"/>
-    <col min="31" max="31" width="26.83203125" customWidth="1"/>
-    <col min="32" max="32" width="26.83203125" customWidth="1"/>
-    <col min="33" max="33" width="26.83203125" customWidth="1"/>
-    <col min="34" max="34" width="26.83203125" customWidth="1"/>
-    <col min="35" max="35" width="26.83203125" customWidth="1"/>
-    <col min="36" max="36" width="26.83203125" customWidth="1"/>
-    <col min="37" max="37" width="26.83203125" customWidth="1"/>
-    <col min="38" max="38" width="26.83203125" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="2" max="2" width="28.83203125" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" customWidth="1"/>
+    <col min="4" max="4" width="28.83203125" customWidth="1"/>
+    <col min="5" max="5" width="28.83203125" customWidth="1"/>
+    <col min="6" max="6" width="28.83203125" customWidth="1"/>
+    <col min="7" max="7" width="28.83203125" customWidth="1"/>
+    <col min="8" max="8" width="28.83203125" customWidth="1"/>
+    <col min="9" max="9" width="28.83203125" customWidth="1"/>
+    <col min="10" max="10" width="28.83203125" customWidth="1"/>
+    <col min="11" max="11" width="28.83203125" customWidth="1"/>
+    <col min="12" max="12" width="28.83203125" customWidth="1"/>
+    <col min="13" max="13" width="28.83203125" customWidth="1"/>
+    <col min="14" max="14" width="28.83203125" customWidth="1"/>
+    <col min="15" max="15" width="28.83203125" customWidth="1"/>
+    <col min="16" max="16" width="28.83203125" customWidth="1"/>
+    <col min="17" max="17" width="28.83203125" customWidth="1"/>
+    <col min="18" max="18" width="28.83203125" customWidth="1"/>
+    <col min="19" max="19" width="28.83203125" customWidth="1"/>
+    <col min="20" max="20" width="28.83203125" customWidth="1"/>
+    <col min="21" max="21" width="28.83203125" customWidth="1"/>
+    <col min="22" max="22" width="28.83203125" customWidth="1"/>
+    <col min="23" max="23" width="28.83203125" customWidth="1"/>
+    <col min="24" max="24" width="28.83203125" customWidth="1"/>
+    <col min="25" max="25" width="28.83203125" customWidth="1"/>
+    <col min="26" max="26" width="28.83203125" customWidth="1"/>
+    <col min="27" max="27" width="28.83203125" customWidth="1"/>
+    <col min="28" max="28" width="28.83203125" customWidth="1"/>
+    <col min="29" max="29" width="28.83203125" customWidth="1"/>
+    <col min="30" max="30" width="28.83203125" customWidth="1"/>
+    <col min="31" max="31" width="28.83203125" customWidth="1"/>
+    <col min="32" max="32" width="28.83203125" customWidth="1"/>
+    <col min="33" max="33" width="28.83203125" customWidth="1"/>
+    <col min="34" max="34" width="28.83203125" customWidth="1"/>
+    <col min="35" max="35" width="28.83203125" customWidth="1"/>
+    <col min="36" max="36" width="28.83203125" customWidth="1"/>
+    <col min="37" max="37" width="28.83203125" customWidth="1"/>
+    <col min="38" max="38" width="28.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4">
@@ -6273,7 +6273,7 @@
         <v>HA</v>
       </c>
       <c r="D8" t="str">
-        <v>CORE PLATFORM</v>
+        <v>INFRASTRUCTURE</v>
       </c>
       <c r="E8" t="str">
         <v>Not W3 Private datacenter</v>
@@ -6285,16 +6285,16 @@
         <v>Full IaaS</v>
       </c>
       <c r="H8" t="str">
-        <v>Seeweb S.r.l. + Proxmox VE</v>
+        <v>Seeweb S.r.l.</v>
       </c>
       <c r="I8" t="str">
         <v>Virtualization Platform - ProxMox</v>
       </c>
       <c r="J8" t="str">
-        <v>Multinodo Cluster</v>
+        <v>1 Cluster Multinodo</v>
       </c>
       <c r="K8" t="str">
-        <v>Seeweb Multinodo Italy (DC1)</v>
+        <v>Seeweb Italy (DC1)</v>
       </c>
       <c r="L8" t="str">
         <v>Resources - SW configuration</v>
@@ -6324,7 +6324,7 @@
         <v>File (TXT)</v>
       </c>
       <c r="U8" t="str">
-        <v>8.1.x</v>
+        <v>Proxmox VE 8.x</v>
       </c>
       <c r="V8" t="str">
         <v>VMI (virtual Machine Image) - KVM</v>
@@ -6369,13 +6369,13 @@
         <v>HW/SW vendor</v>
       </c>
       <c r="AJ8" t="str">
-        <v>VM Mgmt, PBS Replication</v>
+        <v>Cluster Management</v>
       </c>
       <c r="AK8" t="str">
         <v>Public Cloud Consumption</v>
       </c>
       <c r="AL8" t="str">
-        <v>Seeweb Multinodo + PBS</v>
+        <v>Seeweb Multinodo Contract</v>
       </c>
     </row>
     <row r="9">
@@ -6383,13 +6383,13 @@
         <v>PROD</v>
       </c>
       <c r="B9" t="str">
-        <v>99,9%</v>
+        <v>99,5%</v>
       </c>
       <c r="C9" t="str">
-        <v>HA</v>
+        <v>HA-</v>
       </c>
       <c r="D9" t="str">
-        <v>CORE PLATFORM</v>
+        <v>INFRASTRUCTURE</v>
       </c>
       <c r="E9" t="str">
         <v>Not W3 Private datacenter</v>
@@ -6398,19 +6398,19 @@
         <v>Vendor Private</v>
       </c>
       <c r="G9" t="str">
-        <v>Full IaaS</v>
+        <v>HW Appliance</v>
       </c>
       <c r="H9" t="str">
-        <v>Proxmox Server Solutions GmbH</v>
+        <v>Seeweb S.r.l. (Fortinet)</v>
       </c>
       <c r="I9" t="str">
-        <v>Bare Metal-Linux OS</v>
+        <v>HW Appliance - FortiGate NGFW</v>
       </c>
       <c r="J9" t="str">
-        <v>1 (Dedicato)</v>
+        <v>1 (Single)</v>
       </c>
       <c r="K9" t="str">
-        <v>Seeweb Italy (DC2 - DR Site)</v>
+        <v>Seeweb Italy (DC1)</v>
       </c>
       <c r="L9" t="str">
         <v>Resources - SW configuration</v>
@@ -6419,10 +6419,10 @@
         <v>Active</v>
       </c>
       <c r="N9" t="str">
-        <v>Ops Manual</v>
+        <v>Fixed capacity</v>
       </c>
       <c r="O9" t="str">
-        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
+        <v>Do not scale - Fixed capacity</v>
       </c>
       <c r="P9" t="str">
         <v>No outages</v>
@@ -6440,13 +6440,13 @@
         <v>File (TXT)</v>
       </c>
       <c r="U9" t="str">
-        <v>3.x</v>
+        <v>FortiOS 7.x</v>
       </c>
       <c r="V9" t="str">
         <v>SW Bins</v>
       </c>
       <c r="W9" t="str">
-        <v>Object Store (SW bins)</v>
+        <v>Private Others Registry</v>
       </c>
       <c r="X9" t="str">
         <v>Resource Recovery</v>
@@ -6464,13 +6464,13 @@
         <v>1 month</v>
       </c>
       <c r="AC9" t="str">
-        <v>1 min</v>
+        <v>N/A</v>
       </c>
       <c r="AD9" t="str">
-        <v>1 week</v>
+        <v>N/A</v>
       </c>
       <c r="AE9" t="str">
-        <v xml:space="preserve">Region Resilent </v>
+        <v xml:space="preserve">Local Resilent </v>
       </c>
       <c r="AF9" t="str">
         <v>Manual By Operation</v>
@@ -6479,19 +6479,19 @@
         <v>Hour (1-5)</v>
       </c>
       <c r="AH9" t="str">
-        <v>Minutes (1-5)</v>
+        <v>Hour (1-5)</v>
       </c>
       <c r="AI9" t="str">
         <v>HW/SW vendor</v>
       </c>
       <c r="AJ9" t="str">
-        <v>Backup Storage, DR</v>
+        <v>Security Management</v>
       </c>
       <c r="AK9" t="str">
-        <v>Public Cloud Consumption</v>
+        <v>COTs SW License</v>
       </c>
       <c r="AL9" t="str">
-        <v>Seeweb PBS Dedicated</v>
+        <v>Seeweb FortiGate Service</v>
       </c>
     </row>
     <row r="10">
@@ -6499,13 +6499,13 @@
         <v>PROD</v>
       </c>
       <c r="B10" t="str">
-        <v>99,5%</v>
+        <v>99,9%</v>
       </c>
       <c r="C10" t="str">
-        <v>HA-</v>
+        <v>HA</v>
       </c>
       <c r="D10" t="str">
-        <v>CORE PLATFORM</v>
+        <v>INFRASTRUCTURE</v>
       </c>
       <c r="E10" t="str">
         <v>Not W3 Private datacenter</v>
@@ -6514,19 +6514,19 @@
         <v>Vendor Private</v>
       </c>
       <c r="G10" t="str">
-        <v>HW Appliance</v>
+        <v>Bare Metal</v>
       </c>
       <c r="H10" t="str">
-        <v>Fortinet Inc.</v>
+        <v>Seeweb S.r.l.</v>
       </c>
       <c r="I10" t="str">
-        <v>HW Appliance - FortiGate NGFW</v>
+        <v>Bare Metal-Linux OS</v>
       </c>
       <c r="J10" t="str">
-        <v>1 (Single)</v>
+        <v>1 (Dedicato)</v>
       </c>
       <c r="K10" t="str">
-        <v>Seeweb Multinodo Italy (DC1)</v>
+        <v>Seeweb Italy (DC2 - DR)</v>
       </c>
       <c r="L10" t="str">
         <v>Resources - SW configuration</v>
@@ -6535,10 +6535,10 @@
         <v>Active</v>
       </c>
       <c r="N10" t="str">
-        <v>Fixed capacity</v>
+        <v>Ops Manual</v>
       </c>
       <c r="O10" t="str">
-        <v>Do not scale - Fixed capacity</v>
+        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
       </c>
       <c r="P10" t="str">
         <v>No outages</v>
@@ -6556,13 +6556,13 @@
         <v>File (TXT)</v>
       </c>
       <c r="U10" t="str">
-        <v>7.4.x</v>
+        <v>PBS 3.x</v>
       </c>
       <c r="V10" t="str">
         <v>SW Bins</v>
       </c>
       <c r="W10" t="str">
-        <v>Private Others Registry</v>
+        <v>Object Store (SW bins)</v>
       </c>
       <c r="X10" t="str">
         <v>Resource Recovery</v>
@@ -6580,13 +6580,13 @@
         <v>1 month</v>
       </c>
       <c r="AC10" t="str">
-        <v>N/A</v>
+        <v>1 min</v>
       </c>
       <c r="AD10" t="str">
-        <v>N/A</v>
+        <v>1 week</v>
       </c>
       <c r="AE10" t="str">
-        <v xml:space="preserve">Local Resilent </v>
+        <v xml:space="preserve">Region Resilent </v>
       </c>
       <c r="AF10" t="str">
         <v>Manual By Operation</v>
@@ -6595,19 +6595,19 @@
         <v>Hour (1-5)</v>
       </c>
       <c r="AH10" t="str">
-        <v>Hour (1-5)</v>
+        <v>Minutes (1-5)</v>
       </c>
       <c r="AI10" t="str">
         <v>HW/SW vendor</v>
       </c>
       <c r="AJ10" t="str">
-        <v>Security, Monitoring</v>
+        <v>Backup &amp; DR</v>
       </c>
       <c r="AK10" t="str">
-        <v>COTs SW License</v>
+        <v>Public Cloud Consumption</v>
       </c>
       <c r="AL10" t="str">
-        <v>FortiCare + FortiGuard</v>
+        <v>Seeweb PBS Service</v>
       </c>
     </row>
     <row r="11">
@@ -6621,7 +6621,7 @@
         <v>HA</v>
       </c>
       <c r="D11" t="str">
-        <v>CORE PLATFORM</v>
+        <v>APPLICATION</v>
       </c>
       <c r="E11" t="str">
         <v>Not W3 Private datacenter</v>
@@ -6633,16 +6633,16 @@
         <v>Full IaaS</v>
       </c>
       <c r="H11" t="str">
-        <v>W3Suite (Easy Digital Group)</v>
+        <v>Seeweb S.r.l.</v>
       </c>
       <c r="I11" t="str">
         <v>App (RunTime) - Linux native</v>
       </c>
       <c r="J11" t="str">
-        <v>3 VPC</v>
+        <v>1 VPC (Nginx + LB)</v>
       </c>
       <c r="K11" t="str">
-        <v>Seeweb Multinodo Italy (DC1)</v>
+        <v>Seeweb Italy (DC1)</v>
       </c>
       <c r="L11" t="str">
         <v>Resources - SW configuration</v>
@@ -6672,7 +6672,7 @@
         <v>File (Ansible playbook) - VM configuration</v>
       </c>
       <c r="U11" t="str">
-        <v>SemVer</v>
+        <v>Nginx 1.24 + W3Suite FE</v>
       </c>
       <c r="V11" t="str">
         <v>SW Bins</v>
@@ -6708,22 +6708,22 @@
         <v>Automated By App</v>
       </c>
       <c r="AG11" t="str">
-        <v>Minutes (1-5)</v>
+        <v xml:space="preserve">Seconds </v>
       </c>
       <c r="AH11" t="str">
-        <v xml:space="preserve">Seconds </v>
+        <v>N/A</v>
       </c>
       <c r="AI11" t="str">
         <v>SW Integrator</v>
       </c>
       <c r="AJ11" t="str">
-        <v>Deploy, Monitoring</v>
+        <v>TLS, Routing, LB Config</v>
       </c>
       <c r="AK11" t="str">
         <v>Public Cloud Consumption</v>
       </c>
       <c r="AL11" t="str">
-        <v>Seeweb VPC + W3Suite</v>
+        <v>Seeweb VPC</v>
       </c>
     </row>
     <row r="12">
@@ -6737,7 +6737,7 @@
         <v>HA</v>
       </c>
       <c r="D12" t="str">
-        <v>CORE PLATFORM</v>
+        <v>APPLICATION</v>
       </c>
       <c r="E12" t="str">
         <v>Not W3 Private datacenter</v>
@@ -6749,16 +6749,16 @@
         <v>Full IaaS</v>
       </c>
       <c r="H12" t="str">
-        <v>F5 Networks (Nginx)</v>
+        <v>Seeweb S.r.l.</v>
       </c>
       <c r="I12" t="str">
         <v>App (RunTime) - Linux native</v>
       </c>
       <c r="J12" t="str">
-        <v>2 VPC</v>
+        <v>1 VPC (API+Redis+MCP)</v>
       </c>
       <c r="K12" t="str">
-        <v>Seeweb Multinodo Italy (DC1)</v>
+        <v>Seeweb Italy (DC1)</v>
       </c>
       <c r="L12" t="str">
         <v>Resources - SW configuration</v>
@@ -6776,7 +6776,7 @@
         <v>No outages</v>
       </c>
       <c r="Q12" t="str">
-        <v>Ops - Manual</v>
+        <v>Ops - Automated</v>
       </c>
       <c r="R12" t="str">
         <v>Ops Manual - direct Log-on resource</v>
@@ -6785,10 +6785,10 @@
         <v>No outages</v>
       </c>
       <c r="T12" t="str">
-        <v>File (TXT)</v>
+        <v>File (Ansible playbook) - VM configuration</v>
       </c>
       <c r="U12" t="str">
-        <v>1.24.x</v>
+        <v>W3Suite API + Redis + MCP</v>
       </c>
       <c r="V12" t="str">
         <v>SW Bins</v>
@@ -6812,10 +6812,10 @@
         <v>1 month</v>
       </c>
       <c r="AC12" t="str">
-        <v>N/A</v>
+        <v>1 min</v>
       </c>
       <c r="AD12" t="str">
-        <v>N/A</v>
+        <v>1 week</v>
       </c>
       <c r="AE12" t="str">
         <v xml:space="preserve">Region Resilent </v>
@@ -6824,16 +6824,16 @@
         <v>Automated By App</v>
       </c>
       <c r="AG12" t="str">
+        <v>Minutes (1-5)</v>
+      </c>
+      <c r="AH12" t="str">
         <v xml:space="preserve">Seconds </v>
-      </c>
-      <c r="AH12" t="str">
-        <v>N/A</v>
       </c>
       <c r="AI12" t="str">
         <v>SW Integrator</v>
       </c>
       <c r="AJ12" t="str">
-        <v>TLS, Config</v>
+        <v>Deploy, API, AI Gateway</v>
       </c>
       <c r="AK12" t="str">
         <v>Public Cloud Consumption</v>
@@ -6853,7 +6853,7 @@
         <v>HA</v>
       </c>
       <c r="D13" t="str">
-        <v>CORE PLATFORM</v>
+        <v>DATABASE</v>
       </c>
       <c r="E13" t="str">
         <v>Not W3 Private datacenter</v>
@@ -6865,16 +6865,16 @@
         <v>Full IaaS</v>
       </c>
       <c r="H13" t="str">
-        <v>Redis Ltd</v>
+        <v>Seeweb S.r.l.</v>
       </c>
       <c r="I13" t="str">
         <v>App (RunTime) - Linux native</v>
       </c>
       <c r="J13" t="str">
-        <v>2 VPC</v>
+        <v>1 VPC (PostgreSQL Primary)</v>
       </c>
       <c r="K13" t="str">
-        <v>Seeweb Multinodo Italy (DC1)</v>
+        <v>Seeweb Italy (DC1)</v>
       </c>
       <c r="L13" t="str">
         <v>Resources - SW configuration</v>
@@ -6889,7 +6889,7 @@
         <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
       </c>
       <c r="P13" t="str">
-        <v>No outages</v>
+        <v>Minutes (1-10)</v>
       </c>
       <c r="Q13" t="str">
         <v>Ops - Manual</v>
@@ -6898,13 +6898,13 @@
         <v>Ops Manual - direct Log-on resource</v>
       </c>
       <c r="S13" t="str">
-        <v>No outages</v>
+        <v>Minutes (1-10)</v>
       </c>
       <c r="T13" t="str">
         <v>File (TXT)</v>
       </c>
       <c r="U13" t="str">
-        <v>7.2.x</v>
+        <v>PostgreSQL 15.x</v>
       </c>
       <c r="V13" t="str">
         <v>SW Bins</v>
@@ -6913,7 +6913,7 @@
         <v>Object Store (SW bins)</v>
       </c>
       <c r="X13" t="str">
-        <v>Resource Recovery</v>
+        <v>Resource: Release and Recovery</v>
       </c>
       <c r="Y13" t="str">
         <v>On-Premise SW/Appliance</v>
@@ -6940,7 +6940,7 @@
         <v>Automated By App</v>
       </c>
       <c r="AG13" t="str">
-        <v xml:space="preserve">Seconds </v>
+        <v>Minutes (1-5)</v>
       </c>
       <c r="AH13" t="str">
         <v xml:space="preserve">Seconds </v>
@@ -6949,7 +6949,7 @@
         <v>SW Integrator</v>
       </c>
       <c r="AJ13" t="str">
-        <v>Memory Monitoring</v>
+        <v>Backup, Tuning, PITR</v>
       </c>
       <c r="AK13" t="str">
         <v>Public Cloud Consumption</v>
@@ -6969,7 +6969,7 @@
         <v>HA</v>
       </c>
       <c r="D14" t="str">
-        <v>DATABASE LAYER</v>
+        <v>DATABASE</v>
       </c>
       <c r="E14" t="str">
         <v>Not W3 Private datacenter</v>
@@ -6981,22 +6981,22 @@
         <v>Full IaaS</v>
       </c>
       <c r="H14" t="str">
-        <v>PostgreSQL Global Development Group</v>
+        <v>Seeweb S.r.l.</v>
       </c>
       <c r="I14" t="str">
         <v>App (RunTime) - Linux native</v>
       </c>
       <c r="J14" t="str">
-        <v>2 VPC (Primary+Replica)</v>
+        <v>1 VPC (PostgreSQL Replica)</v>
       </c>
       <c r="K14" t="str">
-        <v>Seeweb Multinodo Italy (DC1)</v>
+        <v>Seeweb Italy (DC1)</v>
       </c>
       <c r="L14" t="str">
         <v>Resources - SW configuration</v>
       </c>
       <c r="M14" t="str">
-        <v>Active</v>
+        <v>Standby</v>
       </c>
       <c r="N14" t="str">
         <v>Ops Manual</v>
@@ -7005,7 +7005,7 @@
         <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
       </c>
       <c r="P14" t="str">
-        <v>Minutes (1-10)</v>
+        <v>No outages</v>
       </c>
       <c r="Q14" t="str">
         <v>Ops - Manual</v>
@@ -7014,13 +7014,13 @@
         <v>Ops Manual - direct Log-on resource</v>
       </c>
       <c r="S14" t="str">
-        <v>Minutes (1-10)</v>
+        <v>No outages</v>
       </c>
       <c r="T14" t="str">
         <v>File (TXT)</v>
       </c>
       <c r="U14" t="str">
-        <v>15.x</v>
+        <v>PostgreSQL 15.x</v>
       </c>
       <c r="V14" t="str">
         <v>SW Bins</v>
@@ -7029,7 +7029,7 @@
         <v>Object Store (SW bins)</v>
       </c>
       <c r="X14" t="str">
-        <v>Resource: Release and Recovery</v>
+        <v>Resource Recovery</v>
       </c>
       <c r="Y14" t="str">
         <v>On-Premise SW/Appliance</v>
@@ -7056,7 +7056,7 @@
         <v>Automated By App</v>
       </c>
       <c r="AG14" t="str">
-        <v>Minutes (1-5)</v>
+        <v xml:space="preserve">Seconds </v>
       </c>
       <c r="AH14" t="str">
         <v xml:space="preserve">Seconds </v>
@@ -7065,7 +7065,7 @@
         <v>SW Integrator</v>
       </c>
       <c r="AJ14" t="str">
-        <v>Backup, Tuning, PITR</v>
+        <v>Streaming Replication</v>
       </c>
       <c r="AK14" t="str">
         <v>Public Cloud Consumption</v>
@@ -7074,589 +7074,9 @@
         <v>Seeweb VPC</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>PROD</v>
-      </c>
-      <c r="B15" t="str">
-        <v>99,9%</v>
-      </c>
-      <c r="C15" t="str">
-        <v>HA</v>
-      </c>
-      <c r="D15" t="str">
-        <v>DATABASE LAYER</v>
-      </c>
-      <c r="E15" t="str">
-        <v>Not W3 Private datacenter</v>
-      </c>
-      <c r="F15" t="str">
-        <v>Vendor Private</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Full IaaS</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Seeweb S.r.l. (Ceph Storage)</v>
-      </c>
-      <c r="I15" t="str">
-        <v>Bare Metal-Linux OS</v>
-      </c>
-      <c r="J15" t="str">
-        <v>Cluster Ceph</v>
-      </c>
-      <c r="K15" t="str">
-        <v>Seeweb Multinodo Italy (DC1)</v>
-      </c>
-      <c r="L15" t="str">
-        <v>Resources - SW configuration</v>
-      </c>
-      <c r="M15" t="str">
-        <v>Active</v>
-      </c>
-      <c r="N15" t="str">
-        <v>Ops Manual</v>
-      </c>
-      <c r="O15" t="str">
-        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
-      </c>
-      <c r="P15" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="Q15" t="str">
-        <v>Ops - Manual</v>
-      </c>
-      <c r="R15" t="str">
-        <v>Ops Manual - direct Log-on resource</v>
-      </c>
-      <c r="S15" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="T15" t="str">
-        <v>File (TXT)</v>
-      </c>
-      <c r="U15" t="str">
-        <v>Quincy</v>
-      </c>
-      <c r="V15" t="str">
-        <v>SW Bins</v>
-      </c>
-      <c r="W15" t="str">
-        <v>Object Store (SW bins)</v>
-      </c>
-      <c r="X15" t="str">
-        <v>Resource Recovery</v>
-      </c>
-      <c r="Y15" t="str">
-        <v>On-Premise SW/Appliance</v>
-      </c>
-      <c r="Z15" t="str">
-        <v>On-premise Store (Appliance)</v>
-      </c>
-      <c r="AA15" t="str">
-        <v>Daily</v>
-      </c>
-      <c r="AB15" t="str">
-        <v>1 month</v>
-      </c>
-      <c r="AC15" t="str">
-        <v>1 min</v>
-      </c>
-      <c r="AD15" t="str">
-        <v>1 week</v>
-      </c>
-      <c r="AE15" t="str">
-        <v xml:space="preserve">Zone Resilent </v>
-      </c>
-      <c r="AF15" t="str">
-        <v>Automated By App</v>
-      </c>
-      <c r="AG15" t="str">
-        <v xml:space="preserve">Seconds </v>
-      </c>
-      <c r="AH15" t="str">
-        <v xml:space="preserve">Seconds </v>
-      </c>
-      <c r="AI15" t="str">
-        <v>HW/SW vendor</v>
-      </c>
-      <c r="AJ15" t="str">
-        <v>Capacity, Health</v>
-      </c>
-      <c r="AK15" t="str">
-        <v>Public Cloud Consumption</v>
-      </c>
-      <c r="AL15" t="str">
-        <v>Seeweb Storage</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>PROD</v>
-      </c>
-      <c r="B16" t="str">
-        <v>99,5%</v>
-      </c>
-      <c r="C16" t="str">
-        <v>HA-</v>
-      </c>
-      <c r="D16" t="str">
-        <v>AI SERVICES</v>
-      </c>
-      <c r="E16" t="str">
-        <v>Not W3 Public cloud Tenant</v>
-      </c>
-      <c r="F16" t="str">
-        <v>Vendor Private</v>
-      </c>
-      <c r="G16" t="str">
-        <v>Multi-tenant SaaS</v>
-      </c>
-      <c r="H16" t="str">
-        <v>OpenAI</v>
-      </c>
-      <c r="I16" t="str">
-        <v>SaaS  App - Generic Platform</v>
-      </c>
-      <c r="J16" t="str">
-        <v>SaaS</v>
-      </c>
-      <c r="K16" t="str">
-        <v>OpenAI Cloud (EU)</v>
-      </c>
-      <c r="L16" t="str">
-        <v xml:space="preserve">Internal SaaS/Cloud provider -configuration  </v>
-      </c>
-      <c r="M16" t="str">
-        <v>Active</v>
-      </c>
-      <c r="N16" t="str">
-        <v>Full Automated</v>
-      </c>
-      <c r="O16" t="str">
-        <v>Native autoscale (SaaS /Cloud providers)</v>
-      </c>
-      <c r="P16" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="Q16" t="str">
-        <v>Fully Automated</v>
-      </c>
-      <c r="R16" t="str">
-        <v>Automated By SaaS/Cloud Provider</v>
-      </c>
-      <c r="S16" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="T16" t="str">
-        <v>Database (metadata) - section of application data App configuration</v>
-      </c>
-      <c r="U16" t="str">
-        <v>API v1</v>
-      </c>
-      <c r="V16" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="W16" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="X16" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="Y16" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="Z16" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="AA16" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="AB16" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="AC16" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="AD16" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="AE16" t="str">
-        <v xml:space="preserve">Region Resilent </v>
-      </c>
-      <c r="AF16" t="str">
-        <v>Automated by Cloud/SaaS Provider</v>
-      </c>
-      <c r="AG16" t="str">
-        <v xml:space="preserve">Seconds </v>
-      </c>
-      <c r="AH16" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="AI16" t="str">
-        <v>SaaS Provider</v>
-      </c>
-      <c r="AJ16" t="str">
-        <v>API Monitoring</v>
-      </c>
-      <c r="AK16" t="str">
-        <v>Subscription</v>
-      </c>
-      <c r="AL16" t="str">
-        <v>OpenAI Pay-as-you-go</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>PROD</v>
-      </c>
-      <c r="B17" t="str">
-        <v>99,9%</v>
-      </c>
-      <c r="C17" t="str">
-        <v>HA</v>
-      </c>
-      <c r="D17" t="str">
-        <v>AI SERVICES</v>
-      </c>
-      <c r="E17" t="str">
-        <v>Not W3 Private datacenter</v>
-      </c>
-      <c r="F17" t="str">
-        <v>Vendor Private</v>
-      </c>
-      <c r="G17" t="str">
-        <v>Full IaaS</v>
-      </c>
-      <c r="H17" t="str">
-        <v>W3Suite (Easy Digital Group)</v>
-      </c>
-      <c r="I17" t="str">
-        <v>App (RunTime) - Linux native</v>
-      </c>
-      <c r="J17" t="str">
-        <v>2 VPC</v>
-      </c>
-      <c r="K17" t="str">
-        <v>Seeweb Multinodo Italy (DC1)</v>
-      </c>
-      <c r="L17" t="str">
-        <v>Resources - SW configuration</v>
-      </c>
-      <c r="M17" t="str">
-        <v>Active</v>
-      </c>
-      <c r="N17" t="str">
-        <v>Ops Manual</v>
-      </c>
-      <c r="O17" t="str">
-        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
-      </c>
-      <c r="P17" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="Q17" t="str">
-        <v>Ops - Automated</v>
-      </c>
-      <c r="R17" t="str">
-        <v>Ops Manual - direct Log-on resource</v>
-      </c>
-      <c r="S17" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="T17" t="str">
-        <v>File (Ansible playbook) - VM configuration</v>
-      </c>
-      <c r="U17" t="str">
-        <v>SemVer</v>
-      </c>
-      <c r="V17" t="str">
-        <v>SW Bins</v>
-      </c>
-      <c r="W17" t="str">
-        <v>Object Store (SW bins)</v>
-      </c>
-      <c r="X17" t="str">
-        <v>Resource Recovery</v>
-      </c>
-      <c r="Y17" t="str">
-        <v>On-Premise SW/Appliance</v>
-      </c>
-      <c r="Z17" t="str">
-        <v>On-premise Store (Appliance)</v>
-      </c>
-      <c r="AA17" t="str">
-        <v>Daily</v>
-      </c>
-      <c r="AB17" t="str">
-        <v>1 month</v>
-      </c>
-      <c r="AC17" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="AD17" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="AE17" t="str">
-        <v xml:space="preserve">Region Resilent </v>
-      </c>
-      <c r="AF17" t="str">
-        <v>Automated By App</v>
-      </c>
-      <c r="AG17" t="str">
-        <v xml:space="preserve">Seconds </v>
-      </c>
-      <c r="AH17" t="str">
-        <v xml:space="preserve">Seconds </v>
-      </c>
-      <c r="AI17" t="str">
-        <v>SW Integrator</v>
-      </c>
-      <c r="AJ17" t="str">
-        <v>AI Routing</v>
-      </c>
-      <c r="AK17" t="str">
-        <v>Public Cloud Consumption</v>
-      </c>
-      <c r="AL17" t="str">
-        <v>Seeweb VPC + W3Suite</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>PROD</v>
-      </c>
-      <c r="B18" t="str">
-        <v>99,9%</v>
-      </c>
-      <c r="C18" t="str">
-        <v>HA</v>
-      </c>
-      <c r="D18" t="str">
-        <v>SECURITY</v>
-      </c>
-      <c r="E18" t="str">
-        <v>Not W3 Private datacenter</v>
-      </c>
-      <c r="F18" t="str">
-        <v>Vendor Private</v>
-      </c>
-      <c r="G18" t="str">
-        <v>Full IaaS</v>
-      </c>
-      <c r="H18" t="str">
-        <v>W3Suite (Easy Digital Group)</v>
-      </c>
-      <c r="I18" t="str">
-        <v>App (RunTime) - Linux native</v>
-      </c>
-      <c r="J18" t="str">
-        <v>3 VPC</v>
-      </c>
-      <c r="K18" t="str">
-        <v>Seeweb Multinodo Italy (DC1)</v>
-      </c>
-      <c r="L18" t="str">
-        <v>Resources - SW configuration</v>
-      </c>
-      <c r="M18" t="str">
-        <v>Active</v>
-      </c>
-      <c r="N18" t="str">
-        <v>Ops Manual</v>
-      </c>
-      <c r="O18" t="str">
-        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
-      </c>
-      <c r="P18" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="Q18" t="str">
-        <v>Ops - Automated</v>
-      </c>
-      <c r="R18" t="str">
-        <v>Ops Manual - direct Log-on resource</v>
-      </c>
-      <c r="S18" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="T18" t="str">
-        <v>Database (metadata) - section of application data App configuration</v>
-      </c>
-      <c r="U18" t="str">
-        <v>SemVer</v>
-      </c>
-      <c r="V18" t="str">
-        <v>SW Bins</v>
-      </c>
-      <c r="W18" t="str">
-        <v>Object Store (SW bins)</v>
-      </c>
-      <c r="X18" t="str">
-        <v>Resource: Release and Recovery</v>
-      </c>
-      <c r="Y18" t="str">
-        <v>On-Premise SW/Appliance</v>
-      </c>
-      <c r="Z18" t="str">
-        <v>On-premise Store (Appliance)</v>
-      </c>
-      <c r="AA18" t="str">
-        <v>Daily</v>
-      </c>
-      <c r="AB18" t="str">
-        <v>1 month</v>
-      </c>
-      <c r="AC18" t="str">
-        <v>1 min</v>
-      </c>
-      <c r="AD18" t="str">
-        <v>1 week</v>
-      </c>
-      <c r="AE18" t="str">
-        <v xml:space="preserve">Region Resilent </v>
-      </c>
-      <c r="AF18" t="str">
-        <v>Automated By App</v>
-      </c>
-      <c r="AG18" t="str">
-        <v>Minutes (1-5)</v>
-      </c>
-      <c r="AH18" t="str">
-        <v xml:space="preserve">Seconds </v>
-      </c>
-      <c r="AI18" t="str">
-        <v>SW Integrator</v>
-      </c>
-      <c r="AJ18" t="str">
-        <v>Key Rotation, Audit</v>
-      </c>
-      <c r="AK18" t="str">
-        <v>Public Cloud Consumption</v>
-      </c>
-      <c r="AL18" t="str">
-        <v>Seeweb VPC + W3Suite</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>PROD</v>
-      </c>
-      <c r="B19" t="str">
-        <v>99,5%</v>
-      </c>
-      <c r="C19" t="str">
-        <v>HA-</v>
-      </c>
-      <c r="D19" t="str">
-        <v>OBSERVABILITY</v>
-      </c>
-      <c r="E19" t="str">
-        <v>Not W3 Private datacenter</v>
-      </c>
-      <c r="F19" t="str">
-        <v>Vendor Private</v>
-      </c>
-      <c r="G19" t="str">
-        <v>Full IaaS</v>
-      </c>
-      <c r="H19" t="str">
-        <v>Grafana Labs</v>
-      </c>
-      <c r="I19" t="str">
-        <v>App (RunTime) - Linux native</v>
-      </c>
-      <c r="J19" t="str">
-        <v>2 VPC</v>
-      </c>
-      <c r="K19" t="str">
-        <v>Seeweb Multinodo Italy (DC1)</v>
-      </c>
-      <c r="L19" t="str">
-        <v>Resources - SW configuration</v>
-      </c>
-      <c r="M19" t="str">
-        <v>Active</v>
-      </c>
-      <c r="N19" t="str">
-        <v>Ops Manual</v>
-      </c>
-      <c r="O19" t="str">
-        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
-      </c>
-      <c r="P19" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="Q19" t="str">
-        <v>Ops - Manual</v>
-      </c>
-      <c r="R19" t="str">
-        <v>Ops Manual - direct Log-on resource</v>
-      </c>
-      <c r="S19" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="T19" t="str">
-        <v>File (TXT)</v>
-      </c>
-      <c r="U19" t="str">
-        <v>10.x</v>
-      </c>
-      <c r="V19" t="str">
-        <v>SW Bins</v>
-      </c>
-      <c r="W19" t="str">
-        <v>Object Store (SW bins)</v>
-      </c>
-      <c r="X19" t="str">
-        <v>Resource Recovery</v>
-      </c>
-      <c r="Y19" t="str">
-        <v>On-Premise SW/Appliance</v>
-      </c>
-      <c r="Z19" t="str">
-        <v>On-premise Store (Appliance)</v>
-      </c>
-      <c r="AA19" t="str">
-        <v>Daily</v>
-      </c>
-      <c r="AB19" t="str">
-        <v>1 month</v>
-      </c>
-      <c r="AC19" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="AD19" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="AE19" t="str">
-        <v xml:space="preserve">Region Resilent </v>
-      </c>
-      <c r="AF19" t="str">
-        <v>Manual By Operation</v>
-      </c>
-      <c r="AG19" t="str">
-        <v>Hour (1-5)</v>
-      </c>
-      <c r="AH19" t="str">
-        <v>Hour (1-5)</v>
-      </c>
-      <c r="AI19" t="str">
-        <v>SW Integrator</v>
-      </c>
-      <c r="AJ19" t="str">
-        <v>Dashboards, Alerts</v>
-      </c>
-      <c r="AK19" t="str">
-        <v>Public Cloud Consumption</v>
-      </c>
-      <c r="AL19" t="str">
-        <v>Seeweb VPC</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A4:AL19"/>
+    <ignoredError numberStoredAsText="1" sqref="A4:AL14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/gara-appalto/SERVICE-RESOURCE-MODEL-W3SUITE-FINAL.xlsx
+++ b/docs/gara-appalto/SERVICE-RESOURCE-MODEL-W3SUITE-FINAL.xlsx
@@ -7,9 +7,9 @@
     <sheet name="Proposal Structure" sheetId="2" r:id="rId2"/>
     <sheet name="Resource Model" sheetId="3" r:id="rId3"/>
     <sheet name=" Service Model Example" sheetId="4" r:id="rId4"/>
-    <sheet name="Service Resource Distribution" sheetId="5" r:id="rId5"/>
-    <sheet name="Values&amp;Descriptions" sheetId="6" r:id="rId6"/>
-    <sheet name=" Service Model (to be filled)" sheetId="7" r:id="rId7"/>
+    <sheet name="Values&amp;Descriptions" sheetId="5" r:id="rId5"/>
+    <sheet name=" Service Model (to be filled)" sheetId="6" r:id="rId6"/>
+    <sheet name="Service Resource Distribution" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -2496,154 +2496,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="C1:S12"/>
-  <sheetData>
-    <row r="2">
-      <c r="C2" t="str">
-        <v>Public Cloud Zones or W3 Sites</v>
-      </c>
-    </row>
-    <row r="3" xml:space="preserve">
-      <c r="C3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Field Definition &amp; Values _x000d_
-_x000d_
-Module of solution</v>
-      </c>
-      <c r="D3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Field Definition &amp; Values _x000d_
-_x000d_
-Resource of module</v>
-      </c>
-      <c r="E3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Field Definition &amp; Values_x000d_
-Resource component_x000d_
-Enables to specify (if needed) components of the resources that are assigned to a site, that corrspond to different configuration_x000d_
-The resources intsalled on the site can have differen configuration that is worth to describe_x000d_
-_x000d_
-Example xample 5G Platform has specific configuration (means which cNF are  deployed or not in the istance of specific  site._x000d_
-_x000d_
-For cloud deployment for example a standBy resource can have diffrent configration</v>
-      </c>
-      <c r="F3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Field Definition &amp; Values_x000d_
-_x000d_
-W3 Sites List_x000d_
-</v>
-      </c>
-    </row>
-    <row r="7" xml:space="preserve">
-      <c r="C7" t="str">
-        <v>Module</v>
-      </c>
-      <c r="D7" t="str" xml:space="preserve">
-        <v xml:space="preserve">Service_x000d_
-Resources</v>
-      </c>
-      <c r="E7" t="str" xml:space="preserve">
-        <v xml:space="preserve">Resource _x000d_
-Component (if needed)</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Region (Zone/site)</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Zone/site</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Zone/site</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Zone/site</v>
-      </c>
-      <c r="J7" t="str">
-        <v>Zone/site</v>
-      </c>
-      <c r="K7" t="str">
-        <v>Zone/site</v>
-      </c>
-      <c r="L7" t="str">
-        <v>Zone/site</v>
-      </c>
-      <c r="M7" t="str">
-        <v>Zone/site</v>
-      </c>
-      <c r="N7" t="str">
-        <v>Zone/site</v>
-      </c>
-      <c r="O7" t="str">
-        <v>Zone/site</v>
-      </c>
-      <c r="P7" t="str">
-        <v>Zone/site</v>
-      </c>
-      <c r="Q7" t="str">
-        <v>Zone/site</v>
-      </c>
-      <c r="R7" t="str">
-        <v>Zone/site</v>
-      </c>
-      <c r="S7" t="str">
-        <v>Zone/site</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="F8" t="str">
-        <v>W3-(Core site) - 1</v>
-      </c>
-      <c r="G8" t="str">
-        <v>W3-(Core site) - 1</v>
-      </c>
-      <c r="H8" t="str">
-        <v>W3-(Core site) - 1</v>
-      </c>
-      <c r="I8" t="str">
-        <v>W3-(Core site) - 1</v>
-      </c>
-      <c r="J8" t="str">
-        <v>W3-(Core site) - 1</v>
-      </c>
-      <c r="K8" t="str">
-        <v>W3-(Core site) - 1</v>
-      </c>
-      <c r="L8" t="str">
-        <v>W3-(Core site) - 1</v>
-      </c>
-      <c r="M8" t="str">
-        <v>W3-(Core site) - 1</v>
-      </c>
-      <c r="N8" t="str">
-        <v>W3-(Core site) - 1</v>
-      </c>
-      <c r="O8" t="str">
-        <v>W3-(Core site) - 1</v>
-      </c>
-      <c r="P8" t="str">
-        <v>W3-(Core site) - 1</v>
-      </c>
-      <c r="Q8" t="str">
-        <v>W3-(Core site) - 1</v>
-      </c>
-      <c r="R8" t="str">
-        <v>W3-(Core site) - 1</v>
-      </c>
-      <c r="S8" t="str">
-        <v>W3-(Core site) - 1</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="F3:S3"/>
-    <mergeCell ref="C2:S2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="C1:S12"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="B2:H395"/>
   <sheetData>
     <row r="2">
@@ -5922,460 +5774,354 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A4:AL14"/>
+  <dimension ref="A1:AL15"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" customWidth="1"/>
-    <col min="4" max="4" width="28.83203125" customWidth="1"/>
-    <col min="5" max="5" width="28.83203125" customWidth="1"/>
-    <col min="6" max="6" width="28.83203125" customWidth="1"/>
-    <col min="7" max="7" width="28.83203125" customWidth="1"/>
-    <col min="8" max="8" width="28.83203125" customWidth="1"/>
-    <col min="9" max="9" width="28.83203125" customWidth="1"/>
-    <col min="10" max="10" width="28.83203125" customWidth="1"/>
-    <col min="11" max="11" width="28.83203125" customWidth="1"/>
-    <col min="12" max="12" width="28.83203125" customWidth="1"/>
-    <col min="13" max="13" width="28.83203125" customWidth="1"/>
-    <col min="14" max="14" width="28.83203125" customWidth="1"/>
-    <col min="15" max="15" width="28.83203125" customWidth="1"/>
-    <col min="16" max="16" width="28.83203125" customWidth="1"/>
-    <col min="17" max="17" width="28.83203125" customWidth="1"/>
-    <col min="18" max="18" width="28.83203125" customWidth="1"/>
-    <col min="19" max="19" width="28.83203125" customWidth="1"/>
-    <col min="20" max="20" width="28.83203125" customWidth="1"/>
-    <col min="21" max="21" width="28.83203125" customWidth="1"/>
-    <col min="22" max="22" width="28.83203125" customWidth="1"/>
-    <col min="23" max="23" width="28.83203125" customWidth="1"/>
-    <col min="24" max="24" width="28.83203125" customWidth="1"/>
-    <col min="25" max="25" width="28.83203125" customWidth="1"/>
-    <col min="26" max="26" width="28.83203125" customWidth="1"/>
-    <col min="27" max="27" width="28.83203125" customWidth="1"/>
-    <col min="28" max="28" width="28.83203125" customWidth="1"/>
-    <col min="29" max="29" width="28.83203125" customWidth="1"/>
-    <col min="30" max="30" width="28.83203125" customWidth="1"/>
-    <col min="31" max="31" width="28.83203125" customWidth="1"/>
-    <col min="32" max="32" width="28.83203125" customWidth="1"/>
-    <col min="33" max="33" width="28.83203125" customWidth="1"/>
-    <col min="34" max="34" width="28.83203125" customWidth="1"/>
-    <col min="35" max="35" width="28.83203125" customWidth="1"/>
-    <col min="36" max="36" width="28.83203125" customWidth="1"/>
-    <col min="37" max="37" width="28.83203125" customWidth="1"/>
-    <col min="38" max="38" width="28.83203125" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" customWidth="1"/>
+    <col min="6" max="6" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="22.83203125" customWidth="1"/>
+    <col min="8" max="8" width="22.83203125" customWidth="1"/>
+    <col min="9" max="9" width="22.83203125" customWidth="1"/>
+    <col min="10" max="10" width="22.83203125" customWidth="1"/>
+    <col min="11" max="11" width="22.83203125" customWidth="1"/>
+    <col min="12" max="12" width="22.83203125" customWidth="1"/>
+    <col min="13" max="13" width="22.83203125" customWidth="1"/>
+    <col min="14" max="14" width="22.83203125" customWidth="1"/>
+    <col min="15" max="15" width="22.83203125" customWidth="1"/>
+    <col min="16" max="16" width="22.83203125" customWidth="1"/>
+    <col min="17" max="17" width="22.83203125" customWidth="1"/>
+    <col min="18" max="18" width="22.83203125" customWidth="1"/>
+    <col min="19" max="19" width="22.83203125" customWidth="1"/>
+    <col min="20" max="20" width="22.83203125" customWidth="1"/>
+    <col min="21" max="21" width="22.83203125" customWidth="1"/>
+    <col min="22" max="22" width="22.83203125" customWidth="1"/>
+    <col min="23" max="23" width="22.83203125" customWidth="1"/>
+    <col min="24" max="24" width="22.83203125" customWidth="1"/>
+    <col min="25" max="25" width="22.83203125" customWidth="1"/>
+    <col min="26" max="26" width="22.83203125" customWidth="1"/>
+    <col min="27" max="27" width="22.83203125" customWidth="1"/>
+    <col min="28" max="28" width="22.83203125" customWidth="1"/>
+    <col min="29" max="29" width="22.83203125" customWidth="1"/>
+    <col min="30" max="30" width="22.83203125" customWidth="1"/>
+    <col min="31" max="31" width="22.83203125" customWidth="1"/>
+    <col min="32" max="32" width="22.83203125" customWidth="1"/>
+    <col min="33" max="33" width="22.83203125" customWidth="1"/>
+    <col min="34" max="34" width="22.83203125" customWidth="1"/>
+    <col min="35" max="35" width="22.83203125" customWidth="1"/>
+    <col min="36" max="36" width="22.83203125" customWidth="1"/>
+    <col min="37" max="37" width="22.83203125" customWidth="1"/>
+    <col min="38" max="38" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>HERE YOU CAN FIND SOME NOTES TO HELP YOU UNDERSTAND HOW TO FILL IN THIS FORM. YOU CAN FIND THE COMPLETE VALUES LIST AND RELATED DESCRIPTION ON TAB "Values&amp;Description"</v>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Environment</v>
+      </c>
+      <c r="B5" t="str">
+        <v>SLA Model &amp; Resource Model</v>
+      </c>
+      <c r="C5" t="str">
         <v/>
       </c>
-      <c r="B4" t="str">
-        <v>Environment</v>
-      </c>
-      <c r="C4" t="str">
-        <v>SLA Model &amp; Resource Model</v>
-      </c>
-      <c r="D4" t="str">
+      <c r="D5" t="str">
         <v/>
       </c>
-      <c r="E4" t="str">
+      <c r="E5" t="str">
         <v/>
       </c>
-      <c r="F4" t="str">
+      <c r="F5" t="str">
         <v/>
       </c>
-      <c r="G4" t="str">
+      <c r="G5" t="str">
         <v/>
       </c>
-      <c r="H4" t="str">
+      <c r="H5" t="str">
         <v/>
       </c>
-      <c r="I4" t="str">
+      <c r="I5" t="str">
         <v/>
       </c>
-      <c r="J4" t="str">
+      <c r="J5" t="str">
         <v/>
       </c>
-      <c r="K4" t="str">
+      <c r="K5" t="str">
         <v/>
       </c>
-      <c r="L4" t="str">
+      <c r="L5" t="str">
         <v/>
       </c>
-      <c r="M4" t="str">
+      <c r="M5" t="str">
         <v/>
       </c>
-      <c r="N4" t="str">
+      <c r="N5" t="str">
         <v>Capacity  Model</v>
       </c>
-      <c r="O4" t="str">
+      <c r="O5" t="str">
         <v/>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
+    <row r="7">
+      <c r="A7" t="str">
         <v/>
       </c>
-      <c r="B6" t="str">
+      <c r="B7" t="str">
         <v xml:space="preserve">SLA </v>
       </c>
-      <c r="C6" t="str">
+      <c r="C7" t="str">
         <v/>
       </c>
-      <c r="D6" t="str">
+      <c r="D7" t="str">
         <v>Resource Model</v>
       </c>
-      <c r="E6" t="str">
+      <c r="E7" t="str">
         <v/>
       </c>
-      <c r="F6" t="str">
+      <c r="F7" t="str">
         <v/>
       </c>
-      <c r="G6" t="str">
+      <c r="G7" t="str">
         <v/>
       </c>
-      <c r="H6" t="str">
+      <c r="H7" t="str">
         <v/>
       </c>
-      <c r="I6" t="str">
+      <c r="I7" t="str">
         <v/>
       </c>
-      <c r="J6" t="str">
+      <c r="J7" t="str">
         <v>Resource Distribution Model &amp; HA</v>
       </c>
-      <c r="K6" t="str">
+      <c r="K7" t="str">
         <v/>
       </c>
-      <c r="L6" t="str">
+      <c r="L7" t="str">
         <v/>
       </c>
-      <c r="M6" t="str">
+      <c r="M7" t="str">
         <v/>
       </c>
-      <c r="N6" t="str">
+      <c r="N7" t="str">
         <v>Capacity Model</v>
       </c>
-      <c r="O6" t="str">
+      <c r="O7" t="str">
         <v/>
       </c>
-      <c r="P6" t="str">
+      <c r="P7" t="str">
         <v/>
       </c>
-      <c r="Q6" t="str">
+      <c r="Q7" t="str">
         <v>Release Method</v>
       </c>
-      <c r="R6" t="str">
+      <c r="R7" t="str">
         <v/>
       </c>
-      <c r="S6" t="str">
+      <c r="S7" t="str">
         <v/>
       </c>
-      <c r="T6" t="str">
+      <c r="T7" t="str">
         <v>Release Configuration  &amp; Artifacts</v>
       </c>
-      <c r="U6" t="str">
+      <c r="U7" t="str">
         <v/>
       </c>
-      <c r="V6" t="str">
+      <c r="V7" t="str">
         <v/>
       </c>
-      <c r="W6" t="str">
+      <c r="W7" t="str">
         <v/>
       </c>
-      <c r="X6" t="str">
+      <c r="X7" t="str">
         <v>Use for and Method &amp; store</v>
       </c>
-      <c r="Y6" t="str">
+      <c r="Y7" t="str">
         <v/>
       </c>
-      <c r="Z6" t="str">
+      <c r="Z7" t="str">
         <v/>
       </c>
-      <c r="AA6" t="str">
+      <c r="AA7" t="str">
         <v>Full</v>
       </c>
-      <c r="AB6" t="str">
+      <c r="AB7" t="str">
         <v/>
       </c>
-      <c r="AC6" t="str">
+      <c r="AC7" t="str">
         <v>Incremental (log)</v>
       </c>
-      <c r="AD6" t="str">
+      <c r="AD7" t="str">
         <v/>
       </c>
-      <c r="AE6" t="str">
+      <c r="AE7" t="str">
         <v>Fail-over/Fail-Back (recover full capacity)</v>
       </c>
-      <c r="AF6" t="str">
+      <c r="AF7" t="str">
         <v/>
       </c>
-      <c r="AG6" t="str">
+      <c r="AG7" t="str">
         <v/>
       </c>
-      <c r="AH6" t="str">
+      <c r="AH7" t="str">
         <v/>
       </c>
-      <c r="AI6" t="str">
+      <c r="AI7" t="str">
         <v>Operation Model</v>
       </c>
-      <c r="AJ6" t="str">
+      <c r="AJ7" t="str">
         <v/>
       </c>
-      <c r="AK6" t="str">
+      <c r="AK7" t="str">
         <v>Cost Model</v>
       </c>
-      <c r="AL6" t="str">
+      <c r="AL7" t="str">
         <v/>
       </c>
     </row>
-    <row r="7" xml:space="preserve">
-      <c r="A7" t="str">
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str">
         <v>ENV</v>
       </c>
-      <c r="B7" t="str" xml:space="preserve">
+      <c r="B8" t="str" xml:space="preserve">
         <v xml:space="preserve">SLA
 Value</v>
       </c>
-      <c r="C7" t="str" xml:space="preserve">
+      <c r="C8" t="str" xml:space="preserve">
         <v xml:space="preserve">SLA
 Class</v>
       </c>
-      <c r="D7" t="str" xml:space="preserve">
+      <c r="D8" t="str" xml:space="preserve">
         <v xml:space="preserve">Proposal
  Modules</v>
       </c>
-      <c r="E7" t="str">
+      <c r="E8" t="str">
         <v>Hosting Model</v>
       </c>
-      <c r="F7" t="str" xml:space="preserve">
+      <c r="F8" t="str" xml:space="preserve">
         <v xml:space="preserve">Hosting 
 Provider</v>
       </c>
-      <c r="G7" t="str" xml:space="preserve">
+      <c r="G8" t="str" xml:space="preserve">
         <v xml:space="preserve">Technical Model
 Module</v>
       </c>
-      <c r="H7" t="str" xml:space="preserve">
+      <c r="H8" t="str" xml:space="preserve">
         <v xml:space="preserve"> Service  Resource 
 Vendor Name (Relations)</v>
       </c>
-      <c r="I7" t="str" xml:space="preserve">
+      <c r="I8" t="str" xml:space="preserve">
         <v xml:space="preserve">Service Resources 
 Implementation</v>
       </c>
-      <c r="J7" t="str">
+      <c r="J8" t="str">
         <v># instances</v>
       </c>
-      <c r="K7" t="str">
+      <c r="K8" t="str">
         <v>Region/Zone Distribution</v>
       </c>
-      <c r="L7" t="str">
+      <c r="L8" t="str">
         <v>Distribution Method</v>
       </c>
-      <c r="M7" t="str" xml:space="preserve">
+      <c r="M8" t="str" xml:space="preserve">
         <v xml:space="preserve">Resource Role
 Distribution</v>
       </c>
-      <c r="N7" t="str" xml:space="preserve">
+      <c r="N8" t="str" xml:space="preserve">
         <v xml:space="preserve">Capacity
 Class</v>
       </c>
-      <c r="O7" t="str">
+      <c r="O8" t="str">
         <v>Method</v>
       </c>
-      <c r="P7" t="str">
+      <c r="P8" t="str">
         <v>Outages</v>
       </c>
-      <c r="Q7" t="str" xml:space="preserve">
+      <c r="Q8" t="str" xml:space="preserve">
         <v xml:space="preserve">Release
 Class</v>
       </c>
-      <c r="R7" t="str">
+      <c r="R8" t="str">
         <v>Method</v>
       </c>
-      <c r="S7" t="str">
+      <c r="S8" t="str">
         <v>Outages</v>
       </c>
-      <c r="T7" t="str" xml:space="preserve">
+      <c r="T8" t="str" xml:space="preserve">
         <v xml:space="preserve">Configuration
 Specification</v>
       </c>
-      <c r="U7" t="str" xml:space="preserve">
+      <c r="U8" t="str" xml:space="preserve">
         <v xml:space="preserve">Configuration
 Version</v>
       </c>
-      <c r="V7" t="str" xml:space="preserve">
+      <c r="V8" t="str" xml:space="preserve">
         <v xml:space="preserve">Deploy
 Artifact
 </v>
       </c>
-      <c r="W7" t="str" xml:space="preserve">
+      <c r="W8" t="str" xml:space="preserve">
         <v xml:space="preserve">Artifact 
 Registry</v>
       </c>
-      <c r="X7" t="str">
+      <c r="X8" t="str">
         <v>Use for</v>
       </c>
-      <c r="Y7" t="str">
+      <c r="Y8" t="str">
         <v>Method</v>
       </c>
-      <c r="Z7" t="str">
+      <c r="Z8" t="str">
         <v>Store</v>
       </c>
-      <c r="AA7" t="str">
+      <c r="AA8" t="str">
         <v>Freq.</v>
       </c>
-      <c r="AB7" t="str">
+      <c r="AB8" t="str">
         <v>Retention</v>
       </c>
-      <c r="AC7" t="str">
+      <c r="AC8" t="str">
         <v>Freq.</v>
       </c>
-      <c r="AD7" t="str">
+      <c r="AD8" t="str">
         <v>Retention</v>
       </c>
-      <c r="AE7" t="str" xml:space="preserve">
+      <c r="AE8" t="str" xml:space="preserve">
         <v xml:space="preserve">Recovery 
 Class</v>
       </c>
-      <c r="AF7" t="str">
+      <c r="AF8" t="str">
         <v>Method</v>
       </c>
-      <c r="AG7" t="str">
+      <c r="AG8" t="str">
         <v>RTO</v>
       </c>
-      <c r="AH7" t="str">
+      <c r="AH8" t="str">
         <v>RPO</v>
       </c>
-      <c r="AI7" t="str">
+      <c r="AI8" t="str">
         <v>Operated By</v>
       </c>
-      <c r="AJ7" t="str" xml:space="preserve">
+      <c r="AJ8" t="str" xml:space="preserve">
         <v xml:space="preserve">Operation other Activities
 (which  W3 activities)</v>
       </c>
-      <c r="AK7" t="str">
+      <c r="AK8" t="str">
         <v>Model</v>
       </c>
-      <c r="AL7" t="str">
+      <c r="AL8" t="str">
         <v>Details</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>PROD</v>
-      </c>
-      <c r="B8" t="str">
-        <v>99,9%</v>
-      </c>
-      <c r="C8" t="str">
-        <v>HA</v>
-      </c>
-      <c r="D8" t="str">
-        <v>INFRASTRUCTURE</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Not W3 Private datacenter</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Vendor Private</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Full IaaS</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Seeweb S.r.l.</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Virtualization Platform - ProxMox</v>
-      </c>
-      <c r="J8" t="str">
-        <v>1 Cluster Multinodo</v>
-      </c>
-      <c r="K8" t="str">
-        <v>Seeweb Italy (DC1)</v>
-      </c>
-      <c r="L8" t="str">
-        <v>Resources - SW configuration</v>
-      </c>
-      <c r="M8" t="str">
-        <v>Active</v>
-      </c>
-      <c r="N8" t="str">
-        <v>Ops Manual</v>
-      </c>
-      <c r="O8" t="str">
-        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
-      </c>
-      <c r="P8" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="Q8" t="str">
-        <v>Ops - Manual</v>
-      </c>
-      <c r="R8" t="str">
-        <v>Ops Manual - direct Log-on resource</v>
-      </c>
-      <c r="S8" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="T8" t="str">
-        <v>File (TXT)</v>
-      </c>
-      <c r="U8" t="str">
-        <v>Proxmox VE 8.x</v>
-      </c>
-      <c r="V8" t="str">
-        <v>VMI (virtual Machine Image) - KVM</v>
-      </c>
-      <c r="W8" t="str">
-        <v>Private Others Registry</v>
-      </c>
-      <c r="X8" t="str">
-        <v>Resource Recovery</v>
-      </c>
-      <c r="Y8" t="str">
-        <v>On-Premise SW/Appliance</v>
-      </c>
-      <c r="Z8" t="str">
-        <v>On-premise Store (Appliance)</v>
-      </c>
-      <c r="AA8" t="str">
-        <v>Daily</v>
-      </c>
-      <c r="AB8" t="str">
-        <v>1 month</v>
-      </c>
-      <c r="AC8" t="str">
-        <v>1 min</v>
-      </c>
-      <c r="AD8" t="str">
-        <v>1 week</v>
-      </c>
-      <c r="AE8" t="str">
-        <v xml:space="preserve">Region Resilent </v>
-      </c>
-      <c r="AF8" t="str">
-        <v>Automated By App</v>
-      </c>
-      <c r="AG8" t="str">
-        <v>Minutes (1-5)</v>
-      </c>
-      <c r="AH8" t="str">
-        <v>Minutes (1-5)</v>
-      </c>
-      <c r="AI8" t="str">
-        <v>HW/SW vendor</v>
-      </c>
-      <c r="AJ8" t="str">
-        <v>Cluster Management</v>
-      </c>
-      <c r="AK8" t="str">
-        <v>Public Cloud Consumption</v>
-      </c>
-      <c r="AL8" t="str">
-        <v>Seeweb Multinodo Contract</v>
       </c>
     </row>
     <row r="9">
@@ -6383,10 +6129,10 @@
         <v>PROD</v>
       </c>
       <c r="B9" t="str">
-        <v>99,5%</v>
+        <v>99,9%</v>
       </c>
       <c r="C9" t="str">
-        <v>HA-</v>
+        <v>HA</v>
       </c>
       <c r="D9" t="str">
         <v>INFRASTRUCTURE</v>
@@ -6398,19 +6144,19 @@
         <v>Vendor Private</v>
       </c>
       <c r="G9" t="str">
-        <v>HW Appliance</v>
+        <v>Full IaaS</v>
       </c>
       <c r="H9" t="str">
-        <v>Seeweb S.r.l. (Fortinet)</v>
+        <v>Seeweb S.r.l. - Proxmox VE Cluster</v>
       </c>
       <c r="I9" t="str">
-        <v>HW Appliance - FortiGate NGFW</v>
-      </c>
-      <c r="J9" t="str">
-        <v>1 (Single)</v>
+        <v>Virtualization Platform - ProxMox</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
       </c>
       <c r="K9" t="str">
-        <v>Seeweb Italy (DC1)</v>
+        <v>Cloud-Single-zone</v>
       </c>
       <c r="L9" t="str">
         <v>Resources - SW configuration</v>
@@ -6419,10 +6165,10 @@
         <v>Active</v>
       </c>
       <c r="N9" t="str">
-        <v>Fixed capacity</v>
+        <v>Ops Manual</v>
       </c>
       <c r="O9" t="str">
-        <v>Do not scale - Fixed capacity</v>
+        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
       </c>
       <c r="P9" t="str">
         <v>No outages</v>
@@ -6437,13 +6183,13 @@
         <v>No outages</v>
       </c>
       <c r="T9" t="str">
-        <v>File (TXT)</v>
+        <v>Configuration File (TXT)</v>
       </c>
       <c r="U9" t="str">
-        <v>FortiOS 7.x</v>
+        <v>Vendor Versioning</v>
       </c>
       <c r="V9" t="str">
-        <v>SW Bins</v>
+        <v>VMI (Virtual Machine Image) - KVM</v>
       </c>
       <c r="W9" t="str">
         <v>Private Others Registry</v>
@@ -6464,34 +6210,34 @@
         <v>1 month</v>
       </c>
       <c r="AC9" t="str">
-        <v>N/A</v>
+        <v>1 min</v>
       </c>
       <c r="AD9" t="str">
-        <v>N/A</v>
+        <v>1 week</v>
       </c>
       <c r="AE9" t="str">
-        <v xml:space="preserve">Local Resilent </v>
+        <v xml:space="preserve">Region Resilent </v>
       </c>
       <c r="AF9" t="str">
-        <v>Manual By Operation</v>
+        <v>Automated By App</v>
       </c>
       <c r="AG9" t="str">
-        <v>Hour (1-5)</v>
+        <v>Minutes (1-5)</v>
       </c>
       <c r="AH9" t="str">
-        <v>Hour (1-5)</v>
+        <v>Minutes (1-5)</v>
       </c>
       <c r="AI9" t="str">
         <v>HW/SW vendor</v>
       </c>
       <c r="AJ9" t="str">
-        <v>Security Management</v>
+        <v>Cluster Management, VM Provisioning</v>
       </c>
       <c r="AK9" t="str">
-        <v>COTs SW License</v>
+        <v>Public Cloud Consumption</v>
       </c>
       <c r="AL9" t="str">
-        <v>Seeweb FortiGate Service</v>
+        <v>Seeweb Multinodo Contract</v>
       </c>
     </row>
     <row r="10">
@@ -6499,10 +6245,10 @@
         <v>PROD</v>
       </c>
       <c r="B10" t="str">
-        <v>99,9%</v>
+        <v>99,5%</v>
       </c>
       <c r="C10" t="str">
-        <v>HA</v>
+        <v>HA-</v>
       </c>
       <c r="D10" t="str">
         <v>INFRASTRUCTURE</v>
@@ -6514,31 +6260,31 @@
         <v>Vendor Private</v>
       </c>
       <c r="G10" t="str">
-        <v>Bare Metal</v>
+        <v>HW Appliance</v>
       </c>
       <c r="H10" t="str">
-        <v>Seeweb S.r.l.</v>
+        <v>Seeweb S.r.l. - Fortinet FortiGate</v>
       </c>
       <c r="I10" t="str">
-        <v>Bare Metal-Linux OS</v>
-      </c>
-      <c r="J10" t="str">
-        <v>1 (Dedicato)</v>
+        <v>HW Appliance - FortiGate NGFW</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
       </c>
       <c r="K10" t="str">
-        <v>Seeweb Italy (DC2 - DR)</v>
+        <v>Cloud-Single-zone</v>
       </c>
       <c r="L10" t="str">
-        <v>Resources - SW configuration</v>
+        <v>Resource - Manual Installation</v>
       </c>
       <c r="M10" t="str">
         <v>Active</v>
       </c>
       <c r="N10" t="str">
-        <v>Ops Manual</v>
+        <v>Fixed capacity</v>
       </c>
       <c r="O10" t="str">
-        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
+        <v>Do not scale - Fixed capacity</v>
       </c>
       <c r="P10" t="str">
         <v>No outages</v>
@@ -6553,16 +6299,16 @@
         <v>No outages</v>
       </c>
       <c r="T10" t="str">
-        <v>File (TXT)</v>
+        <v>Configuration File (TXT)</v>
       </c>
       <c r="U10" t="str">
-        <v>PBS 3.x</v>
+        <v>Vendor Versioning</v>
       </c>
       <c r="V10" t="str">
         <v>SW Bins</v>
       </c>
       <c r="W10" t="str">
-        <v>Object Store (SW bins)</v>
+        <v>Private Others Registry</v>
       </c>
       <c r="X10" t="str">
         <v>Resource Recovery</v>
@@ -6580,13 +6326,13 @@
         <v>1 month</v>
       </c>
       <c r="AC10" t="str">
-        <v>1 min</v>
+        <v>N/A</v>
       </c>
       <c r="AD10" t="str">
-        <v>1 week</v>
+        <v>N/A</v>
       </c>
       <c r="AE10" t="str">
-        <v xml:space="preserve">Region Resilent </v>
+        <v xml:space="preserve">Local Resilent </v>
       </c>
       <c r="AF10" t="str">
         <v>Manual By Operation</v>
@@ -6595,19 +6341,19 @@
         <v>Hour (1-5)</v>
       </c>
       <c r="AH10" t="str">
-        <v>Minutes (1-5)</v>
+        <v>Hour (1-5)</v>
       </c>
       <c r="AI10" t="str">
         <v>HW/SW vendor</v>
       </c>
       <c r="AJ10" t="str">
-        <v>Backup &amp; DR</v>
+        <v>Security Policy, Threat Monitoring</v>
       </c>
       <c r="AK10" t="str">
-        <v>Public Cloud Consumption</v>
+        <v>COTs SW License</v>
       </c>
       <c r="AL10" t="str">
-        <v>Seeweb PBS Service</v>
+        <v>FortiCare via Seeweb</v>
       </c>
     </row>
     <row r="11">
@@ -6621,7 +6367,7 @@
         <v>HA</v>
       </c>
       <c r="D11" t="str">
-        <v>APPLICATION</v>
+        <v>INFRASTRUCTURE</v>
       </c>
       <c r="E11" t="str">
         <v>Not W3 Private datacenter</v>
@@ -6630,19 +6376,19 @@
         <v>Vendor Private</v>
       </c>
       <c r="G11" t="str">
-        <v>Full IaaS</v>
+        <v>Bare Metal</v>
       </c>
       <c r="H11" t="str">
-        <v>Seeweb S.r.l.</v>
+        <v>Seeweb S.r.l. - Proxmox Backup Server</v>
       </c>
       <c r="I11" t="str">
-        <v>App (RunTime) - Linux native</v>
-      </c>
-      <c r="J11" t="str">
-        <v>1 VPC (Nginx + LB)</v>
+        <v>Bare Metal - PBS Dedicated</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
       </c>
       <c r="K11" t="str">
-        <v>Seeweb Italy (DC1)</v>
+        <v>Cloud-Single-zone</v>
       </c>
       <c r="L11" t="str">
         <v>Resources - SW configuration</v>
@@ -6660,7 +6406,7 @@
         <v>No outages</v>
       </c>
       <c r="Q11" t="str">
-        <v>Ops - Automated</v>
+        <v>Ops - Manual</v>
       </c>
       <c r="R11" t="str">
         <v>Ops Manual - direct Log-on resource</v>
@@ -6669,10 +6415,10 @@
         <v>No outages</v>
       </c>
       <c r="T11" t="str">
-        <v>File (Ansible playbook) - VM configuration</v>
+        <v>Configuration File (TXT)</v>
       </c>
       <c r="U11" t="str">
-        <v>Nginx 1.24 + W3Suite FE</v>
+        <v>Vendor Versioning</v>
       </c>
       <c r="V11" t="str">
         <v>SW Bins</v>
@@ -6705,25 +6451,25 @@
         <v xml:space="preserve">Region Resilent </v>
       </c>
       <c r="AF11" t="str">
-        <v>Automated By App</v>
+        <v>Manual By Operation</v>
       </c>
       <c r="AG11" t="str">
-        <v xml:space="preserve">Seconds </v>
+        <v>Hour (1-5)</v>
       </c>
       <c r="AH11" t="str">
-        <v>N/A</v>
+        <v>Minutes (1-5)</v>
       </c>
       <c r="AI11" t="str">
-        <v>SW Integrator</v>
+        <v>HW/SW vendor</v>
       </c>
       <c r="AJ11" t="str">
-        <v>TLS, Routing, LB Config</v>
+        <v>Backup Storage, DR Recovery</v>
       </c>
       <c r="AK11" t="str">
         <v>Public Cloud Consumption</v>
       </c>
       <c r="AL11" t="str">
-        <v>Seeweb VPC</v>
+        <v>Seeweb PBS Service</v>
       </c>
     </row>
     <row r="12">
@@ -6749,16 +6495,16 @@
         <v>Full IaaS</v>
       </c>
       <c r="H12" t="str">
-        <v>Seeweb S.r.l.</v>
+        <v>Seeweb S.r.l. - W3Suite Frontend</v>
       </c>
       <c r="I12" t="str">
         <v>App (RunTime) - Linux native</v>
       </c>
-      <c r="J12" t="str">
-        <v>1 VPC (API+Redis+MCP)</v>
+      <c r="J12">
+        <v>1</v>
       </c>
       <c r="K12" t="str">
-        <v>Seeweb Italy (DC1)</v>
+        <v>Cloud-Single-zone</v>
       </c>
       <c r="L12" t="str">
         <v>Resources - SW configuration</v>
@@ -6779,16 +6525,16 @@
         <v>Ops - Automated</v>
       </c>
       <c r="R12" t="str">
-        <v>Ops Manual - direct Log-on resource</v>
+        <v xml:space="preserve">Ops Automated (SW) - DevOps </v>
       </c>
       <c r="S12" t="str">
         <v>No outages</v>
       </c>
       <c r="T12" t="str">
-        <v>File (Ansible playbook) - VM configuration</v>
+        <v>Configuration File (YAML)</v>
       </c>
       <c r="U12" t="str">
-        <v>W3Suite API + Redis + MCP</v>
+        <v>W3 Git</v>
       </c>
       <c r="V12" t="str">
         <v>SW Bins</v>
@@ -6824,7 +6570,7 @@
         <v>Automated By App</v>
       </c>
       <c r="AG12" t="str">
-        <v>Minutes (1-5)</v>
+        <v xml:space="preserve">Seconds </v>
       </c>
       <c r="AH12" t="str">
         <v xml:space="preserve">Seconds </v>
@@ -6833,7 +6579,7 @@
         <v>SW Integrator</v>
       </c>
       <c r="AJ12" t="str">
-        <v>Deploy, API, AI Gateway</v>
+        <v>TLS, Routing, LB Config</v>
       </c>
       <c r="AK12" t="str">
         <v>Public Cloud Consumption</v>
@@ -6853,7 +6599,7 @@
         <v>HA</v>
       </c>
       <c r="D13" t="str">
-        <v>DATABASE</v>
+        <v>APPLICATION</v>
       </c>
       <c r="E13" t="str">
         <v>Not W3 Private datacenter</v>
@@ -6865,16 +6611,16 @@
         <v>Full IaaS</v>
       </c>
       <c r="H13" t="str">
-        <v>Seeweb S.r.l.</v>
+        <v>Seeweb S.r.l. - W3Suite Backend</v>
       </c>
       <c r="I13" t="str">
         <v>App (RunTime) - Linux native</v>
       </c>
-      <c r="J13" t="str">
-        <v>1 VPC (PostgreSQL Primary)</v>
+      <c r="J13">
+        <v>1</v>
       </c>
       <c r="K13" t="str">
-        <v>Seeweb Italy (DC1)</v>
+        <v>Cloud-Single-zone</v>
       </c>
       <c r="L13" t="str">
         <v>Resources - SW configuration</v>
@@ -6889,22 +6635,22 @@
         <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
       </c>
       <c r="P13" t="str">
-        <v>Minutes (1-10)</v>
+        <v>No outages</v>
       </c>
       <c r="Q13" t="str">
-        <v>Ops - Manual</v>
+        <v>Ops - Automated</v>
       </c>
       <c r="R13" t="str">
-        <v>Ops Manual - direct Log-on resource</v>
+        <v xml:space="preserve">Ops Automated (SW) - DevOps </v>
       </c>
       <c r="S13" t="str">
-        <v>Minutes (1-10)</v>
+        <v>No outages</v>
       </c>
       <c r="T13" t="str">
-        <v>File (TXT)</v>
+        <v>Configuration File (YAML)</v>
       </c>
       <c r="U13" t="str">
-        <v>PostgreSQL 15.x</v>
+        <v>W3 Git</v>
       </c>
       <c r="V13" t="str">
         <v>SW Bins</v>
@@ -6913,7 +6659,7 @@
         <v>Object Store (SW bins)</v>
       </c>
       <c r="X13" t="str">
-        <v>Resource: Release and Recovery</v>
+        <v>Resource Recovery</v>
       </c>
       <c r="Y13" t="str">
         <v>On-Premise SW/Appliance</v>
@@ -6949,7 +6695,7 @@
         <v>SW Integrator</v>
       </c>
       <c r="AJ13" t="str">
-        <v>Backup, Tuning, PITR</v>
+        <v>Deploy, API, AI Gateway, Cache</v>
       </c>
       <c r="AK13" t="str">
         <v>Public Cloud Consumption</v>
@@ -6966,7 +6712,7 @@
         <v>99,9%</v>
       </c>
       <c r="C14" t="str">
-        <v>HA</v>
+        <v>HA+</v>
       </c>
       <c r="D14" t="str">
         <v>DATABASE</v>
@@ -6981,22 +6727,22 @@
         <v>Full IaaS</v>
       </c>
       <c r="H14" t="str">
-        <v>Seeweb S.r.l.</v>
+        <v>Seeweb S.r.l. - PostgreSQL Primary</v>
       </c>
       <c r="I14" t="str">
         <v>App (RunTime) - Linux native</v>
       </c>
-      <c r="J14" t="str">
-        <v>1 VPC (PostgreSQL Replica)</v>
+      <c r="J14">
+        <v>1</v>
       </c>
       <c r="K14" t="str">
-        <v>Seeweb Italy (DC1)</v>
+        <v>Cloud-Single-zone</v>
       </c>
       <c r="L14" t="str">
         <v>Resources - SW configuration</v>
       </c>
       <c r="M14" t="str">
-        <v>Standby</v>
+        <v>Active</v>
       </c>
       <c r="N14" t="str">
         <v>Ops Manual</v>
@@ -7005,7 +6751,7 @@
         <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
       </c>
       <c r="P14" t="str">
-        <v>No outages</v>
+        <v>Minutes (1-10)</v>
       </c>
       <c r="Q14" t="str">
         <v>Ops - Manual</v>
@@ -7014,13 +6760,13 @@
         <v>Ops Manual - direct Log-on resource</v>
       </c>
       <c r="S14" t="str">
-        <v>No outages</v>
+        <v>Minutes (1-10)</v>
       </c>
       <c r="T14" t="str">
-        <v>File (TXT)</v>
+        <v>Configuration File (TXT)</v>
       </c>
       <c r="U14" t="str">
-        <v>PostgreSQL 15.x</v>
+        <v>Vendor Versioning</v>
       </c>
       <c r="V14" t="str">
         <v>SW Bins</v>
@@ -7029,7 +6775,7 @@
         <v>Object Store (SW bins)</v>
       </c>
       <c r="X14" t="str">
-        <v>Resource Recovery</v>
+        <v>Resource: Release and Recovery</v>
       </c>
       <c r="Y14" t="str">
         <v>On-Premise SW/Appliance</v>
@@ -7056,7 +6802,7 @@
         <v>Automated By App</v>
       </c>
       <c r="AG14" t="str">
-        <v xml:space="preserve">Seconds </v>
+        <v>Minutes (1-5)</v>
       </c>
       <c r="AH14" t="str">
         <v xml:space="preserve">Seconds </v>
@@ -7065,7 +6811,7 @@
         <v>SW Integrator</v>
       </c>
       <c r="AJ14" t="str">
-        <v>Streaming Replication</v>
+        <v>Backup, Tuning, PITR, WAL</v>
       </c>
       <c r="AK14" t="str">
         <v>Public Cloud Consumption</v>
@@ -7074,9 +6820,380 @@
         <v>Seeweb VPC</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>PROD</v>
+      </c>
+      <c r="B15" t="str">
+        <v>99,9%</v>
+      </c>
+      <c r="C15" t="str">
+        <v>HA</v>
+      </c>
+      <c r="D15" t="str">
+        <v>DATABASE</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Not W3 Private datacenter</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Vendor Private</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Full IaaS</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Seeweb S.r.l. - PostgreSQL Replica</v>
+      </c>
+      <c r="I15" t="str">
+        <v>App (RunTime) - Linux native</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Cloud-Single-zone</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Resources - SW configuration</v>
+      </c>
+      <c r="M15" t="str">
+        <v>Standby</v>
+      </c>
+      <c r="N15" t="str">
+        <v>Ops Manual</v>
+      </c>
+      <c r="O15" t="str">
+        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
+      </c>
+      <c r="P15" t="str">
+        <v>No outages</v>
+      </c>
+      <c r="Q15" t="str">
+        <v>Ops - Manual</v>
+      </c>
+      <c r="R15" t="str">
+        <v>Ops Manual - direct Log-on resource</v>
+      </c>
+      <c r="S15" t="str">
+        <v>No outages</v>
+      </c>
+      <c r="T15" t="str">
+        <v>Configuration File (TXT)</v>
+      </c>
+      <c r="U15" t="str">
+        <v>Vendor Versioning</v>
+      </c>
+      <c r="V15" t="str">
+        <v>SW Bins</v>
+      </c>
+      <c r="W15" t="str">
+        <v>Object Store (SW bins)</v>
+      </c>
+      <c r="X15" t="str">
+        <v>Resource Recovery</v>
+      </c>
+      <c r="Y15" t="str">
+        <v>On-Premise SW/Appliance</v>
+      </c>
+      <c r="Z15" t="str">
+        <v>On-premise Store (Appliance)</v>
+      </c>
+      <c r="AA15" t="str">
+        <v>Daily</v>
+      </c>
+      <c r="AB15" t="str">
+        <v>1 month</v>
+      </c>
+      <c r="AC15" t="str">
+        <v>1 min</v>
+      </c>
+      <c r="AD15" t="str">
+        <v>1 week</v>
+      </c>
+      <c r="AE15" t="str">
+        <v xml:space="preserve">Region Resilent </v>
+      </c>
+      <c r="AF15" t="str">
+        <v>Automated By App</v>
+      </c>
+      <c r="AG15" t="str">
+        <v xml:space="preserve">Seconds </v>
+      </c>
+      <c r="AH15" t="str">
+        <v xml:space="preserve">Seconds </v>
+      </c>
+      <c r="AI15" t="str">
+        <v>SW Integrator</v>
+      </c>
+      <c r="AJ15" t="str">
+        <v>Streaming Replication, Failover</v>
+      </c>
+      <c r="AK15" t="str">
+        <v>Public Cloud Consumption</v>
+      </c>
+      <c r="AL15" t="str">
+        <v>Seeweb VPC</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A4:AL14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AL15"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A2:G15"/>
+  <cols>
+    <col min="1" max="1" width="25.83203125" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="4" width="25.83203125" customWidth="1"/>
+    <col min="5" max="5" width="25.83203125" customWidth="1"/>
+    <col min="6" max="6" width="25.83203125" customWidth="1"/>
+    <col min="7" max="7" width="25.83203125" customWidth="1"/>
+    <col min="8" max="8" width="25.83203125" customWidth="1"/>
+    <col min="9" max="9" width="25.83203125" customWidth="1"/>
+    <col min="10" max="10" width="25.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Public Cloud Zones or W3 Sites</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Field Definition &amp; Values 
+Module of solution</v>
+      </c>
+      <c r="B3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Field Definition &amp; Values 
+Resource of module</v>
+      </c>
+      <c r="C3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Field Definition &amp; Values
+Resource component</v>
+      </c>
+      <c r="D3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Field Definition &amp; Values
+Sites List</v>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>Module</v>
+      </c>
+      <c r="B7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Service
+Resources</v>
+      </c>
+      <c r="C7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Resource 
+Component (if needed)</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Region (Zone/site)</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Zone/site</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Zone/site</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Zone/site</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v/>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v>Seeweb Italy DC1</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Seeweb Italy DC2</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>INFRASTRUCTURE</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Proxmox VE Cluster</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Multinodo Cluster</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Seeweb DC1 (Primary)</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>INFRASTRUCTURE</v>
+      </c>
+      <c r="B10" t="str">
+        <v>FortiGate NGFW</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Single Appliance</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Seeweb DC1</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>INFRASTRUCTURE</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Proxmox Backup Server</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Dedicated Server</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v>Seeweb DC2 (DR)</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>APPLICATION</v>
+      </c>
+      <c r="B12" t="str">
+        <v>W3Suite Frontend</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Nginx + LB</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Seeweb DC1</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>APPLICATION</v>
+      </c>
+      <c r="B13" t="str">
+        <v>W3Suite Backend</v>
+      </c>
+      <c r="C13" t="str">
+        <v>API + Redis + MCP</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Seeweb DC1</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>DATABASE</v>
+      </c>
+      <c r="B14" t="str">
+        <v>PostgreSQL Primary</v>
+      </c>
+      <c r="C14" t="str">
+        <v>DB Primary</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Seeweb DC1</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>DATABASE</v>
+      </c>
+      <c r="B15" t="str">
+        <v>PostgreSQL Replica</v>
+      </c>
+      <c r="C15" t="str">
+        <v>DB Standby</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Seeweb DC1</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A2:G15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/gara-appalto/SERVICE-RESOURCE-MODEL-W3SUITE-FINAL.xlsx
+++ b/docs/gara-appalto/SERVICE-RESOURCE-MODEL-W3SUITE-FINAL.xlsx
@@ -5778,6 +5778,1175 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AL15"/>
   <cols>
+    <col min="1" max="1" width="24.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="24.83203125" customWidth="1"/>
+    <col min="4" max="4" width="24.83203125" customWidth="1"/>
+    <col min="5" max="5" width="24.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
+    <col min="7" max="7" width="24.83203125" customWidth="1"/>
+    <col min="8" max="8" width="24.83203125" customWidth="1"/>
+    <col min="9" max="9" width="24.83203125" customWidth="1"/>
+    <col min="10" max="10" width="24.83203125" customWidth="1"/>
+    <col min="11" max="11" width="24.83203125" customWidth="1"/>
+    <col min="12" max="12" width="24.83203125" customWidth="1"/>
+    <col min="13" max="13" width="24.83203125" customWidth="1"/>
+    <col min="14" max="14" width="24.83203125" customWidth="1"/>
+    <col min="15" max="15" width="24.83203125" customWidth="1"/>
+    <col min="16" max="16" width="24.83203125" customWidth="1"/>
+    <col min="17" max="17" width="24.83203125" customWidth="1"/>
+    <col min="18" max="18" width="24.83203125" customWidth="1"/>
+    <col min="19" max="19" width="24.83203125" customWidth="1"/>
+    <col min="20" max="20" width="24.83203125" customWidth="1"/>
+    <col min="21" max="21" width="24.83203125" customWidth="1"/>
+    <col min="22" max="22" width="24.83203125" customWidth="1"/>
+    <col min="23" max="23" width="24.83203125" customWidth="1"/>
+    <col min="24" max="24" width="24.83203125" customWidth="1"/>
+    <col min="25" max="25" width="24.83203125" customWidth="1"/>
+    <col min="26" max="26" width="24.83203125" customWidth="1"/>
+    <col min="27" max="27" width="24.83203125" customWidth="1"/>
+    <col min="28" max="28" width="24.83203125" customWidth="1"/>
+    <col min="29" max="29" width="24.83203125" customWidth="1"/>
+    <col min="30" max="30" width="24.83203125" customWidth="1"/>
+    <col min="31" max="31" width="24.83203125" customWidth="1"/>
+    <col min="32" max="32" width="24.83203125" customWidth="1"/>
+    <col min="33" max="33" width="24.83203125" customWidth="1"/>
+    <col min="34" max="34" width="24.83203125" customWidth="1"/>
+    <col min="35" max="35" width="24.83203125" customWidth="1"/>
+    <col min="36" max="36" width="24.83203125" customWidth="1"/>
+    <col min="37" max="37" width="24.83203125" customWidth="1"/>
+    <col min="38" max="38" width="24.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>W3Suite - Service Resource Model - Seeweb Infrastructure</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Environment</v>
+      </c>
+      <c r="B5" t="str">
+        <v>SLA Model &amp; Resource Model</v>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v>Capacity  Model</v>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v xml:space="preserve">SLA </v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>Resource Model</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v>Resource Distribution Model &amp; HA</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v>Capacity Model</v>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v>Release Method</v>
+      </c>
+      <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
+      <c r="T7" t="str">
+        <v>Release Configuration  &amp; Artifacts</v>
+      </c>
+      <c r="U7" t="str">
+        <v/>
+      </c>
+      <c r="V7" t="str">
+        <v/>
+      </c>
+      <c r="W7" t="str">
+        <v/>
+      </c>
+      <c r="X7" t="str">
+        <v>Use for and Method &amp; store</v>
+      </c>
+      <c r="Y7" t="str">
+        <v/>
+      </c>
+      <c r="Z7" t="str">
+        <v/>
+      </c>
+      <c r="AA7" t="str">
+        <v>Full</v>
+      </c>
+      <c r="AB7" t="str">
+        <v/>
+      </c>
+      <c r="AC7" t="str">
+        <v>Incremental (log)</v>
+      </c>
+      <c r="AD7" t="str">
+        <v/>
+      </c>
+      <c r="AE7" t="str">
+        <v>Fail-over/Fail-Back (recover full capacity)</v>
+      </c>
+      <c r="AF7" t="str">
+        <v/>
+      </c>
+      <c r="AG7" t="str">
+        <v/>
+      </c>
+      <c r="AH7" t="str">
+        <v/>
+      </c>
+      <c r="AI7" t="str">
+        <v>Operation Model</v>
+      </c>
+      <c r="AJ7" t="str">
+        <v/>
+      </c>
+      <c r="AK7" t="str">
+        <v>Cost Model</v>
+      </c>
+      <c r="AL7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str">
+        <v>ENV</v>
+      </c>
+      <c r="B8" t="str" xml:space="preserve">
+        <v xml:space="preserve">SLA
+Value</v>
+      </c>
+      <c r="C8" t="str" xml:space="preserve">
+        <v xml:space="preserve">SLA
+Class</v>
+      </c>
+      <c r="D8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Proposal
+ Modules</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Hosting Model</v>
+      </c>
+      <c r="F8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hosting 
+Provider</v>
+      </c>
+      <c r="G8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Technical Model
+Module</v>
+      </c>
+      <c r="H8" t="str" xml:space="preserve">
+        <v xml:space="preserve"> Service  Resource 
+Vendor Name (Relations)</v>
+      </c>
+      <c r="I8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Service Resources 
+Implementation</v>
+      </c>
+      <c r="J8" t="str">
+        <v># instances</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Region/Zone Distribution</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Distribution Method</v>
+      </c>
+      <c r="M8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Resource Role
+Distribution</v>
+      </c>
+      <c r="N8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Capacity
+Class</v>
+      </c>
+      <c r="O8" t="str">
+        <v>Method</v>
+      </c>
+      <c r="P8" t="str">
+        <v>Outages</v>
+      </c>
+      <c r="Q8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Release
+Class</v>
+      </c>
+      <c r="R8" t="str">
+        <v>Method</v>
+      </c>
+      <c r="S8" t="str">
+        <v>Outages</v>
+      </c>
+      <c r="T8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Configuration
+Specification</v>
+      </c>
+      <c r="U8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Configuration
+Version</v>
+      </c>
+      <c r="V8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Deploy
+Artifact
+</v>
+      </c>
+      <c r="W8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Artifact 
+Registry</v>
+      </c>
+      <c r="X8" t="str">
+        <v>Use for</v>
+      </c>
+      <c r="Y8" t="str">
+        <v>Method</v>
+      </c>
+      <c r="Z8" t="str">
+        <v>Store</v>
+      </c>
+      <c r="AA8" t="str">
+        <v>Freq.</v>
+      </c>
+      <c r="AB8" t="str">
+        <v>Retention</v>
+      </c>
+      <c r="AC8" t="str">
+        <v>Freq.</v>
+      </c>
+      <c r="AD8" t="str">
+        <v>Retention</v>
+      </c>
+      <c r="AE8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Recovery 
+Class</v>
+      </c>
+      <c r="AF8" t="str">
+        <v>Method</v>
+      </c>
+      <c r="AG8" t="str">
+        <v>RTO</v>
+      </c>
+      <c r="AH8" t="str">
+        <v>RPO</v>
+      </c>
+      <c r="AI8" t="str">
+        <v>Operated By</v>
+      </c>
+      <c r="AJ8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Operation other Activities
+(which  W3 activities)</v>
+      </c>
+      <c r="AK8" t="str">
+        <v>Model</v>
+      </c>
+      <c r="AL8" t="str">
+        <v>Details</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>PROD</v>
+      </c>
+      <c r="B9" t="str">
+        <v>99,9%</v>
+      </c>
+      <c r="C9" t="str">
+        <v>HA</v>
+      </c>
+      <c r="D9" t="str">
+        <v>INFRASTRUCTURE</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Not W3 Private datacenter</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Vendor Private</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Full IaaS</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Seeweb S.r.l. - Proxmox VE Cluster</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Virtualization Platform - ProxMox</v>
+      </c>
+      <c r="J9" t="str">
+        <v>3+ nodi</v>
+      </c>
+      <c r="K9" t="str">
+        <v xml:space="preserve">Cloud-Multi-region </v>
+      </c>
+      <c r="L9" t="str">
+        <v>Resources - SW configuration</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Active</v>
+      </c>
+      <c r="N9" t="str">
+        <v>Ops Manual</v>
+      </c>
+      <c r="O9" t="str">
+        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
+      </c>
+      <c r="P9" t="str">
+        <v>No outages</v>
+      </c>
+      <c r="Q9" t="str">
+        <v>Ops - Manual</v>
+      </c>
+      <c r="R9" t="str">
+        <v>Ops Manual - direct Log-on resource</v>
+      </c>
+      <c r="S9" t="str">
+        <v>No outages</v>
+      </c>
+      <c r="T9" t="str">
+        <v>Configuration File (TXT)</v>
+      </c>
+      <c r="U9" t="str">
+        <v>Vendor Versioning</v>
+      </c>
+      <c r="V9" t="str">
+        <v>VMI (Virtual Machine Image) - KVM</v>
+      </c>
+      <c r="W9" t="str">
+        <v>Private Others Registry</v>
+      </c>
+      <c r="X9" t="str">
+        <v>Resource Recovery</v>
+      </c>
+      <c r="Y9" t="str">
+        <v>On-Premise SW/Appliance</v>
+      </c>
+      <c r="Z9" t="str">
+        <v>On-premise Store (Appliance)</v>
+      </c>
+      <c r="AA9" t="str">
+        <v>Daily</v>
+      </c>
+      <c r="AB9" t="str">
+        <v>1 month</v>
+      </c>
+      <c r="AC9" t="str">
+        <v>1 min</v>
+      </c>
+      <c r="AD9" t="str">
+        <v>1 week</v>
+      </c>
+      <c r="AE9" t="str">
+        <v xml:space="preserve">Region Resilent </v>
+      </c>
+      <c r="AF9" t="str">
+        <v>Automated By App</v>
+      </c>
+      <c r="AG9" t="str">
+        <v>Minutes (1-5)</v>
+      </c>
+      <c r="AH9" t="str">
+        <v>Minutes (1-5)</v>
+      </c>
+      <c r="AI9" t="str">
+        <v>HW/SW vendor</v>
+      </c>
+      <c r="AJ9" t="str">
+        <v>Cluster Management, VM Provisioning, HA</v>
+      </c>
+      <c r="AK9" t="str">
+        <v>Public Cloud Consumption</v>
+      </c>
+      <c r="AL9" t="str">
+        <v>Seeweb Multinodo Contract</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>PROD</v>
+      </c>
+      <c r="B10" t="str">
+        <v>99,5%</v>
+      </c>
+      <c r="C10" t="str">
+        <v>HA-</v>
+      </c>
+      <c r="D10" t="str">
+        <v>INFRASTRUCTURE</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Not W3 Private datacenter</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Vendor Private</v>
+      </c>
+      <c r="G10" t="str">
+        <v>HW Appliance</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Seeweb S.r.l. - Fortinet FortiGate</v>
+      </c>
+      <c r="I10" t="str">
+        <v>HW Appliance - FortiGate NGFW</v>
+      </c>
+      <c r="J10" t="str">
+        <v>1 (Single)</v>
+      </c>
+      <c r="K10" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Resource - Manual Installation</v>
+      </c>
+      <c r="M10" t="str">
+        <v>Active</v>
+      </c>
+      <c r="N10" t="str">
+        <v>Fixed capacity</v>
+      </c>
+      <c r="O10" t="str">
+        <v>Do not scale - Fixed capacity</v>
+      </c>
+      <c r="P10" t="str">
+        <v>No outages</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>Ops - Manual</v>
+      </c>
+      <c r="R10" t="str">
+        <v>Ops Manual - direct Log-on resource</v>
+      </c>
+      <c r="S10" t="str">
+        <v>Hours (1-5)</v>
+      </c>
+      <c r="T10" t="str">
+        <v>Configuration File (TXT)</v>
+      </c>
+      <c r="U10" t="str">
+        <v>Vendor Versioning</v>
+      </c>
+      <c r="V10" t="str">
+        <v>SW Bins</v>
+      </c>
+      <c r="W10" t="str">
+        <v>Private Others Registry</v>
+      </c>
+      <c r="X10" t="str">
+        <v>Resource Recovery</v>
+      </c>
+      <c r="Y10" t="str">
+        <v>On-Premise SW/Appliance</v>
+      </c>
+      <c r="Z10" t="str">
+        <v>On-premise Store (Appliance)</v>
+      </c>
+      <c r="AA10" t="str">
+        <v>Daily</v>
+      </c>
+      <c r="AB10" t="str">
+        <v>1 month</v>
+      </c>
+      <c r="AC10" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AD10" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AE10" t="str">
+        <v xml:space="preserve">Local Resilent </v>
+      </c>
+      <c r="AF10" t="str">
+        <v>Manual By Operation</v>
+      </c>
+      <c r="AG10" t="str">
+        <v>Hour (1-5)</v>
+      </c>
+      <c r="AH10" t="str">
+        <v>Hour (1-5)</v>
+      </c>
+      <c r="AI10" t="str">
+        <v>HW/SW vendor</v>
+      </c>
+      <c r="AJ10" t="str">
+        <v>Security Policy, Threat Monitoring, FW Rules</v>
+      </c>
+      <c r="AK10" t="str">
+        <v>(on-premise) HW Buy &amp; Support</v>
+      </c>
+      <c r="AL10" t="str">
+        <v>FortiGate HW + FortiCare Support</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>PROD</v>
+      </c>
+      <c r="B11" t="str">
+        <v>99,9%</v>
+      </c>
+      <c r="C11" t="str">
+        <v>HA</v>
+      </c>
+      <c r="D11" t="str">
+        <v>INFRASTRUCTURE</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Not W3 Private datacenter</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Vendor Private</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Bare Metal</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Seeweb S.r.l. - Proxmox Backup Server</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Bare Metal - PBS Dedicated</v>
+      </c>
+      <c r="J11" t="str">
+        <v>1 (Dedicato)</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Cloud-Single-zone</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Resources - SW configuration</v>
+      </c>
+      <c r="M11" t="str">
+        <v>Active</v>
+      </c>
+      <c r="N11" t="str">
+        <v>Ops Manual</v>
+      </c>
+      <c r="O11" t="str">
+        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
+      </c>
+      <c r="P11" t="str">
+        <v>No outages</v>
+      </c>
+      <c r="Q11" t="str">
+        <v>Ops - Manual</v>
+      </c>
+      <c r="R11" t="str">
+        <v>Ops Manual - direct Log-on resource</v>
+      </c>
+      <c r="S11" t="str">
+        <v>No outages</v>
+      </c>
+      <c r="T11" t="str">
+        <v>Configuration File (TXT)</v>
+      </c>
+      <c r="U11" t="str">
+        <v>Vendor Versioning</v>
+      </c>
+      <c r="V11" t="str">
+        <v>SW Bins</v>
+      </c>
+      <c r="W11" t="str">
+        <v>Object Store (SW bins)</v>
+      </c>
+      <c r="X11" t="str">
+        <v>Resource Recovery</v>
+      </c>
+      <c r="Y11" t="str">
+        <v>On-Premise SW/Appliance</v>
+      </c>
+      <c r="Z11" t="str">
+        <v>On-premise Store (Appliance)</v>
+      </c>
+      <c r="AA11" t="str">
+        <v>Daily</v>
+      </c>
+      <c r="AB11" t="str">
+        <v>1 month</v>
+      </c>
+      <c r="AC11" t="str">
+        <v>1 min</v>
+      </c>
+      <c r="AD11" t="str">
+        <v>1 week</v>
+      </c>
+      <c r="AE11" t="str">
+        <v xml:space="preserve">Region Resilent </v>
+      </c>
+      <c r="AF11" t="str">
+        <v>Manual By Operation</v>
+      </c>
+      <c r="AG11" t="str">
+        <v>Hour (1-5)</v>
+      </c>
+      <c r="AH11" t="str">
+        <v>Minutes (1-5)</v>
+      </c>
+      <c r="AI11" t="str">
+        <v>HW/SW vendor</v>
+      </c>
+      <c r="AJ11" t="str">
+        <v>Backup Storage, DR Recovery, Retention</v>
+      </c>
+      <c r="AK11" t="str">
+        <v>Public Cloud Consumption</v>
+      </c>
+      <c r="AL11" t="str">
+        <v>Seeweb PBS Service</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>PROD</v>
+      </c>
+      <c r="B12" t="str">
+        <v>99,9%</v>
+      </c>
+      <c r="C12" t="str">
+        <v>HA</v>
+      </c>
+      <c r="D12" t="str">
+        <v>APPLICATION</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Not W3 Private datacenter</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Vendor Private</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Full IaaS</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Seeweb S.r.l. - W3Suite Frontend</v>
+      </c>
+      <c r="I12" t="str">
+        <v>App (RunTime) - Linux native</v>
+      </c>
+      <c r="J12" t="str">
+        <v>1 VPC</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Cloud-Single-zone</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Resources - SW configuration</v>
+      </c>
+      <c r="M12" t="str">
+        <v>Active</v>
+      </c>
+      <c r="N12" t="str">
+        <v>Ops Manual</v>
+      </c>
+      <c r="O12" t="str">
+        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
+      </c>
+      <c r="P12" t="str">
+        <v>No outages</v>
+      </c>
+      <c r="Q12" t="str">
+        <v>Ops - Automated</v>
+      </c>
+      <c r="R12" t="str">
+        <v xml:space="preserve">Ops Automated (SW) - DevOps </v>
+      </c>
+      <c r="S12" t="str">
+        <v>No outages</v>
+      </c>
+      <c r="T12" t="str">
+        <v>Configuration File (YAML)</v>
+      </c>
+      <c r="U12" t="str">
+        <v>W3 Git</v>
+      </c>
+      <c r="V12" t="str">
+        <v>SW Bins</v>
+      </c>
+      <c r="W12" t="str">
+        <v>Object Store (SW bins)</v>
+      </c>
+      <c r="X12" t="str">
+        <v>Resource Recovery</v>
+      </c>
+      <c r="Y12" t="str">
+        <v>On-Premise SW/Appliance</v>
+      </c>
+      <c r="Z12" t="str">
+        <v>On-premise Store (Appliance)</v>
+      </c>
+      <c r="AA12" t="str">
+        <v>Daily</v>
+      </c>
+      <c r="AB12" t="str">
+        <v>1 month</v>
+      </c>
+      <c r="AC12" t="str">
+        <v>1 min</v>
+      </c>
+      <c r="AD12" t="str">
+        <v>1 week</v>
+      </c>
+      <c r="AE12" t="str">
+        <v xml:space="preserve">Region Resilent </v>
+      </c>
+      <c r="AF12" t="str">
+        <v>Automated By App</v>
+      </c>
+      <c r="AG12" t="str">
+        <v xml:space="preserve">Seconds </v>
+      </c>
+      <c r="AH12" t="str">
+        <v xml:space="preserve">Seconds </v>
+      </c>
+      <c r="AI12" t="str">
+        <v>SW Integrator</v>
+      </c>
+      <c r="AJ12" t="str">
+        <v>TLS, Routing, LB Config, CDN</v>
+      </c>
+      <c r="AK12" t="str">
+        <v>Public Cloud Consumption</v>
+      </c>
+      <c r="AL12" t="str">
+        <v>Seeweb VPC</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>PROD</v>
+      </c>
+      <c r="B13" t="str">
+        <v>99,9%</v>
+      </c>
+      <c r="C13" t="str">
+        <v>HA</v>
+      </c>
+      <c r="D13" t="str">
+        <v>APPLICATION</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Not W3 Private datacenter</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Vendor Private</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Full IaaS</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Seeweb S.r.l. - W3Suite Backend</v>
+      </c>
+      <c r="I13" t="str">
+        <v>App (RunTime) - Linux native</v>
+      </c>
+      <c r="J13" t="str">
+        <v>1 VPC</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Cloud-Single-zone</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Resources - SW configuration</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Active</v>
+      </c>
+      <c r="N13" t="str">
+        <v>Ops Manual</v>
+      </c>
+      <c r="O13" t="str">
+        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
+      </c>
+      <c r="P13" t="str">
+        <v>No outages</v>
+      </c>
+      <c r="Q13" t="str">
+        <v>Ops - Automated</v>
+      </c>
+      <c r="R13" t="str">
+        <v xml:space="preserve">Ops Automated (SW) - DevOps </v>
+      </c>
+      <c r="S13" t="str">
+        <v>No outages</v>
+      </c>
+      <c r="T13" t="str">
+        <v>Configuration File (YAML)</v>
+      </c>
+      <c r="U13" t="str">
+        <v>W3 Git</v>
+      </c>
+      <c r="V13" t="str">
+        <v>SW Bins</v>
+      </c>
+      <c r="W13" t="str">
+        <v>Object Store (SW bins)</v>
+      </c>
+      <c r="X13" t="str">
+        <v>Resource Recovery</v>
+      </c>
+      <c r="Y13" t="str">
+        <v>On-Premise SW/Appliance</v>
+      </c>
+      <c r="Z13" t="str">
+        <v>On-premise Store (Appliance)</v>
+      </c>
+      <c r="AA13" t="str">
+        <v>Daily</v>
+      </c>
+      <c r="AB13" t="str">
+        <v>1 month</v>
+      </c>
+      <c r="AC13" t="str">
+        <v>1 min</v>
+      </c>
+      <c r="AD13" t="str">
+        <v>1 week</v>
+      </c>
+      <c r="AE13" t="str">
+        <v xml:space="preserve">Region Resilent </v>
+      </c>
+      <c r="AF13" t="str">
+        <v>Automated By App</v>
+      </c>
+      <c r="AG13" t="str">
+        <v>Minutes (1-5)</v>
+      </c>
+      <c r="AH13" t="str">
+        <v xml:space="preserve">Seconds </v>
+      </c>
+      <c r="AI13" t="str">
+        <v>SW Integrator</v>
+      </c>
+      <c r="AJ13" t="str">
+        <v>Deploy, API, AI Gateway, Redis Cache</v>
+      </c>
+      <c r="AK13" t="str">
+        <v>Public Cloud Consumption</v>
+      </c>
+      <c r="AL13" t="str">
+        <v>Seeweb VPC</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>PROD</v>
+      </c>
+      <c r="B14" t="str">
+        <v>99,9%</v>
+      </c>
+      <c r="C14" t="str">
+        <v>HA+</v>
+      </c>
+      <c r="D14" t="str">
+        <v>DATABASE</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Not W3 Private datacenter</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Vendor Private</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Full IaaS</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Seeweb S.r.l. - PostgreSQL Primary</v>
+      </c>
+      <c r="I14" t="str">
+        <v>App (RunTime) - Linux native</v>
+      </c>
+      <c r="J14" t="str">
+        <v>1 VPC</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Cloud-Single-zone</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Resources - SW configuration</v>
+      </c>
+      <c r="M14" t="str">
+        <v xml:space="preserve">Active+ </v>
+      </c>
+      <c r="N14" t="str">
+        <v>Ops Manual</v>
+      </c>
+      <c r="O14" t="str">
+        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
+      </c>
+      <c r="P14" t="str">
+        <v>Minutes (1-10)</v>
+      </c>
+      <c r="Q14" t="str">
+        <v>Ops - Manual</v>
+      </c>
+      <c r="R14" t="str">
+        <v>Ops Manual - direct Log-on resource</v>
+      </c>
+      <c r="S14" t="str">
+        <v>Minutes (1-10)</v>
+      </c>
+      <c r="T14" t="str">
+        <v>Configuration File (TXT)</v>
+      </c>
+      <c r="U14" t="str">
+        <v>Vendor Versioning</v>
+      </c>
+      <c r="V14" t="str">
+        <v>SW Bins</v>
+      </c>
+      <c r="W14" t="str">
+        <v>Object Store (SW bins)</v>
+      </c>
+      <c r="X14" t="str">
+        <v>Resource: Release and Recovery</v>
+      </c>
+      <c r="Y14" t="str">
+        <v>On-Premise SW/Appliance</v>
+      </c>
+      <c r="Z14" t="str">
+        <v>On-premise Store (Appliance)</v>
+      </c>
+      <c r="AA14" t="str">
+        <v>Daily</v>
+      </c>
+      <c r="AB14" t="str">
+        <v>1 month</v>
+      </c>
+      <c r="AC14" t="str">
+        <v>1 min</v>
+      </c>
+      <c r="AD14" t="str">
+        <v>1 week</v>
+      </c>
+      <c r="AE14" t="str">
+        <v xml:space="preserve">Region Resilent </v>
+      </c>
+      <c r="AF14" t="str">
+        <v>Automated By App</v>
+      </c>
+      <c r="AG14" t="str">
+        <v>Minutes (1-5)</v>
+      </c>
+      <c r="AH14" t="str">
+        <v xml:space="preserve">Seconds </v>
+      </c>
+      <c r="AI14" t="str">
+        <v>SW Integrator</v>
+      </c>
+      <c r="AJ14" t="str">
+        <v>Backup, Tuning, PITR, WAL Shipping</v>
+      </c>
+      <c r="AK14" t="str">
+        <v>Public Cloud Consumption</v>
+      </c>
+      <c r="AL14" t="str">
+        <v>Seeweb VPC</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>PROD</v>
+      </c>
+      <c r="B15" t="str">
+        <v>99,9%</v>
+      </c>
+      <c r="C15" t="str">
+        <v>HA</v>
+      </c>
+      <c r="D15" t="str">
+        <v>DATABASE</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Not W3 Private datacenter</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Vendor Private</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Full IaaS</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Seeweb S.r.l. - PostgreSQL Replica</v>
+      </c>
+      <c r="I15" t="str">
+        <v>App (RunTime) - Linux native</v>
+      </c>
+      <c r="J15" t="str">
+        <v>1 VPC</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Cloud-Single-zone</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Resources - SW configuration</v>
+      </c>
+      <c r="M15" t="str">
+        <v>Standby</v>
+      </c>
+      <c r="N15" t="str">
+        <v>Ops Manual</v>
+      </c>
+      <c r="O15" t="str">
+        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
+      </c>
+      <c r="P15" t="str">
+        <v>No outages</v>
+      </c>
+      <c r="Q15" t="str">
+        <v>Ops - Manual</v>
+      </c>
+      <c r="R15" t="str">
+        <v>Ops Manual - direct Log-on resource</v>
+      </c>
+      <c r="S15" t="str">
+        <v>No outages</v>
+      </c>
+      <c r="T15" t="str">
+        <v>Configuration File (TXT)</v>
+      </c>
+      <c r="U15" t="str">
+        <v>Vendor Versioning</v>
+      </c>
+      <c r="V15" t="str">
+        <v>SW Bins</v>
+      </c>
+      <c r="W15" t="str">
+        <v>Object Store (SW bins)</v>
+      </c>
+      <c r="X15" t="str">
+        <v>Resource Recovery</v>
+      </c>
+      <c r="Y15" t="str">
+        <v>On-Premise SW/Appliance</v>
+      </c>
+      <c r="Z15" t="str">
+        <v>On-premise Store (Appliance)</v>
+      </c>
+      <c r="AA15" t="str">
+        <v>Daily</v>
+      </c>
+      <c r="AB15" t="str">
+        <v>1 month</v>
+      </c>
+      <c r="AC15" t="str">
+        <v>1 min</v>
+      </c>
+      <c r="AD15" t="str">
+        <v>1 week</v>
+      </c>
+      <c r="AE15" t="str">
+        <v xml:space="preserve">Region Resilent </v>
+      </c>
+      <c r="AF15" t="str">
+        <v>Automated By App</v>
+      </c>
+      <c r="AG15" t="str">
+        <v xml:space="preserve">Seconds </v>
+      </c>
+      <c r="AH15" t="str">
+        <v xml:space="preserve">Seconds </v>
+      </c>
+      <c r="AI15" t="str">
+        <v>SW Integrator</v>
+      </c>
+      <c r="AJ15" t="str">
+        <v>Streaming Replication, Failover Ready</v>
+      </c>
+      <c r="AK15" t="str">
+        <v>Public Cloud Consumption</v>
+      </c>
+      <c r="AL15" t="str">
+        <v>Seeweb VPC</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:AL15"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A2:G17"/>
+  <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
     <col min="3" max="3" width="22.83203125" customWidth="1"/>
@@ -5788,1198 +6957,11 @@
     <col min="8" max="8" width="22.83203125" customWidth="1"/>
     <col min="9" max="9" width="22.83203125" customWidth="1"/>
     <col min="10" max="10" width="22.83203125" customWidth="1"/>
-    <col min="11" max="11" width="22.83203125" customWidth="1"/>
-    <col min="12" max="12" width="22.83203125" customWidth="1"/>
-    <col min="13" max="13" width="22.83203125" customWidth="1"/>
-    <col min="14" max="14" width="22.83203125" customWidth="1"/>
-    <col min="15" max="15" width="22.83203125" customWidth="1"/>
-    <col min="16" max="16" width="22.83203125" customWidth="1"/>
-    <col min="17" max="17" width="22.83203125" customWidth="1"/>
-    <col min="18" max="18" width="22.83203125" customWidth="1"/>
-    <col min="19" max="19" width="22.83203125" customWidth="1"/>
-    <col min="20" max="20" width="22.83203125" customWidth="1"/>
-    <col min="21" max="21" width="22.83203125" customWidth="1"/>
-    <col min="22" max="22" width="22.83203125" customWidth="1"/>
-    <col min="23" max="23" width="22.83203125" customWidth="1"/>
-    <col min="24" max="24" width="22.83203125" customWidth="1"/>
-    <col min="25" max="25" width="22.83203125" customWidth="1"/>
-    <col min="26" max="26" width="22.83203125" customWidth="1"/>
-    <col min="27" max="27" width="22.83203125" customWidth="1"/>
-    <col min="28" max="28" width="22.83203125" customWidth="1"/>
-    <col min="29" max="29" width="22.83203125" customWidth="1"/>
-    <col min="30" max="30" width="22.83203125" customWidth="1"/>
-    <col min="31" max="31" width="22.83203125" customWidth="1"/>
-    <col min="32" max="32" width="22.83203125" customWidth="1"/>
-    <col min="33" max="33" width="22.83203125" customWidth="1"/>
-    <col min="34" max="34" width="22.83203125" customWidth="1"/>
-    <col min="35" max="35" width="22.83203125" customWidth="1"/>
-    <col min="36" max="36" width="22.83203125" customWidth="1"/>
-    <col min="37" max="37" width="22.83203125" customWidth="1"/>
-    <col min="38" max="38" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>HERE YOU CAN FIND SOME NOTES TO HELP YOU UNDERSTAND HOW TO FILL IN THIS FORM. YOU CAN FIND THE COMPLETE VALUES LIST AND RELATED DESCRIPTION ON TAB "Values&amp;Description"</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Environment</v>
-      </c>
-      <c r="B5" t="str">
-        <v>SLA Model &amp; Resource Model</v>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
-        <v/>
-      </c>
-      <c r="N5" t="str">
-        <v>Capacity  Model</v>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v/>
-      </c>
-      <c r="B7" t="str">
-        <v xml:space="preserve">SLA </v>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v>Resource Model</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v/>
-      </c>
-      <c r="J7" t="str">
-        <v>Resource Distribution Model &amp; HA</v>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
-        <v/>
-      </c>
-      <c r="N7" t="str">
-        <v>Capacity Model</v>
-      </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7" t="str">
-        <v/>
-      </c>
-      <c r="Q7" t="str">
-        <v>Release Method</v>
-      </c>
-      <c r="R7" t="str">
-        <v/>
-      </c>
-      <c r="S7" t="str">
-        <v/>
-      </c>
-      <c r="T7" t="str">
-        <v>Release Configuration  &amp; Artifacts</v>
-      </c>
-      <c r="U7" t="str">
-        <v/>
-      </c>
-      <c r="V7" t="str">
-        <v/>
-      </c>
-      <c r="W7" t="str">
-        <v/>
-      </c>
-      <c r="X7" t="str">
-        <v>Use for and Method &amp; store</v>
-      </c>
-      <c r="Y7" t="str">
-        <v/>
-      </c>
-      <c r="Z7" t="str">
-        <v/>
-      </c>
-      <c r="AA7" t="str">
-        <v>Full</v>
-      </c>
-      <c r="AB7" t="str">
-        <v/>
-      </c>
-      <c r="AC7" t="str">
-        <v>Incremental (log)</v>
-      </c>
-      <c r="AD7" t="str">
-        <v/>
-      </c>
-      <c r="AE7" t="str">
-        <v>Fail-over/Fail-Back (recover full capacity)</v>
-      </c>
-      <c r="AF7" t="str">
-        <v/>
-      </c>
-      <c r="AG7" t="str">
-        <v/>
-      </c>
-      <c r="AH7" t="str">
-        <v/>
-      </c>
-      <c r="AI7" t="str">
-        <v>Operation Model</v>
-      </c>
-      <c r="AJ7" t="str">
-        <v/>
-      </c>
-      <c r="AK7" t="str">
-        <v>Cost Model</v>
-      </c>
-      <c r="AL7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8" xml:space="preserve">
-      <c r="A8" t="str">
-        <v>ENV</v>
-      </c>
-      <c r="B8" t="str" xml:space="preserve">
-        <v xml:space="preserve">SLA
-Value</v>
-      </c>
-      <c r="C8" t="str" xml:space="preserve">
-        <v xml:space="preserve">SLA
-Class</v>
-      </c>
-      <c r="D8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Proposal
- Modules</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Hosting Model</v>
-      </c>
-      <c r="F8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hosting 
-Provider</v>
-      </c>
-      <c r="G8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Technical Model
-Module</v>
-      </c>
-      <c r="H8" t="str" xml:space="preserve">
-        <v xml:space="preserve"> Service  Resource 
-Vendor Name (Relations)</v>
-      </c>
-      <c r="I8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Service Resources 
-Implementation</v>
-      </c>
-      <c r="J8" t="str">
-        <v># instances</v>
-      </c>
-      <c r="K8" t="str">
-        <v>Region/Zone Distribution</v>
-      </c>
-      <c r="L8" t="str">
-        <v>Distribution Method</v>
-      </c>
-      <c r="M8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Resource Role
-Distribution</v>
-      </c>
-      <c r="N8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Capacity
-Class</v>
-      </c>
-      <c r="O8" t="str">
-        <v>Method</v>
-      </c>
-      <c r="P8" t="str">
-        <v>Outages</v>
-      </c>
-      <c r="Q8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Release
-Class</v>
-      </c>
-      <c r="R8" t="str">
-        <v>Method</v>
-      </c>
-      <c r="S8" t="str">
-        <v>Outages</v>
-      </c>
-      <c r="T8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Configuration
-Specification</v>
-      </c>
-      <c r="U8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Configuration
-Version</v>
-      </c>
-      <c r="V8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Deploy
-Artifact
-</v>
-      </c>
-      <c r="W8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Artifact 
-Registry</v>
-      </c>
-      <c r="X8" t="str">
-        <v>Use for</v>
-      </c>
-      <c r="Y8" t="str">
-        <v>Method</v>
-      </c>
-      <c r="Z8" t="str">
-        <v>Store</v>
-      </c>
-      <c r="AA8" t="str">
-        <v>Freq.</v>
-      </c>
-      <c r="AB8" t="str">
-        <v>Retention</v>
-      </c>
-      <c r="AC8" t="str">
-        <v>Freq.</v>
-      </c>
-      <c r="AD8" t="str">
-        <v>Retention</v>
-      </c>
-      <c r="AE8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Recovery 
-Class</v>
-      </c>
-      <c r="AF8" t="str">
-        <v>Method</v>
-      </c>
-      <c r="AG8" t="str">
-        <v>RTO</v>
-      </c>
-      <c r="AH8" t="str">
-        <v>RPO</v>
-      </c>
-      <c r="AI8" t="str">
-        <v>Operated By</v>
-      </c>
-      <c r="AJ8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Operation other Activities
-(which  W3 activities)</v>
-      </c>
-      <c r="AK8" t="str">
-        <v>Model</v>
-      </c>
-      <c r="AL8" t="str">
-        <v>Details</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>PROD</v>
-      </c>
-      <c r="B9" t="str">
-        <v>99,9%</v>
-      </c>
-      <c r="C9" t="str">
-        <v>HA</v>
-      </c>
-      <c r="D9" t="str">
-        <v>INFRASTRUCTURE</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Not W3 Private datacenter</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Vendor Private</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Full IaaS</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Seeweb S.r.l. - Proxmox VE Cluster</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Virtualization Platform - ProxMox</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9" t="str">
-        <v>Cloud-Single-zone</v>
-      </c>
-      <c r="L9" t="str">
-        <v>Resources - SW configuration</v>
-      </c>
-      <c r="M9" t="str">
-        <v>Active</v>
-      </c>
-      <c r="N9" t="str">
-        <v>Ops Manual</v>
-      </c>
-      <c r="O9" t="str">
-        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
-      </c>
-      <c r="P9" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="Q9" t="str">
-        <v>Ops - Manual</v>
-      </c>
-      <c r="R9" t="str">
-        <v>Ops Manual - direct Log-on resource</v>
-      </c>
-      <c r="S9" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="T9" t="str">
-        <v>Configuration File (TXT)</v>
-      </c>
-      <c r="U9" t="str">
-        <v>Vendor Versioning</v>
-      </c>
-      <c r="V9" t="str">
-        <v>VMI (Virtual Machine Image) - KVM</v>
-      </c>
-      <c r="W9" t="str">
-        <v>Private Others Registry</v>
-      </c>
-      <c r="X9" t="str">
-        <v>Resource Recovery</v>
-      </c>
-      <c r="Y9" t="str">
-        <v>On-Premise SW/Appliance</v>
-      </c>
-      <c r="Z9" t="str">
-        <v>On-premise Store (Appliance)</v>
-      </c>
-      <c r="AA9" t="str">
-        <v>Daily</v>
-      </c>
-      <c r="AB9" t="str">
-        <v>1 month</v>
-      </c>
-      <c r="AC9" t="str">
-        <v>1 min</v>
-      </c>
-      <c r="AD9" t="str">
-        <v>1 week</v>
-      </c>
-      <c r="AE9" t="str">
-        <v xml:space="preserve">Region Resilent </v>
-      </c>
-      <c r="AF9" t="str">
-        <v>Automated By App</v>
-      </c>
-      <c r="AG9" t="str">
-        <v>Minutes (1-5)</v>
-      </c>
-      <c r="AH9" t="str">
-        <v>Minutes (1-5)</v>
-      </c>
-      <c r="AI9" t="str">
-        <v>HW/SW vendor</v>
-      </c>
-      <c r="AJ9" t="str">
-        <v>Cluster Management, VM Provisioning</v>
-      </c>
-      <c r="AK9" t="str">
-        <v>Public Cloud Consumption</v>
-      </c>
-      <c r="AL9" t="str">
-        <v>Seeweb Multinodo Contract</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>PROD</v>
-      </c>
-      <c r="B10" t="str">
-        <v>99,5%</v>
-      </c>
-      <c r="C10" t="str">
-        <v>HA-</v>
-      </c>
-      <c r="D10" t="str">
-        <v>INFRASTRUCTURE</v>
-      </c>
-      <c r="E10" t="str">
-        <v>Not W3 Private datacenter</v>
-      </c>
-      <c r="F10" t="str">
-        <v>Vendor Private</v>
-      </c>
-      <c r="G10" t="str">
-        <v>HW Appliance</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Seeweb S.r.l. - Fortinet FortiGate</v>
-      </c>
-      <c r="I10" t="str">
-        <v>HW Appliance - FortiGate NGFW</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10" t="str">
-        <v>Cloud-Single-zone</v>
-      </c>
-      <c r="L10" t="str">
-        <v>Resource - Manual Installation</v>
-      </c>
-      <c r="M10" t="str">
-        <v>Active</v>
-      </c>
-      <c r="N10" t="str">
-        <v>Fixed capacity</v>
-      </c>
-      <c r="O10" t="str">
-        <v>Do not scale - Fixed capacity</v>
-      </c>
-      <c r="P10" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="Q10" t="str">
-        <v>Ops - Manual</v>
-      </c>
-      <c r="R10" t="str">
-        <v>Ops Manual - direct Log-on resource</v>
-      </c>
-      <c r="S10" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="T10" t="str">
-        <v>Configuration File (TXT)</v>
-      </c>
-      <c r="U10" t="str">
-        <v>Vendor Versioning</v>
-      </c>
-      <c r="V10" t="str">
-        <v>SW Bins</v>
-      </c>
-      <c r="W10" t="str">
-        <v>Private Others Registry</v>
-      </c>
-      <c r="X10" t="str">
-        <v>Resource Recovery</v>
-      </c>
-      <c r="Y10" t="str">
-        <v>On-Premise SW/Appliance</v>
-      </c>
-      <c r="Z10" t="str">
-        <v>On-premise Store (Appliance)</v>
-      </c>
-      <c r="AA10" t="str">
-        <v>Daily</v>
-      </c>
-      <c r="AB10" t="str">
-        <v>1 month</v>
-      </c>
-      <c r="AC10" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="AD10" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="AE10" t="str">
-        <v xml:space="preserve">Local Resilent </v>
-      </c>
-      <c r="AF10" t="str">
-        <v>Manual By Operation</v>
-      </c>
-      <c r="AG10" t="str">
-        <v>Hour (1-5)</v>
-      </c>
-      <c r="AH10" t="str">
-        <v>Hour (1-5)</v>
-      </c>
-      <c r="AI10" t="str">
-        <v>HW/SW vendor</v>
-      </c>
-      <c r="AJ10" t="str">
-        <v>Security Policy, Threat Monitoring</v>
-      </c>
-      <c r="AK10" t="str">
-        <v>COTs SW License</v>
-      </c>
-      <c r="AL10" t="str">
-        <v>FortiCare via Seeweb</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>PROD</v>
-      </c>
-      <c r="B11" t="str">
-        <v>99,9%</v>
-      </c>
-      <c r="C11" t="str">
-        <v>HA</v>
-      </c>
-      <c r="D11" t="str">
-        <v>INFRASTRUCTURE</v>
-      </c>
-      <c r="E11" t="str">
-        <v>Not W3 Private datacenter</v>
-      </c>
-      <c r="F11" t="str">
-        <v>Vendor Private</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Bare Metal</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Seeweb S.r.l. - Proxmox Backup Server</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Bare Metal - PBS Dedicated</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="K11" t="str">
-        <v>Cloud-Single-zone</v>
-      </c>
-      <c r="L11" t="str">
-        <v>Resources - SW configuration</v>
-      </c>
-      <c r="M11" t="str">
-        <v>Active</v>
-      </c>
-      <c r="N11" t="str">
-        <v>Ops Manual</v>
-      </c>
-      <c r="O11" t="str">
-        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
-      </c>
-      <c r="P11" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="Q11" t="str">
-        <v>Ops - Manual</v>
-      </c>
-      <c r="R11" t="str">
-        <v>Ops Manual - direct Log-on resource</v>
-      </c>
-      <c r="S11" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="T11" t="str">
-        <v>Configuration File (TXT)</v>
-      </c>
-      <c r="U11" t="str">
-        <v>Vendor Versioning</v>
-      </c>
-      <c r="V11" t="str">
-        <v>SW Bins</v>
-      </c>
-      <c r="W11" t="str">
-        <v>Object Store (SW bins)</v>
-      </c>
-      <c r="X11" t="str">
-        <v>Resource Recovery</v>
-      </c>
-      <c r="Y11" t="str">
-        <v>On-Premise SW/Appliance</v>
-      </c>
-      <c r="Z11" t="str">
-        <v>On-premise Store (Appliance)</v>
-      </c>
-      <c r="AA11" t="str">
-        <v>Daily</v>
-      </c>
-      <c r="AB11" t="str">
-        <v>1 month</v>
-      </c>
-      <c r="AC11" t="str">
-        <v>1 min</v>
-      </c>
-      <c r="AD11" t="str">
-        <v>1 week</v>
-      </c>
-      <c r="AE11" t="str">
-        <v xml:space="preserve">Region Resilent </v>
-      </c>
-      <c r="AF11" t="str">
-        <v>Manual By Operation</v>
-      </c>
-      <c r="AG11" t="str">
-        <v>Hour (1-5)</v>
-      </c>
-      <c r="AH11" t="str">
-        <v>Minutes (1-5)</v>
-      </c>
-      <c r="AI11" t="str">
-        <v>HW/SW vendor</v>
-      </c>
-      <c r="AJ11" t="str">
-        <v>Backup Storage, DR Recovery</v>
-      </c>
-      <c r="AK11" t="str">
-        <v>Public Cloud Consumption</v>
-      </c>
-      <c r="AL11" t="str">
-        <v>Seeweb PBS Service</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>PROD</v>
-      </c>
-      <c r="B12" t="str">
-        <v>99,9%</v>
-      </c>
-      <c r="C12" t="str">
-        <v>HA</v>
-      </c>
-      <c r="D12" t="str">
-        <v>APPLICATION</v>
-      </c>
-      <c r="E12" t="str">
-        <v>Not W3 Private datacenter</v>
-      </c>
-      <c r="F12" t="str">
-        <v>Vendor Private</v>
-      </c>
-      <c r="G12" t="str">
-        <v>Full IaaS</v>
-      </c>
-      <c r="H12" t="str">
-        <v>Seeweb S.r.l. - W3Suite Frontend</v>
-      </c>
-      <c r="I12" t="str">
-        <v>App (RunTime) - Linux native</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="K12" t="str">
-        <v>Cloud-Single-zone</v>
-      </c>
-      <c r="L12" t="str">
-        <v>Resources - SW configuration</v>
-      </c>
-      <c r="M12" t="str">
-        <v>Active</v>
-      </c>
-      <c r="N12" t="str">
-        <v>Ops Manual</v>
-      </c>
-      <c r="O12" t="str">
-        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
-      </c>
-      <c r="P12" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="Q12" t="str">
-        <v>Ops - Automated</v>
-      </c>
-      <c r="R12" t="str">
-        <v xml:space="preserve">Ops Automated (SW) - DevOps </v>
-      </c>
-      <c r="S12" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="T12" t="str">
-        <v>Configuration File (YAML)</v>
-      </c>
-      <c r="U12" t="str">
-        <v>W3 Git</v>
-      </c>
-      <c r="V12" t="str">
-        <v>SW Bins</v>
-      </c>
-      <c r="W12" t="str">
-        <v>Object Store (SW bins)</v>
-      </c>
-      <c r="X12" t="str">
-        <v>Resource Recovery</v>
-      </c>
-      <c r="Y12" t="str">
-        <v>On-Premise SW/Appliance</v>
-      </c>
-      <c r="Z12" t="str">
-        <v>On-premise Store (Appliance)</v>
-      </c>
-      <c r="AA12" t="str">
-        <v>Daily</v>
-      </c>
-      <c r="AB12" t="str">
-        <v>1 month</v>
-      </c>
-      <c r="AC12" t="str">
-        <v>1 min</v>
-      </c>
-      <c r="AD12" t="str">
-        <v>1 week</v>
-      </c>
-      <c r="AE12" t="str">
-        <v xml:space="preserve">Region Resilent </v>
-      </c>
-      <c r="AF12" t="str">
-        <v>Automated By App</v>
-      </c>
-      <c r="AG12" t="str">
-        <v xml:space="preserve">Seconds </v>
-      </c>
-      <c r="AH12" t="str">
-        <v xml:space="preserve">Seconds </v>
-      </c>
-      <c r="AI12" t="str">
-        <v>SW Integrator</v>
-      </c>
-      <c r="AJ12" t="str">
-        <v>TLS, Routing, LB Config</v>
-      </c>
-      <c r="AK12" t="str">
-        <v>Public Cloud Consumption</v>
-      </c>
-      <c r="AL12" t="str">
-        <v>Seeweb VPC</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>PROD</v>
-      </c>
-      <c r="B13" t="str">
-        <v>99,9%</v>
-      </c>
-      <c r="C13" t="str">
-        <v>HA</v>
-      </c>
-      <c r="D13" t="str">
-        <v>APPLICATION</v>
-      </c>
-      <c r="E13" t="str">
-        <v>Not W3 Private datacenter</v>
-      </c>
-      <c r="F13" t="str">
-        <v>Vendor Private</v>
-      </c>
-      <c r="G13" t="str">
-        <v>Full IaaS</v>
-      </c>
-      <c r="H13" t="str">
-        <v>Seeweb S.r.l. - W3Suite Backend</v>
-      </c>
-      <c r="I13" t="str">
-        <v>App (RunTime) - Linux native</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="K13" t="str">
-        <v>Cloud-Single-zone</v>
-      </c>
-      <c r="L13" t="str">
-        <v>Resources - SW configuration</v>
-      </c>
-      <c r="M13" t="str">
-        <v>Active</v>
-      </c>
-      <c r="N13" t="str">
-        <v>Ops Manual</v>
-      </c>
-      <c r="O13" t="str">
-        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
-      </c>
-      <c r="P13" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="Q13" t="str">
-        <v>Ops - Automated</v>
-      </c>
-      <c r="R13" t="str">
-        <v xml:space="preserve">Ops Automated (SW) - DevOps </v>
-      </c>
-      <c r="S13" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="T13" t="str">
-        <v>Configuration File (YAML)</v>
-      </c>
-      <c r="U13" t="str">
-        <v>W3 Git</v>
-      </c>
-      <c r="V13" t="str">
-        <v>SW Bins</v>
-      </c>
-      <c r="W13" t="str">
-        <v>Object Store (SW bins)</v>
-      </c>
-      <c r="X13" t="str">
-        <v>Resource Recovery</v>
-      </c>
-      <c r="Y13" t="str">
-        <v>On-Premise SW/Appliance</v>
-      </c>
-      <c r="Z13" t="str">
-        <v>On-premise Store (Appliance)</v>
-      </c>
-      <c r="AA13" t="str">
-        <v>Daily</v>
-      </c>
-      <c r="AB13" t="str">
-        <v>1 month</v>
-      </c>
-      <c r="AC13" t="str">
-        <v>1 min</v>
-      </c>
-      <c r="AD13" t="str">
-        <v>1 week</v>
-      </c>
-      <c r="AE13" t="str">
-        <v xml:space="preserve">Region Resilent </v>
-      </c>
-      <c r="AF13" t="str">
-        <v>Automated By App</v>
-      </c>
-      <c r="AG13" t="str">
-        <v>Minutes (1-5)</v>
-      </c>
-      <c r="AH13" t="str">
-        <v xml:space="preserve">Seconds </v>
-      </c>
-      <c r="AI13" t="str">
-        <v>SW Integrator</v>
-      </c>
-      <c r="AJ13" t="str">
-        <v>Deploy, API, AI Gateway, Cache</v>
-      </c>
-      <c r="AK13" t="str">
-        <v>Public Cloud Consumption</v>
-      </c>
-      <c r="AL13" t="str">
-        <v>Seeweb VPC</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>PROD</v>
-      </c>
-      <c r="B14" t="str">
-        <v>99,9%</v>
-      </c>
-      <c r="C14" t="str">
-        <v>HA+</v>
-      </c>
-      <c r="D14" t="str">
-        <v>DATABASE</v>
-      </c>
-      <c r="E14" t="str">
-        <v>Not W3 Private datacenter</v>
-      </c>
-      <c r="F14" t="str">
-        <v>Vendor Private</v>
-      </c>
-      <c r="G14" t="str">
-        <v>Full IaaS</v>
-      </c>
-      <c r="H14" t="str">
-        <v>Seeweb S.r.l. - PostgreSQL Primary</v>
-      </c>
-      <c r="I14" t="str">
-        <v>App (RunTime) - Linux native</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14" t="str">
-        <v>Cloud-Single-zone</v>
-      </c>
-      <c r="L14" t="str">
-        <v>Resources - SW configuration</v>
-      </c>
-      <c r="M14" t="str">
-        <v>Active</v>
-      </c>
-      <c r="N14" t="str">
-        <v>Ops Manual</v>
-      </c>
-      <c r="O14" t="str">
-        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
-      </c>
-      <c r="P14" t="str">
-        <v>Minutes (1-10)</v>
-      </c>
-      <c r="Q14" t="str">
-        <v>Ops - Manual</v>
-      </c>
-      <c r="R14" t="str">
-        <v>Ops Manual - direct Log-on resource</v>
-      </c>
-      <c r="S14" t="str">
-        <v>Minutes (1-10)</v>
-      </c>
-      <c r="T14" t="str">
-        <v>Configuration File (TXT)</v>
-      </c>
-      <c r="U14" t="str">
-        <v>Vendor Versioning</v>
-      </c>
-      <c r="V14" t="str">
-        <v>SW Bins</v>
-      </c>
-      <c r="W14" t="str">
-        <v>Object Store (SW bins)</v>
-      </c>
-      <c r="X14" t="str">
-        <v>Resource: Release and Recovery</v>
-      </c>
-      <c r="Y14" t="str">
-        <v>On-Premise SW/Appliance</v>
-      </c>
-      <c r="Z14" t="str">
-        <v>On-premise Store (Appliance)</v>
-      </c>
-      <c r="AA14" t="str">
-        <v>Daily</v>
-      </c>
-      <c r="AB14" t="str">
-        <v>1 month</v>
-      </c>
-      <c r="AC14" t="str">
-        <v>1 min</v>
-      </c>
-      <c r="AD14" t="str">
-        <v>1 week</v>
-      </c>
-      <c r="AE14" t="str">
-        <v xml:space="preserve">Region Resilent </v>
-      </c>
-      <c r="AF14" t="str">
-        <v>Automated By App</v>
-      </c>
-      <c r="AG14" t="str">
-        <v>Minutes (1-5)</v>
-      </c>
-      <c r="AH14" t="str">
-        <v xml:space="preserve">Seconds </v>
-      </c>
-      <c r="AI14" t="str">
-        <v>SW Integrator</v>
-      </c>
-      <c r="AJ14" t="str">
-        <v>Backup, Tuning, PITR, WAL</v>
-      </c>
-      <c r="AK14" t="str">
-        <v>Public Cloud Consumption</v>
-      </c>
-      <c r="AL14" t="str">
-        <v>Seeweb VPC</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>PROD</v>
-      </c>
-      <c r="B15" t="str">
-        <v>99,9%</v>
-      </c>
-      <c r="C15" t="str">
-        <v>HA</v>
-      </c>
-      <c r="D15" t="str">
-        <v>DATABASE</v>
-      </c>
-      <c r="E15" t="str">
-        <v>Not W3 Private datacenter</v>
-      </c>
-      <c r="F15" t="str">
-        <v>Vendor Private</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Full IaaS</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Seeweb S.r.l. - PostgreSQL Replica</v>
-      </c>
-      <c r="I15" t="str">
-        <v>App (RunTime) - Linux native</v>
-      </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="K15" t="str">
-        <v>Cloud-Single-zone</v>
-      </c>
-      <c r="L15" t="str">
-        <v>Resources - SW configuration</v>
-      </c>
-      <c r="M15" t="str">
-        <v>Standby</v>
-      </c>
-      <c r="N15" t="str">
-        <v>Ops Manual</v>
-      </c>
-      <c r="O15" t="str">
-        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
-      </c>
-      <c r="P15" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="Q15" t="str">
-        <v>Ops - Manual</v>
-      </c>
-      <c r="R15" t="str">
-        <v>Ops Manual - direct Log-on resource</v>
-      </c>
-      <c r="S15" t="str">
-        <v>No outages</v>
-      </c>
-      <c r="T15" t="str">
-        <v>Configuration File (TXT)</v>
-      </c>
-      <c r="U15" t="str">
-        <v>Vendor Versioning</v>
-      </c>
-      <c r="V15" t="str">
-        <v>SW Bins</v>
-      </c>
-      <c r="W15" t="str">
-        <v>Object Store (SW bins)</v>
-      </c>
-      <c r="X15" t="str">
-        <v>Resource Recovery</v>
-      </c>
-      <c r="Y15" t="str">
-        <v>On-Premise SW/Appliance</v>
-      </c>
-      <c r="Z15" t="str">
-        <v>On-premise Store (Appliance)</v>
-      </c>
-      <c r="AA15" t="str">
-        <v>Daily</v>
-      </c>
-      <c r="AB15" t="str">
-        <v>1 month</v>
-      </c>
-      <c r="AC15" t="str">
-        <v>1 min</v>
-      </c>
-      <c r="AD15" t="str">
-        <v>1 week</v>
-      </c>
-      <c r="AE15" t="str">
-        <v xml:space="preserve">Region Resilent </v>
-      </c>
-      <c r="AF15" t="str">
-        <v>Automated By App</v>
-      </c>
-      <c r="AG15" t="str">
-        <v xml:space="preserve">Seconds </v>
-      </c>
-      <c r="AH15" t="str">
-        <v xml:space="preserve">Seconds </v>
-      </c>
-      <c r="AI15" t="str">
-        <v>SW Integrator</v>
-      </c>
-      <c r="AJ15" t="str">
-        <v>Streaming Replication, Failover</v>
-      </c>
-      <c r="AK15" t="str">
-        <v>Public Cloud Consumption</v>
-      </c>
-      <c r="AL15" t="str">
-        <v>Seeweb VPC</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AL15"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:G15"/>
-  <cols>
-    <col min="1" max="1" width="25.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="25.83203125" customWidth="1"/>
-    <col min="5" max="5" width="25.83203125" customWidth="1"/>
-    <col min="6" max="6" width="25.83203125" customWidth="1"/>
-    <col min="7" max="7" width="25.83203125" customWidth="1"/>
-    <col min="8" max="8" width="25.83203125" customWidth="1"/>
-    <col min="9" max="9" width="25.83203125" customWidth="1"/>
-    <col min="10" max="10" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="A2" t="str">
-        <v>Public Cloud Zones or W3 Sites</v>
-      </c>
-    </row>
-    <row r="3" xml:space="preserve">
-      <c r="A3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Field Definition &amp; Values 
-Module of solution</v>
-      </c>
-      <c r="B3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Field Definition &amp; Values 
-Resource of module</v>
-      </c>
-      <c r="C3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Field Definition &amp; Values
-Resource component</v>
-      </c>
-      <c r="D3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Field Definition &amp; Values
-Sites List</v>
+        <v>Public Cloud Zones or W3 Sites - Seeweb Italy</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">
@@ -6992,19 +6974,21 @@
       </c>
       <c r="C7" t="str" xml:space="preserve">
         <v xml:space="preserve">Resource 
-Component (if needed)</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Region (Zone/site)</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Zone/site</v>
+Component</v>
+      </c>
+      <c r="D7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Seeweb DC1
+(Primary)</v>
+      </c>
+      <c r="E7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Seeweb DC2
+(DR)</v>
       </c>
       <c r="F7" t="str">
-        <v>Zone/site</v>
+        <v>Seeweb DC3</v>
       </c>
       <c r="G7" t="str">
-        <v>Zone/site</v>
+        <v>Notes</v>
       </c>
     </row>
     <row r="8">
@@ -7018,10 +7002,10 @@
         <v/>
       </c>
       <c r="D8" t="str">
-        <v>Seeweb Italy DC1</v>
+        <v>Milan/Rome</v>
       </c>
       <c r="E8" t="str">
-        <v>Seeweb Italy DC2</v>
+        <v>Rome/Milan</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -7038,10 +7022,10 @@
         <v>Proxmox VE Cluster</v>
       </c>
       <c r="C9" t="str">
-        <v>Multinodo Cluster</v>
+        <v>Nodo 1</v>
       </c>
       <c r="D9" t="str">
-        <v>Seeweb DC1 (Primary)</v>
+        <v>Active</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -7050,7 +7034,7 @@
         <v/>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>Primary compute</v>
       </c>
     </row>
     <row r="10">
@@ -7058,13 +7042,13 @@
         <v>INFRASTRUCTURE</v>
       </c>
       <c r="B10" t="str">
-        <v>FortiGate NGFW</v>
+        <v>Proxmox VE Cluster</v>
       </c>
       <c r="C10" t="str">
-        <v>Single Appliance</v>
+        <v>Nodo 2</v>
       </c>
       <c r="D10" t="str">
-        <v>Seeweb DC1</v>
+        <v>Active</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -7073,7 +7057,7 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>HA compute</v>
       </c>
     </row>
     <row r="11">
@@ -7081,36 +7065,36 @@
         <v>INFRASTRUCTURE</v>
       </c>
       <c r="B11" t="str">
-        <v>Proxmox Backup Server</v>
+        <v>Proxmox VE Cluster</v>
       </c>
       <c r="C11" t="str">
-        <v>Dedicated Server</v>
+        <v>Nodo 3</v>
       </c>
       <c r="D11" t="str">
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>Seeweb DC2 (DR)</v>
+        <v>Active</v>
       </c>
       <c r="F11" t="str">
         <v/>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>DR compute</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>APPLICATION</v>
+        <v>INFRASTRUCTURE</v>
       </c>
       <c r="B12" t="str">
-        <v>W3Suite Frontend</v>
+        <v>FortiGate NGFW</v>
       </c>
       <c r="C12" t="str">
-        <v>Nginx + LB</v>
+        <v>Single Appliance</v>
       </c>
       <c r="D12" t="str">
-        <v>Seeweb DC1</v>
+        <v>Active</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -7119,44 +7103,44 @@
         <v/>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>HW Appliance - No HA</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>APPLICATION</v>
+        <v>INFRASTRUCTURE</v>
       </c>
       <c r="B13" t="str">
-        <v>W3Suite Backend</v>
+        <v>Proxmox Backup Server</v>
       </c>
       <c r="C13" t="str">
-        <v>API + Redis + MCP</v>
+        <v>Dedicated</v>
       </c>
       <c r="D13" t="str">
-        <v>Seeweb DC1</v>
+        <v/>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>Active</v>
       </c>
       <c r="F13" t="str">
         <v/>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>DR Backup Storage</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>DATABASE</v>
+        <v>APPLICATION</v>
       </c>
       <c r="B14" t="str">
-        <v>PostgreSQL Primary</v>
+        <v>W3Suite Frontend</v>
       </c>
       <c r="C14" t="str">
-        <v>DB Primary</v>
+        <v>Nginx + LB</v>
       </c>
       <c r="D14" t="str">
-        <v>Seeweb DC1</v>
+        <v>Active</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -7170,16 +7154,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>DATABASE</v>
+        <v>APPLICATION</v>
       </c>
       <c r="B15" t="str">
-        <v>PostgreSQL Replica</v>
+        <v>W3Suite Backend</v>
       </c>
       <c r="C15" t="str">
-        <v>DB Standby</v>
+        <v>API + Redis + MCP</v>
       </c>
       <c r="D15" t="str">
-        <v>Seeweb DC1</v>
+        <v>Active</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -7191,9 +7175,55 @@
         <v/>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>DATABASE</v>
+      </c>
+      <c r="B16" t="str">
+        <v>PostgreSQL Primary</v>
+      </c>
+      <c r="C16" t="str">
+        <v>DB Primary</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Active</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v>Read/Write</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>DATABASE</v>
+      </c>
+      <c r="B17" t="str">
+        <v>PostgreSQL Replica</v>
+      </c>
+      <c r="C17" t="str">
+        <v>DB Standby</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Standby</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v>Streaming Replication</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A2:G15"/>
+    <ignoredError numberStoredAsText="1" sqref="A2:G17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/gara-appalto/SERVICE-RESOURCE-MODEL-W3SUITE-FINAL.xlsx
+++ b/docs/gara-appalto/SERVICE-RESOURCE-MODEL-W3SUITE-FINAL.xlsx
@@ -5820,7 +5820,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>W3Suite - Service Resource Model - Seeweb Infrastructure</v>
+        <v>W3Suite - Service Resource Model - Seeweb Infrastructure (Verified)</v>
       </c>
     </row>
     <row r="4">
@@ -6144,13 +6144,13 @@
         <v>Vendor Private</v>
       </c>
       <c r="G9" t="str">
-        <v>Full IaaS</v>
+        <v>Bare Metal</v>
       </c>
       <c r="H9" t="str">
-        <v>Seeweb S.r.l. - Proxmox VE Cluster</v>
+        <v>Seeweb S.r.l. - Foundation Server Cluster</v>
       </c>
       <c r="I9" t="str">
-        <v>Virtualization Platform - ProxMox</v>
+        <v>Bare Metal - Proxmox VE Hosts</v>
       </c>
       <c r="J9" t="str">
         <v>3+ nodi</v>
@@ -6237,7 +6237,7 @@
         <v>Public Cloud Consumption</v>
       </c>
       <c r="AL9" t="str">
-        <v>Seeweb Multinodo Contract</v>
+        <v>Seeweb Foundation Server Contract</v>
       </c>
     </row>
     <row r="10">
@@ -6260,31 +6260,31 @@
         <v>Vendor Private</v>
       </c>
       <c r="G10" t="str">
-        <v>HW Appliance</v>
+        <v>Full IaaS</v>
       </c>
       <c r="H10" t="str">
-        <v>Seeweb S.r.l. - Fortinet FortiGate</v>
+        <v>Seeweb S.r.l. - Fortinet FortiGate VM</v>
       </c>
       <c r="I10" t="str">
-        <v>HW Appliance - FortiGate NGFW</v>
+        <v>Virtual Appliance - FortiGate NGFW</v>
       </c>
       <c r="J10" t="str">
         <v>1 (Single)</v>
       </c>
       <c r="K10" t="str">
-        <v>N/A</v>
+        <v>Cloud-Single-zone</v>
       </c>
       <c r="L10" t="str">
-        <v>Resource - Manual Installation</v>
+        <v>Resources - SW configuration</v>
       </c>
       <c r="M10" t="str">
         <v>Active</v>
       </c>
       <c r="N10" t="str">
-        <v>Fixed capacity</v>
+        <v>Ops Manual</v>
       </c>
       <c r="O10" t="str">
-        <v>Do not scale - Fixed capacity</v>
+        <v>Ops Manual - Cloud consolle/direct Log-on resource</v>
       </c>
       <c r="P10" t="str">
         <v>No outages</v>
@@ -6305,7 +6305,7 @@
         <v>Vendor Versioning</v>
       </c>
       <c r="V10" t="str">
-        <v>SW Bins</v>
+        <v>VMI (Virtual Machine Image) - KVM</v>
       </c>
       <c r="W10" t="str">
         <v>Private Others Registry</v>
@@ -6350,10 +6350,10 @@
         <v>Security Policy, Threat Monitoring, FW Rules</v>
       </c>
       <c r="AK10" t="str">
-        <v>(on-premise) HW Buy &amp; Support</v>
+        <v>COTs SW License</v>
       </c>
       <c r="AL10" t="str">
-        <v>FortiGate HW + FortiCare Support</v>
+        <v>FortiGate VM + FortiCare Support</v>
       </c>
     </row>
     <row r="11">
@@ -6376,16 +6376,16 @@
         <v>Vendor Private</v>
       </c>
       <c r="G11" t="str">
-        <v>Bare Metal</v>
+        <v>Full IaaS</v>
       </c>
       <c r="H11" t="str">
-        <v>Seeweb S.r.l. - Proxmox Backup Server</v>
+        <v>Seeweb S.r.l. - Cloud Backup (PBS)</v>
       </c>
       <c r="I11" t="str">
-        <v>Bare Metal - PBS Dedicated</v>
+        <v>Cloud Service - Proxmox Backup Server</v>
       </c>
       <c r="J11" t="str">
-        <v>1 (Dedicato)</v>
+        <v>1 (Servizio)</v>
       </c>
       <c r="K11" t="str">
         <v>Cloud-Single-zone</v>
@@ -6469,7 +6469,7 @@
         <v>Public Cloud Consumption</v>
       </c>
       <c r="AL11" t="str">
-        <v>Seeweb PBS Service</v>
+        <v>Seeweb Cloud Backup 23€/100GB</v>
       </c>
     </row>
     <row r="12">
@@ -6945,7 +6945,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:G17"/>
+  <dimension ref="A2:F17"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -6961,7 +6961,7 @@
   <sheetData>
     <row r="2">
       <c r="A2" t="str">
-        <v>Public Cloud Zones or W3 Sites - Seeweb Italy</v>
+        <v>Public Cloud Zones or W3 Sites - Seeweb Italy (Verified from seeweb.it)</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">
@@ -6985,9 +6985,6 @@
 (DR)</v>
       </c>
       <c r="F7" t="str">
-        <v>Seeweb DC3</v>
-      </c>
-      <c r="G7" t="str">
         <v>Notes</v>
       </c>
     </row>
@@ -7002,15 +6999,12 @@
         <v/>
       </c>
       <c r="D8" t="str">
-        <v>Milan/Rome</v>
+        <v>Foundation Server</v>
       </c>
       <c r="E8" t="str">
-        <v>Rome/Milan</v>
+        <v>Cloud Backup</v>
       </c>
       <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
         <v/>
       </c>
     </row>
@@ -7019,10 +7013,10 @@
         <v>INFRASTRUCTURE</v>
       </c>
       <c r="B9" t="str">
-        <v>Proxmox VE Cluster</v>
+        <v>Foundation Server Cluster</v>
       </c>
       <c r="C9" t="str">
-        <v>Nodo 1</v>
+        <v>Nodo 1 (Bare Metal)</v>
       </c>
       <c r="D9" t="str">
         <v>Active</v>
@@ -7031,10 +7025,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v>Primary compute</v>
+        <v>Proxmox VE Host</v>
       </c>
     </row>
     <row r="10">
@@ -7042,10 +7033,10 @@
         <v>INFRASTRUCTURE</v>
       </c>
       <c r="B10" t="str">
-        <v>Proxmox VE Cluster</v>
+        <v>Foundation Server Cluster</v>
       </c>
       <c r="C10" t="str">
-        <v>Nodo 2</v>
+        <v>Nodo 2 (Bare Metal)</v>
       </c>
       <c r="D10" t="str">
         <v>Active</v>
@@ -7054,10 +7045,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v>HA compute</v>
+        <v>Proxmox VE Host</v>
       </c>
     </row>
     <row r="11">
@@ -7065,10 +7053,10 @@
         <v>INFRASTRUCTURE</v>
       </c>
       <c r="B11" t="str">
-        <v>Proxmox VE Cluster</v>
+        <v>Foundation Server Cluster</v>
       </c>
       <c r="C11" t="str">
-        <v>Nodo 3</v>
+        <v>Nodo 3 (Bare Metal)</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -7077,10 +7065,7 @@
         <v>Active</v>
       </c>
       <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v>DR compute</v>
+        <v>DR Node</v>
       </c>
     </row>
     <row r="12">
@@ -7088,10 +7073,10 @@
         <v>INFRASTRUCTURE</v>
       </c>
       <c r="B12" t="str">
-        <v>FortiGate NGFW</v>
+        <v>FortiGate VM</v>
       </c>
       <c r="C12" t="str">
-        <v>Single Appliance</v>
+        <v>Virtual Appliance</v>
       </c>
       <c r="D12" t="str">
         <v>Active</v>
@@ -7100,10 +7085,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v>HW Appliance - No HA</v>
+        <v>NGFW (1-4 CPU)</v>
       </c>
     </row>
     <row r="13">
@@ -7111,10 +7093,10 @@
         <v>INFRASTRUCTURE</v>
       </c>
       <c r="B13" t="str">
-        <v>Proxmox Backup Server</v>
+        <v>Cloud Backup (PBS)</v>
       </c>
       <c r="C13" t="str">
-        <v>Dedicated</v>
+        <v>Cloud Service</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -7123,10 +7105,7 @@
         <v>Active</v>
       </c>
       <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v>DR Backup Storage</v>
+        <v>23€/100GB</v>
       </c>
     </row>
     <row r="14">
@@ -7137,7 +7116,7 @@
         <v>W3Suite Frontend</v>
       </c>
       <c r="C14" t="str">
-        <v>Nginx + LB</v>
+        <v>VPC (VM)</v>
       </c>
       <c r="D14" t="str">
         <v>Active</v>
@@ -7146,10 +7125,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
+        <v>Nginx + LB</v>
       </c>
     </row>
     <row r="15">
@@ -7160,7 +7136,7 @@
         <v>W3Suite Backend</v>
       </c>
       <c r="C15" t="str">
-        <v>API + Redis + MCP</v>
+        <v>VPC (VM)</v>
       </c>
       <c r="D15" t="str">
         <v>Active</v>
@@ -7169,10 +7145,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
+        <v>API + Redis + MCP</v>
       </c>
     </row>
     <row r="16">
@@ -7183,7 +7156,7 @@
         <v>PostgreSQL Primary</v>
       </c>
       <c r="C16" t="str">
-        <v>DB Primary</v>
+        <v>VPC (VM)</v>
       </c>
       <c r="D16" t="str">
         <v>Active</v>
@@ -7192,9 +7165,6 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
         <v>Read/Write</v>
       </c>
     </row>
@@ -7206,7 +7176,7 @@
         <v>PostgreSQL Replica</v>
       </c>
       <c r="C17" t="str">
-        <v>DB Standby</v>
+        <v>VPC (VM)</v>
       </c>
       <c r="D17" t="str">
         <v>Standby</v>
@@ -7215,15 +7185,12 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v/>
-      </c>
-      <c r="G17" t="str">
         <v>Streaming Replication</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A2:G17"/>
+    <ignoredError numberStoredAsText="1" sqref="A2:F17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/gara-appalto/SERVICE-RESOURCE-MODEL-W3SUITE-FINAL.xlsx
+++ b/docs/gara-appalto/SERVICE-RESOURCE-MODEL-W3SUITE-FINAL.xlsx
@@ -5820,7 +5820,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>W3Suite - Service Resource Model - Seeweb Infrastructure (Verified)</v>
+        <v>W3Suite - Service Resource Model - Seeweb Infrastructure</v>
       </c>
     </row>
     <row r="4">
@@ -6153,10 +6153,10 @@
         <v>Bare Metal - Proxmox VE Hosts</v>
       </c>
       <c r="J9" t="str">
-        <v>3+ nodi</v>
+        <v>2 nodi</v>
       </c>
       <c r="K9" t="str">
-        <v xml:space="preserve">Cloud-Multi-region </v>
+        <v>Cloud-Multi-zone</v>
       </c>
       <c r="L9" t="str">
         <v>Resources - SW configuration</v>
@@ -6216,7 +6216,7 @@
         <v>1 week</v>
       </c>
       <c r="AE9" t="str">
-        <v xml:space="preserve">Region Resilent </v>
+        <v xml:space="preserve">Zone Resilent </v>
       </c>
       <c r="AF9" t="str">
         <v>Automated By App</v>
@@ -6945,7 +6945,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:F17"/>
+  <dimension ref="A2:F16"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -6961,7 +6961,7 @@
   <sheetData>
     <row r="2">
       <c r="A2" t="str">
-        <v>Public Cloud Zones or W3 Sites - Seeweb Italy (Verified from seeweb.it)</v>
+        <v>Public Cloud Zones or W3 Sites - Seeweb Italy</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="E7" t="str" xml:space="preserve">
         <v xml:space="preserve">Seeweb DC2
-(DR)</v>
+(Backup)</v>
       </c>
       <c r="F7" t="str">
         <v>Notes</v>
@@ -7045,7 +7045,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>Proxmox VE Host</v>
+        <v>Proxmox VE Host + HA Appliance</v>
       </c>
     </row>
     <row r="11">
@@ -7053,19 +7053,19 @@
         <v>INFRASTRUCTURE</v>
       </c>
       <c r="B11" t="str">
-        <v>Foundation Server Cluster</v>
+        <v>FortiGate VM</v>
       </c>
       <c r="C11" t="str">
-        <v>Nodo 3 (Bare Metal)</v>
+        <v>Virtual Appliance</v>
       </c>
       <c r="D11" t="str">
+        <v>Active</v>
+      </c>
+      <c r="E11" t="str">
         <v/>
       </c>
-      <c r="E11" t="str">
-        <v>Active</v>
-      </c>
       <c r="F11" t="str">
-        <v>DR Node</v>
+        <v>NGFW (1-4 CPU)</v>
       </c>
     </row>
     <row r="12">
@@ -7073,39 +7073,39 @@
         <v>INFRASTRUCTURE</v>
       </c>
       <c r="B12" t="str">
-        <v>FortiGate VM</v>
+        <v>Cloud Backup (PBS)</v>
       </c>
       <c r="C12" t="str">
-        <v>Virtual Appliance</v>
+        <v>Cloud Service</v>
       </c>
       <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
         <v>Active</v>
       </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
       <c r="F12" t="str">
-        <v>NGFW (1-4 CPU)</v>
+        <v>23€/100GB - DR</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>INFRASTRUCTURE</v>
+        <v>APPLICATION</v>
       </c>
       <c r="B13" t="str">
-        <v>Cloud Backup (PBS)</v>
+        <v>W3Suite Frontend</v>
       </c>
       <c r="C13" t="str">
-        <v>Cloud Service</v>
+        <v>VPC (VM)</v>
       </c>
       <c r="D13" t="str">
+        <v>Active</v>
+      </c>
+      <c r="E13" t="str">
         <v/>
       </c>
-      <c r="E13" t="str">
-        <v>Active</v>
-      </c>
       <c r="F13" t="str">
-        <v>23€/100GB</v>
+        <v>Nginx + LB</v>
       </c>
     </row>
     <row r="14">
@@ -7113,7 +7113,7 @@
         <v>APPLICATION</v>
       </c>
       <c r="B14" t="str">
-        <v>W3Suite Frontend</v>
+        <v>W3Suite Backend</v>
       </c>
       <c r="C14" t="str">
         <v>VPC (VM)</v>
@@ -7125,15 +7125,15 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>Nginx + LB</v>
+        <v>API + Redis + MCP</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>APPLICATION</v>
+        <v>DATABASE</v>
       </c>
       <c r="B15" t="str">
-        <v>W3Suite Backend</v>
+        <v>PostgreSQL Primary</v>
       </c>
       <c r="C15" t="str">
         <v>VPC (VM)</v>
@@ -7145,7 +7145,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>API + Redis + MCP</v>
+        <v>Read/Write</v>
       </c>
     </row>
     <row r="16">
@@ -7153,44 +7153,24 @@
         <v>DATABASE</v>
       </c>
       <c r="B16" t="str">
-        <v>PostgreSQL Primary</v>
+        <v>PostgreSQL Replica</v>
       </c>
       <c r="C16" t="str">
         <v>VPC (VM)</v>
       </c>
       <c r="D16" t="str">
-        <v>Active</v>
+        <v>Standby</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Read/Write</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>DATABASE</v>
-      </c>
-      <c r="B17" t="str">
-        <v>PostgreSQL Replica</v>
-      </c>
-      <c r="C17" t="str">
-        <v>VPC (VM)</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Standby</v>
-      </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
-      <c r="F17" t="str">
         <v>Streaming Replication</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A2:F17"/>
+    <ignoredError numberStoredAsText="1" sqref="A2:F16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/gara-appalto/SERVICE-RESOURCE-MODEL-W3SUITE-FINAL.xlsx
+++ b/docs/gara-appalto/SERVICE-RESOURCE-MODEL-W3SUITE-FINAL.xlsx
@@ -6195,7 +6195,7 @@
         <v>Private Others Registry</v>
       </c>
       <c r="X9" t="str">
-        <v>Resource Recovery</v>
+        <v>Resource: Release and Recovery</v>
       </c>
       <c r="Y9" t="str">
         <v>On-Premise SW/Appliance</v>
@@ -6311,7 +6311,7 @@
         <v>Private Others Registry</v>
       </c>
       <c r="X10" t="str">
-        <v>Resource Recovery</v>
+        <v>Resource: Release and Recovery</v>
       </c>
       <c r="Y10" t="str">
         <v>On-Premise SW/Appliance</v>
@@ -6326,13 +6326,13 @@
         <v>1 month</v>
       </c>
       <c r="AC10" t="str">
-        <v>N/A</v>
+        <v>1 min</v>
       </c>
       <c r="AD10" t="str">
-        <v>N/A</v>
+        <v>1 week</v>
       </c>
       <c r="AE10" t="str">
-        <v xml:space="preserve">Local Resilent </v>
+        <v xml:space="preserve">Region Resilent </v>
       </c>
       <c r="AF10" t="str">
         <v>Manual By Operation</v>
@@ -6341,7 +6341,7 @@
         <v>Hour (1-5)</v>
       </c>
       <c r="AH10" t="str">
-        <v>Hour (1-5)</v>
+        <v>Minutes (1-5)</v>
       </c>
       <c r="AI10" t="str">
         <v>HW/SW vendor</v>
@@ -6463,7 +6463,7 @@
         <v>HW/SW vendor</v>
       </c>
       <c r="AJ11" t="str">
-        <v>Backup Storage, DR Recovery, Retention</v>
+        <v>Backup Storage, Snapshot + Incremental, DR Recovery</v>
       </c>
       <c r="AK11" t="str">
         <v>Public Cloud Consumption</v>
@@ -6543,7 +6543,7 @@
         <v>Object Store (SW bins)</v>
       </c>
       <c r="X12" t="str">
-        <v>Resource Recovery</v>
+        <v>Resource: Release and Recovery</v>
       </c>
       <c r="Y12" t="str">
         <v>On-Premise SW/Appliance</v>
@@ -6659,7 +6659,7 @@
         <v>Object Store (SW bins)</v>
       </c>
       <c r="X13" t="str">
-        <v>Resource Recovery</v>
+        <v>Resource: Release and Recovery</v>
       </c>
       <c r="Y13" t="str">
         <v>On-Premise SW/Appliance</v>
@@ -6891,7 +6891,7 @@
         <v>Object Store (SW bins)</v>
       </c>
       <c r="X15" t="str">
-        <v>Resource Recovery</v>
+        <v>Resource: Release and Recovery</v>
       </c>
       <c r="Y15" t="str">
         <v>On-Premise SW/Appliance</v>
@@ -6945,7 +6945,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:F16"/>
+  <dimension ref="A2:G16"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -6985,6 +6985,9 @@
 (Backup)</v>
       </c>
       <c r="F7" t="str">
+        <v>Backup Type</v>
+      </c>
+      <c r="G7" t="str">
         <v>Notes</v>
       </c>
     </row>
@@ -7007,6 +7010,9 @@
       <c r="F8" t="str">
         <v/>
       </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -7025,6 +7031,9 @@
         <v/>
       </c>
       <c r="F9" t="str">
+        <v>Snapshot + Incr</v>
+      </c>
+      <c r="G9" t="str">
         <v>Proxmox VE Host</v>
       </c>
     </row>
@@ -7045,7 +7054,10 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>Proxmox VE Host + HA Appliance</v>
+        <v>Snapshot + Incr</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Proxmox VE Host + HA</v>
       </c>
     </row>
     <row r="11">
@@ -7065,7 +7077,10 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>NGFW (1-4 CPU)</v>
+        <v>Snapshot + Incr</v>
+      </c>
+      <c r="G11" t="str">
+        <v>NGFW</v>
       </c>
     </row>
     <row r="12">
@@ -7085,7 +7100,10 @@
         <v>Active</v>
       </c>
       <c r="F12" t="str">
-        <v>23€/100GB - DR</v>
+        <v>-</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Backup Target DC2</v>
       </c>
     </row>
     <row r="13">
@@ -7105,6 +7123,9 @@
         <v/>
       </c>
       <c r="F13" t="str">
+        <v>Snapshot + Incr</v>
+      </c>
+      <c r="G13" t="str">
         <v>Nginx + LB</v>
       </c>
     </row>
@@ -7125,6 +7146,9 @@
         <v/>
       </c>
       <c r="F14" t="str">
+        <v>Snapshot + Incr</v>
+      </c>
+      <c r="G14" t="str">
         <v>API + Redis + MCP</v>
       </c>
     </row>
@@ -7145,7 +7169,10 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Read/Write</v>
+        <v>Snapshot + Incr</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Read/Write + WAL</v>
       </c>
     </row>
     <row r="16">
@@ -7165,12 +7192,15 @@
         <v/>
       </c>
       <c r="F16" t="str">
+        <v>Snapshot + Incr</v>
+      </c>
+      <c r="G16" t="str">
         <v>Streaming Replication</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A2:F16"/>
+    <ignoredError numberStoredAsText="1" sqref="A2:G16"/>
   </ignoredErrors>
 </worksheet>
 </file>